--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -769,13 +769,13 @@
     <t>Shiaijo B</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
     <t>Red</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>White</t>
   </si>
   <si>
     <t>V</t>
@@ -6925,7 +6925,7 @@
       <c r="O4" s="20"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B5" s="21"/>
@@ -6935,10 +6935,10 @@
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J5" s="21"/>
@@ -6948,13 +6948,13 @@
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
-      <c r="O5" s="24" t="s">
+      <c r="O5" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -6962,10 +6962,10 @@
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I6" s="21" t="str">
-        <f>data!$B$49</f>
+        <f>data!$B$50</f>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -6973,7 +6973,7 @@
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
       <c r="O6" s="21" t="str">
-        <f>data!$B$50</f>
+        <f>data!$B$49</f>
       </c>
     </row>
     <row r="7">
@@ -7098,7 +7098,7 @@
     </row>
     <row r="13">
       <c r="A13" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B13" s="21" t="s">
         <v>242</v>
@@ -7114,10 +7114,10 @@
         <v>242</v>
       </c>
       <c r="G13" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I13" s="21" t="str">
-        <f>data!$B$49</f>
+        <f>data!$B$50</f>
       </c>
       <c r="J13" s="21" t="s">
         <v>242</v>
@@ -7133,7 +7133,7 @@
         <v>242</v>
       </c>
       <c r="O13" s="21" t="str">
-        <f>data!$B$50</f>
+        <f>data!$B$49</f>
       </c>
     </row>
     <row r="14">
@@ -7161,7 +7161,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B18" s="21"/>
@@ -7171,10 +7171,10 @@
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J18" s="21"/>
@@ -7184,13 +7184,13 @@
       </c>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
-      <c r="O18" s="24" t="s">
+      <c r="O18" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -7198,10 +7198,10 @@
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I19" s="21" t="str">
-        <f>data!$B$49</f>
+        <f>data!$B$51</f>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -7209,7 +7209,7 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21" t="str">
-        <f>data!$B$51</f>
+        <f>data!$B$49</f>
       </c>
     </row>
     <row r="20">
@@ -7334,7 +7334,7 @@
     </row>
     <row r="26">
       <c r="A26" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B26" s="21" t="s">
         <v>242</v>
@@ -7350,10 +7350,10 @@
         <v>242</v>
       </c>
       <c r="G26" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I26" s="21" t="str">
-        <f>data!$B$49</f>
+        <f>data!$B$51</f>
       </c>
       <c r="J26" s="21" t="s">
         <v>242</v>
@@ -7369,7 +7369,7 @@
         <v>242</v>
       </c>
       <c r="O26" s="21" t="str">
-        <f>data!$B$51</f>
+        <f>data!$B$49</f>
       </c>
     </row>
     <row r="27">
@@ -7397,7 +7397,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B31" s="21"/>
@@ -7407,10 +7407,10 @@
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
-      <c r="G31" s="24" t="s">
+      <c r="G31" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I31" s="23" t="s">
+      <c r="I31" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J31" s="21"/>
@@ -7420,13 +7420,13 @@
       </c>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
-      <c r="O31" s="24" t="s">
+      <c r="O31" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -7434,10 +7434,10 @@
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I32" s="21" t="str">
-        <f>data!$B$50</f>
+        <f>data!$B$51</f>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
@@ -7445,7 +7445,7 @@
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="21" t="str">
-        <f>data!$B$51</f>
+        <f>data!$B$50</f>
       </c>
     </row>
     <row r="33">
@@ -7570,7 +7570,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B39" s="21" t="s">
         <v>242</v>
@@ -7586,10 +7586,10 @@
         <v>242</v>
       </c>
       <c r="G39" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I39" s="21" t="str">
-        <f>data!$B$50</f>
+        <f>data!$B$51</f>
       </c>
       <c r="J39" s="21" t="s">
         <v>242</v>
@@ -7605,7 +7605,7 @@
         <v>242</v>
       </c>
       <c r="O39" s="21" t="str">
-        <f>data!$B$51</f>
+        <f>data!$B$50</f>
       </c>
     </row>
     <row r="40">
@@ -7633,7 +7633,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B44" s="21"/>
@@ -7643,13 +7643,13 @@
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -7657,7 +7657,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="46">
@@ -7727,7 +7727,7 @@
     </row>
     <row r="52">
       <c r="A52" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B52" s="21" t="s">
         <v>242</v>
@@ -7743,7 +7743,7 @@
         <v>242</v>
       </c>
       <c r="G52" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="53">
@@ -7816,7 +7816,7 @@
       <c r="O61" s="20"/>
     </row>
     <row r="62">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B62" s="21"/>
@@ -7826,10 +7826,10 @@
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
-      <c r="G62" s="24" t="s">
+      <c r="G62" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I62" s="23" t="s">
+      <c r="I62" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J62" s="21"/>
@@ -7839,13 +7839,13 @@
       </c>
       <c r="M62" s="21"/>
       <c r="N62" s="21"/>
-      <c r="O62" s="24" t="s">
+      <c r="O62" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
@@ -7853,10 +7853,10 @@
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
       <c r="G63" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
       <c r="I63" s="21" t="str">
-        <f>data!$B$52</f>
+        <f>data!$B$53</f>
       </c>
       <c r="J63" s="21"/>
       <c r="K63" s="21"/>
@@ -7864,7 +7864,7 @@
       <c r="M63" s="21"/>
       <c r="N63" s="21"/>
       <c r="O63" s="21" t="str">
-        <f>data!$B$53</f>
+        <f>data!$B$52</f>
       </c>
     </row>
     <row r="64">
@@ -7989,7 +7989,7 @@
     </row>
     <row r="70">
       <c r="A70" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B70" s="21" t="s">
         <v>242</v>
@@ -8005,10 +8005,10 @@
         <v>242</v>
       </c>
       <c r="G70" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
       <c r="I70" s="21" t="str">
-        <f>data!$B$52</f>
+        <f>data!$B$53</f>
       </c>
       <c r="J70" s="21" t="s">
         <v>242</v>
@@ -8024,7 +8024,7 @@
         <v>242</v>
       </c>
       <c r="O70" s="21" t="str">
-        <f>data!$B$53</f>
+        <f>data!$B$52</f>
       </c>
     </row>
     <row r="71">
@@ -8052,7 +8052,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B75" s="21"/>
@@ -8062,10 +8062,10 @@
       </c>
       <c r="E75" s="21"/>
       <c r="F75" s="21"/>
-      <c r="G75" s="24" t="s">
+      <c r="G75" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I75" s="23" t="s">
+      <c r="I75" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J75" s="21"/>
@@ -8075,13 +8075,13 @@
       </c>
       <c r="M75" s="21"/>
       <c r="N75" s="21"/>
-      <c r="O75" s="24" t="s">
+      <c r="O75" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B76" s="21"/>
       <c r="C76" s="21"/>
@@ -8089,10 +8089,10 @@
       <c r="E76" s="21"/>
       <c r="F76" s="21"/>
       <c r="G76" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="I76" s="21" t="str">
-        <f>data!$B$52</f>
+        <f>data!$B$54</f>
       </c>
       <c r="J76" s="21"/>
       <c r="K76" s="21"/>
@@ -8100,7 +8100,7 @@
       <c r="M76" s="21"/>
       <c r="N76" s="21"/>
       <c r="O76" s="21" t="str">
-        <f>data!$B$54</f>
+        <f>data!$B$52</f>
       </c>
     </row>
     <row r="77">
@@ -8225,7 +8225,7 @@
     </row>
     <row r="83">
       <c r="A83" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B83" s="21" t="s">
         <v>242</v>
@@ -8241,10 +8241,10 @@
         <v>242</v>
       </c>
       <c r="G83" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="I83" s="21" t="str">
-        <f>data!$B$52</f>
+        <f>data!$B$54</f>
       </c>
       <c r="J83" s="21" t="s">
         <v>242</v>
@@ -8260,7 +8260,7 @@
         <v>242</v>
       </c>
       <c r="O83" s="21" t="str">
-        <f>data!$B$54</f>
+        <f>data!$B$52</f>
       </c>
     </row>
     <row r="84">
@@ -8288,7 +8288,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B88" s="21"/>
@@ -8298,10 +8298,10 @@
       </c>
       <c r="E88" s="21"/>
       <c r="F88" s="21"/>
-      <c r="G88" s="24" t="s">
+      <c r="G88" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I88" s="23" t="s">
+      <c r="I88" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J88" s="21"/>
@@ -8311,13 +8311,13 @@
       </c>
       <c r="M88" s="21"/>
       <c r="N88" s="21"/>
-      <c r="O88" s="24" t="s">
+      <c r="O88" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
@@ -8325,10 +8325,10 @@
       <c r="E89" s="21"/>
       <c r="F89" s="21"/>
       <c r="G89" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$8</f>
       </c>
       <c r="I89" s="21" t="str">
-        <f>data!$B$53</f>
+        <f>data!$B$54</f>
       </c>
       <c r="J89" s="21"/>
       <c r="K89" s="21"/>
@@ -8336,7 +8336,7 @@
       <c r="M89" s="21"/>
       <c r="N89" s="21"/>
       <c r="O89" s="21" t="str">
-        <f>data!$B$54</f>
+        <f>data!$B$53</f>
       </c>
     </row>
     <row r="90">
@@ -8461,7 +8461,7 @@
     </row>
     <row r="96">
       <c r="A96" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B96" s="21" t="s">
         <v>242</v>
@@ -8477,10 +8477,10 @@
         <v>242</v>
       </c>
       <c r="G96" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$8</f>
       </c>
       <c r="I96" s="21" t="str">
-        <f>data!$B$53</f>
+        <f>data!$B$54</f>
       </c>
       <c r="J96" s="21" t="s">
         <v>242</v>
@@ -8496,7 +8496,7 @@
         <v>242</v>
       </c>
       <c r="O96" s="21" t="str">
-        <f>data!$B$54</f>
+        <f>data!$B$53</f>
       </c>
     </row>
     <row r="97">
@@ -8574,7 +8574,7 @@
       <c r="O104" s="20"/>
     </row>
     <row r="105">
-      <c r="A105" s="23" t="s">
+      <c r="A105" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B105" s="21"/>
@@ -8584,10 +8584,10 @@
       </c>
       <c r="E105" s="21"/>
       <c r="F105" s="21"/>
-      <c r="G105" s="24" t="s">
+      <c r="G105" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I105" s="23" t="s">
+      <c r="I105" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J105" s="21"/>
@@ -8597,13 +8597,13 @@
       </c>
       <c r="M105" s="21"/>
       <c r="N105" s="21"/>
-      <c r="O105" s="24" t="s">
+      <c r="O105" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
       <c r="B106" s="21"/>
       <c r="C106" s="21"/>
@@ -8611,10 +8611,10 @@
       <c r="E106" s="21"/>
       <c r="F106" s="21"/>
       <c r="G106" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I106" s="21" t="str">
-        <f>data!$B$55</f>
+        <f>data!$B$56</f>
       </c>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
@@ -8622,7 +8622,7 @@
       <c r="M106" s="21"/>
       <c r="N106" s="21"/>
       <c r="O106" s="21" t="str">
-        <f>data!$B$56</f>
+        <f>data!$B$55</f>
       </c>
     </row>
     <row r="107">
@@ -8747,7 +8747,7 @@
     </row>
     <row r="113">
       <c r="A113" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
       <c r="B113" s="21" t="s">
         <v>242</v>
@@ -8763,10 +8763,10 @@
         <v>242</v>
       </c>
       <c r="G113" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I113" s="21" t="str">
-        <f>data!$B$55</f>
+        <f>data!$B$56</f>
       </c>
       <c r="J113" s="21" t="s">
         <v>242</v>
@@ -8782,7 +8782,7 @@
         <v>242</v>
       </c>
       <c r="O113" s="21" t="str">
-        <f>data!$B$56</f>
+        <f>data!$B$55</f>
       </c>
     </row>
     <row r="114">
@@ -8810,7 +8810,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="23" t="s">
+      <c r="A118" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B118" s="21"/>
@@ -8820,10 +8820,10 @@
       </c>
       <c r="E118" s="21"/>
       <c r="F118" s="21"/>
-      <c r="G118" s="24" t="s">
+      <c r="G118" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I118" s="23" t="s">
+      <c r="I118" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J118" s="21"/>
@@ -8833,13 +8833,13 @@
       </c>
       <c r="M118" s="21"/>
       <c r="N118" s="21"/>
-      <c r="O118" s="24" t="s">
+      <c r="O118" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$12</f>
       </c>
       <c r="B119" s="21"/>
       <c r="C119" s="21"/>
@@ -8847,10 +8847,10 @@
       <c r="E119" s="21"/>
       <c r="F119" s="21"/>
       <c r="G119" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I119" s="21" t="str">
-        <f>data!$B$55</f>
+        <f>data!$B$57</f>
       </c>
       <c r="J119" s="21"/>
       <c r="K119" s="21"/>
@@ -8858,7 +8858,7 @@
       <c r="M119" s="21"/>
       <c r="N119" s="21"/>
       <c r="O119" s="21" t="str">
-        <f>data!$B$57</f>
+        <f>data!$B$55</f>
       </c>
     </row>
     <row r="120">
@@ -8983,7 +8983,7 @@
     </row>
     <row r="126">
       <c r="A126" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$12</f>
       </c>
       <c r="B126" s="21" t="s">
         <v>242</v>
@@ -8999,10 +8999,10 @@
         <v>242</v>
       </c>
       <c r="G126" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I126" s="21" t="str">
-        <f>data!$B$55</f>
+        <f>data!$B$57</f>
       </c>
       <c r="J126" s="21" t="s">
         <v>242</v>
@@ -9018,7 +9018,7 @@
         <v>242</v>
       </c>
       <c r="O126" s="21" t="str">
-        <f>data!$B$57</f>
+        <f>data!$B$55</f>
       </c>
     </row>
     <row r="127">
@@ -9046,7 +9046,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="23" t="s">
+      <c r="A131" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B131" s="21"/>
@@ -9056,10 +9056,10 @@
       </c>
       <c r="E131" s="21"/>
       <c r="F131" s="21"/>
-      <c r="G131" s="24" t="s">
+      <c r="G131" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I131" s="23" t="s">
+      <c r="I131" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J131" s="21"/>
@@ -9069,13 +9069,13 @@
       </c>
       <c r="M131" s="21"/>
       <c r="N131" s="21"/>
-      <c r="O131" s="24" t="s">
+      <c r="O131" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$12</f>
       </c>
       <c r="B132" s="21"/>
       <c r="C132" s="21"/>
@@ -9083,10 +9083,10 @@
       <c r="E132" s="21"/>
       <c r="F132" s="21"/>
       <c r="G132" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$11</f>
       </c>
       <c r="I132" s="21" t="str">
-        <f>data!$B$56</f>
+        <f>data!$B$57</f>
       </c>
       <c r="J132" s="21"/>
       <c r="K132" s="21"/>
@@ -9094,7 +9094,7 @@
       <c r="M132" s="21"/>
       <c r="N132" s="21"/>
       <c r="O132" s="21" t="str">
-        <f>data!$B$57</f>
+        <f>data!$B$56</f>
       </c>
     </row>
     <row r="133">
@@ -9219,7 +9219,7 @@
     </row>
     <row r="139">
       <c r="A139" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$12</f>
       </c>
       <c r="B139" s="21" t="s">
         <v>242</v>
@@ -9235,10 +9235,10 @@
         <v>242</v>
       </c>
       <c r="G139" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$11</f>
       </c>
       <c r="I139" s="21" t="str">
-        <f>data!$B$56</f>
+        <f>data!$B$57</f>
       </c>
       <c r="J139" s="21" t="s">
         <v>242</v>
@@ -9254,7 +9254,7 @@
         <v>242</v>
       </c>
       <c r="O139" s="21" t="str">
-        <f>data!$B$57</f>
+        <f>data!$B$56</f>
       </c>
     </row>
     <row r="140">
@@ -9332,7 +9332,7 @@
       <c r="O147" s="20"/>
     </row>
     <row r="148">
-      <c r="A148" s="23" t="s">
+      <c r="A148" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B148" s="21"/>
@@ -9342,10 +9342,10 @@
       </c>
       <c r="E148" s="21"/>
       <c r="F148" s="21"/>
-      <c r="G148" s="24" t="s">
+      <c r="G148" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I148" s="23" t="s">
+      <c r="I148" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J148" s="21"/>
@@ -9355,13 +9355,13 @@
       </c>
       <c r="M148" s="21"/>
       <c r="N148" s="21"/>
-      <c r="O148" s="24" t="s">
+      <c r="O148" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$14</f>
       </c>
       <c r="B149" s="21"/>
       <c r="C149" s="21"/>
@@ -9369,10 +9369,10 @@
       <c r="E149" s="21"/>
       <c r="F149" s="21"/>
       <c r="G149" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$13</f>
       </c>
       <c r="I149" s="21" t="str">
-        <f>data!$B$58</f>
+        <f>data!$B$59</f>
       </c>
       <c r="J149" s="21"/>
       <c r="K149" s="21"/>
@@ -9380,7 +9380,7 @@
       <c r="M149" s="21"/>
       <c r="N149" s="21"/>
       <c r="O149" s="21" t="str">
-        <f>data!$B$59</f>
+        <f>data!$B$58</f>
       </c>
     </row>
     <row r="150">
@@ -9505,7 +9505,7 @@
     </row>
     <row r="156">
       <c r="A156" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$14</f>
       </c>
       <c r="B156" s="21" t="s">
         <v>242</v>
@@ -9521,10 +9521,10 @@
         <v>242</v>
       </c>
       <c r="G156" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$13</f>
       </c>
       <c r="I156" s="21" t="str">
-        <f>data!$B$58</f>
+        <f>data!$B$59</f>
       </c>
       <c r="J156" s="21" t="s">
         <v>242</v>
@@ -9540,7 +9540,7 @@
         <v>242</v>
       </c>
       <c r="O156" s="21" t="str">
-        <f>data!$B$59</f>
+        <f>data!$B$58</f>
       </c>
     </row>
     <row r="157">
@@ -9568,7 +9568,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="23" t="s">
+      <c r="A161" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B161" s="21"/>
@@ -9578,10 +9578,10 @@
       </c>
       <c r="E161" s="21"/>
       <c r="F161" s="21"/>
-      <c r="G161" s="24" t="s">
+      <c r="G161" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I161" s="23" t="s">
+      <c r="I161" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J161" s="21"/>
@@ -9591,13 +9591,13 @@
       </c>
       <c r="M161" s="21"/>
       <c r="N161" s="21"/>
-      <c r="O161" s="24" t="s">
+      <c r="O161" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$15</f>
       </c>
       <c r="B162" s="21"/>
       <c r="C162" s="21"/>
@@ -9605,10 +9605,10 @@
       <c r="E162" s="21"/>
       <c r="F162" s="21"/>
       <c r="G162" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$13</f>
       </c>
       <c r="I162" s="21" t="str">
-        <f>data!$B$58</f>
+        <f>data!$B$60</f>
       </c>
       <c r="J162" s="21"/>
       <c r="K162" s="21"/>
@@ -9616,7 +9616,7 @@
       <c r="M162" s="21"/>
       <c r="N162" s="21"/>
       <c r="O162" s="21" t="str">
-        <f>data!$B$60</f>
+        <f>data!$B$58</f>
       </c>
     </row>
     <row r="163">
@@ -9741,7 +9741,7 @@
     </row>
     <row r="169">
       <c r="A169" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$15</f>
       </c>
       <c r="B169" s="21" t="s">
         <v>242</v>
@@ -9757,10 +9757,10 @@
         <v>242</v>
       </c>
       <c r="G169" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$13</f>
       </c>
       <c r="I169" s="21" t="str">
-        <f>data!$B$58</f>
+        <f>data!$B$60</f>
       </c>
       <c r="J169" s="21" t="s">
         <v>242</v>
@@ -9776,7 +9776,7 @@
         <v>242</v>
       </c>
       <c r="O169" s="21" t="str">
-        <f>data!$B$60</f>
+        <f>data!$B$58</f>
       </c>
     </row>
     <row r="170">
@@ -9804,7 +9804,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="23" t="s">
+      <c r="A174" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B174" s="21"/>
@@ -9814,10 +9814,10 @@
       </c>
       <c r="E174" s="21"/>
       <c r="F174" s="21"/>
-      <c r="G174" s="24" t="s">
+      <c r="G174" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I174" s="23" t="s">
+      <c r="I174" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J174" s="21"/>
@@ -9827,13 +9827,13 @@
       </c>
       <c r="M174" s="21"/>
       <c r="N174" s="21"/>
-      <c r="O174" s="24" t="s">
+      <c r="O174" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$15</f>
       </c>
       <c r="B175" s="21"/>
       <c r="C175" s="21"/>
@@ -9841,10 +9841,10 @@
       <c r="E175" s="21"/>
       <c r="F175" s="21"/>
       <c r="G175" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$14</f>
       </c>
       <c r="I175" s="21" t="str">
-        <f>data!$B$59</f>
+        <f>data!$B$60</f>
       </c>
       <c r="J175" s="21"/>
       <c r="K175" s="21"/>
@@ -9852,7 +9852,7 @@
       <c r="M175" s="21"/>
       <c r="N175" s="21"/>
       <c r="O175" s="21" t="str">
-        <f>data!$B$60</f>
+        <f>data!$B$59</f>
       </c>
     </row>
     <row r="176">
@@ -9977,7 +9977,7 @@
     </row>
     <row r="182">
       <c r="A182" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$15</f>
       </c>
       <c r="B182" s="21" t="s">
         <v>242</v>
@@ -9993,10 +9993,10 @@
         <v>242</v>
       </c>
       <c r="G182" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$14</f>
       </c>
       <c r="I182" s="21" t="str">
-        <f>data!$B$59</f>
+        <f>data!$B$60</f>
       </c>
       <c r="J182" s="21" t="s">
         <v>242</v>
@@ -10012,7 +10012,7 @@
         <v>242</v>
       </c>
       <c r="O182" s="21" t="str">
-        <f>data!$B$60</f>
+        <f>data!$B$59</f>
       </c>
     </row>
     <row r="183">
@@ -10090,7 +10090,7 @@
       <c r="O190" s="20"/>
     </row>
     <row r="191">
-      <c r="A191" s="23" t="s">
+      <c r="A191" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="21"/>
@@ -10100,10 +10100,10 @@
       </c>
       <c r="E191" s="21"/>
       <c r="F191" s="21"/>
-      <c r="G191" s="24" t="s">
+      <c r="G191" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I191" s="23" t="s">
+      <c r="I191" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J191" s="21"/>
@@ -10113,13 +10113,13 @@
       </c>
       <c r="M191" s="21"/>
       <c r="N191" s="21"/>
-      <c r="O191" s="24" t="s">
+      <c r="O191" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$17</f>
       </c>
       <c r="B192" s="21"/>
       <c r="C192" s="21"/>
@@ -10127,10 +10127,10 @@
       <c r="E192" s="21"/>
       <c r="F192" s="21"/>
       <c r="G192" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$16</f>
       </c>
       <c r="I192" s="21" t="str">
-        <f>data!$B$61</f>
+        <f>data!$B$62</f>
       </c>
       <c r="J192" s="21"/>
       <c r="K192" s="21"/>
@@ -10138,7 +10138,7 @@
       <c r="M192" s="21"/>
       <c r="N192" s="21"/>
       <c r="O192" s="21" t="str">
-        <f>data!$B$62</f>
+        <f>data!$B$61</f>
       </c>
     </row>
     <row r="193">
@@ -10263,7 +10263,7 @@
     </row>
     <row r="199">
       <c r="A199" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$17</f>
       </c>
       <c r="B199" s="21" t="s">
         <v>242</v>
@@ -10279,10 +10279,10 @@
         <v>242</v>
       </c>
       <c r="G199" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$16</f>
       </c>
       <c r="I199" s="21" t="str">
-        <f>data!$B$61</f>
+        <f>data!$B$62</f>
       </c>
       <c r="J199" s="21" t="s">
         <v>242</v>
@@ -10298,7 +10298,7 @@
         <v>242</v>
       </c>
       <c r="O199" s="21" t="str">
-        <f>data!$B$62</f>
+        <f>data!$B$61</f>
       </c>
     </row>
     <row r="200">
@@ -10326,7 +10326,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="23" t="s">
+      <c r="A204" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B204" s="21"/>
@@ -10336,10 +10336,10 @@
       </c>
       <c r="E204" s="21"/>
       <c r="F204" s="21"/>
-      <c r="G204" s="24" t="s">
+      <c r="G204" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I204" s="23" t="s">
+      <c r="I204" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J204" s="21"/>
@@ -10349,13 +10349,13 @@
       </c>
       <c r="M204" s="21"/>
       <c r="N204" s="21"/>
-      <c r="O204" s="24" t="s">
+      <c r="O204" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$18</f>
       </c>
       <c r="B205" s="21"/>
       <c r="C205" s="21"/>
@@ -10363,10 +10363,10 @@
       <c r="E205" s="21"/>
       <c r="F205" s="21"/>
       <c r="G205" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$16</f>
       </c>
       <c r="I205" s="21" t="str">
-        <f>data!$B$61</f>
+        <f>data!$B$63</f>
       </c>
       <c r="J205" s="21"/>
       <c r="K205" s="21"/>
@@ -10374,7 +10374,7 @@
       <c r="M205" s="21"/>
       <c r="N205" s="21"/>
       <c r="O205" s="21" t="str">
-        <f>data!$B$63</f>
+        <f>data!$B$61</f>
       </c>
     </row>
     <row r="206">
@@ -10499,7 +10499,7 @@
     </row>
     <row r="212">
       <c r="A212" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$18</f>
       </c>
       <c r="B212" s="21" t="s">
         <v>242</v>
@@ -10515,10 +10515,10 @@
         <v>242</v>
       </c>
       <c r="G212" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$16</f>
       </c>
       <c r="I212" s="21" t="str">
-        <f>data!$B$61</f>
+        <f>data!$B$63</f>
       </c>
       <c r="J212" s="21" t="s">
         <v>242</v>
@@ -10534,7 +10534,7 @@
         <v>242</v>
       </c>
       <c r="O212" s="21" t="str">
-        <f>data!$B$63</f>
+        <f>data!$B$61</f>
       </c>
     </row>
     <row r="213">
@@ -10562,7 +10562,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="23" t="s">
+      <c r="A217" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B217" s="21"/>
@@ -10572,10 +10572,10 @@
       </c>
       <c r="E217" s="21"/>
       <c r="F217" s="21"/>
-      <c r="G217" s="24" t="s">
+      <c r="G217" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I217" s="23" t="s">
+      <c r="I217" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J217" s="21"/>
@@ -10585,13 +10585,13 @@
       </c>
       <c r="M217" s="21"/>
       <c r="N217" s="21"/>
-      <c r="O217" s="24" t="s">
+      <c r="O217" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$18</f>
       </c>
       <c r="B218" s="21"/>
       <c r="C218" s="21"/>
@@ -10599,10 +10599,10 @@
       <c r="E218" s="21"/>
       <c r="F218" s="21"/>
       <c r="G218" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$17</f>
       </c>
       <c r="I218" s="21" t="str">
-        <f>data!$B$62</f>
+        <f>data!$B$63</f>
       </c>
       <c r="J218" s="21"/>
       <c r="K218" s="21"/>
@@ -10610,7 +10610,7 @@
       <c r="M218" s="21"/>
       <c r="N218" s="21"/>
       <c r="O218" s="21" t="str">
-        <f>data!$B$63</f>
+        <f>data!$B$62</f>
       </c>
     </row>
     <row r="219">
@@ -10735,7 +10735,7 @@
     </row>
     <row r="225">
       <c r="A225" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$18</f>
       </c>
       <c r="B225" s="21" t="s">
         <v>242</v>
@@ -10751,10 +10751,10 @@
         <v>242</v>
       </c>
       <c r="G225" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$17</f>
       </c>
       <c r="I225" s="21" t="str">
-        <f>data!$B$62</f>
+        <f>data!$B$63</f>
       </c>
       <c r="J225" s="21" t="s">
         <v>242</v>
@@ -10770,7 +10770,7 @@
         <v>242</v>
       </c>
       <c r="O225" s="21" t="str">
-        <f>data!$B$63</f>
+        <f>data!$B$62</f>
       </c>
     </row>
     <row r="226">
@@ -10848,7 +10848,7 @@
       <c r="O233" s="20"/>
     </row>
     <row r="234">
-      <c r="A234" s="23" t="s">
+      <c r="A234" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B234" s="21"/>
@@ -10858,10 +10858,10 @@
       </c>
       <c r="E234" s="21"/>
       <c r="F234" s="21"/>
-      <c r="G234" s="24" t="s">
+      <c r="G234" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I234" s="23" t="s">
+      <c r="I234" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J234" s="21"/>
@@ -10871,13 +10871,13 @@
       </c>
       <c r="M234" s="21"/>
       <c r="N234" s="21"/>
-      <c r="O234" s="24" t="s">
+      <c r="O234" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$20</f>
       </c>
       <c r="B235" s="21"/>
       <c r="C235" s="21"/>
@@ -10885,10 +10885,10 @@
       <c r="E235" s="21"/>
       <c r="F235" s="21"/>
       <c r="G235" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$19</f>
       </c>
       <c r="I235" s="21" t="str">
-        <f>data!$B$64</f>
+        <f>data!$B$65</f>
       </c>
       <c r="J235" s="21"/>
       <c r="K235" s="21"/>
@@ -10896,7 +10896,7 @@
       <c r="M235" s="21"/>
       <c r="N235" s="21"/>
       <c r="O235" s="21" t="str">
-        <f>data!$B$65</f>
+        <f>data!$B$64</f>
       </c>
     </row>
     <row r="236">
@@ -11021,7 +11021,7 @@
     </row>
     <row r="242">
       <c r="A242" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$20</f>
       </c>
       <c r="B242" s="21" t="s">
         <v>242</v>
@@ -11037,10 +11037,10 @@
         <v>242</v>
       </c>
       <c r="G242" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$19</f>
       </c>
       <c r="I242" s="21" t="str">
-        <f>data!$B$64</f>
+        <f>data!$B$65</f>
       </c>
       <c r="J242" s="21" t="s">
         <v>242</v>
@@ -11056,7 +11056,7 @@
         <v>242</v>
       </c>
       <c r="O242" s="21" t="str">
-        <f>data!$B$65</f>
+        <f>data!$B$64</f>
       </c>
     </row>
     <row r="243">
@@ -11084,7 +11084,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="23" t="s">
+      <c r="A247" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B247" s="21"/>
@@ -11094,10 +11094,10 @@
       </c>
       <c r="E247" s="21"/>
       <c r="F247" s="21"/>
-      <c r="G247" s="24" t="s">
+      <c r="G247" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I247" s="23" t="s">
+      <c r="I247" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J247" s="21"/>
@@ -11107,13 +11107,13 @@
       </c>
       <c r="M247" s="21"/>
       <c r="N247" s="21"/>
-      <c r="O247" s="24" t="s">
+      <c r="O247" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$21</f>
       </c>
       <c r="B248" s="21"/>
       <c r="C248" s="21"/>
@@ -11121,10 +11121,10 @@
       <c r="E248" s="21"/>
       <c r="F248" s="21"/>
       <c r="G248" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$19</f>
       </c>
       <c r="I248" s="21" t="str">
-        <f>data!$B$64</f>
+        <f>data!$B$66</f>
       </c>
       <c r="J248" s="21"/>
       <c r="K248" s="21"/>
@@ -11132,7 +11132,7 @@
       <c r="M248" s="21"/>
       <c r="N248" s="21"/>
       <c r="O248" s="21" t="str">
-        <f>data!$B$66</f>
+        <f>data!$B$64</f>
       </c>
     </row>
     <row r="249">
@@ -11257,7 +11257,7 @@
     </row>
     <row r="255">
       <c r="A255" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$21</f>
       </c>
       <c r="B255" s="21" t="s">
         <v>242</v>
@@ -11273,10 +11273,10 @@
         <v>242</v>
       </c>
       <c r="G255" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$19</f>
       </c>
       <c r="I255" s="21" t="str">
-        <f>data!$B$64</f>
+        <f>data!$B$66</f>
       </c>
       <c r="J255" s="21" t="s">
         <v>242</v>
@@ -11292,7 +11292,7 @@
         <v>242</v>
       </c>
       <c r="O255" s="21" t="str">
-        <f>data!$B$66</f>
+        <f>data!$B$64</f>
       </c>
     </row>
     <row r="256">
@@ -11320,7 +11320,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="23" t="s">
+      <c r="A260" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B260" s="21"/>
@@ -11330,10 +11330,10 @@
       </c>
       <c r="E260" s="21"/>
       <c r="F260" s="21"/>
-      <c r="G260" s="24" t="s">
+      <c r="G260" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I260" s="23" t="s">
+      <c r="I260" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J260" s="21"/>
@@ -11343,13 +11343,13 @@
       </c>
       <c r="M260" s="21"/>
       <c r="N260" s="21"/>
-      <c r="O260" s="24" t="s">
+      <c r="O260" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$21</f>
       </c>
       <c r="B261" s="21"/>
       <c r="C261" s="21"/>
@@ -11357,10 +11357,10 @@
       <c r="E261" s="21"/>
       <c r="F261" s="21"/>
       <c r="G261" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$20</f>
       </c>
       <c r="I261" s="21" t="str">
-        <f>data!$B$65</f>
+        <f>data!$B$66</f>
       </c>
       <c r="J261" s="21"/>
       <c r="K261" s="21"/>
@@ -11368,7 +11368,7 @@
       <c r="M261" s="21"/>
       <c r="N261" s="21"/>
       <c r="O261" s="21" t="str">
-        <f>data!$B$66</f>
+        <f>data!$B$65</f>
       </c>
     </row>
     <row r="262">
@@ -11493,7 +11493,7 @@
     </row>
     <row r="268">
       <c r="A268" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$21</f>
       </c>
       <c r="B268" s="21" t="s">
         <v>242</v>
@@ -11509,10 +11509,10 @@
         <v>242</v>
       </c>
       <c r="G268" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$20</f>
       </c>
       <c r="I268" s="21" t="str">
-        <f>data!$B$65</f>
+        <f>data!$B$66</f>
       </c>
       <c r="J268" s="21" t="s">
         <v>242</v>
@@ -11528,7 +11528,7 @@
         <v>242</v>
       </c>
       <c r="O268" s="21" t="str">
-        <f>data!$B$66</f>
+        <f>data!$B$65</f>
       </c>
     </row>
     <row r="269">
@@ -11606,7 +11606,7 @@
       <c r="O276" s="20"/>
     </row>
     <row r="277">
-      <c r="A277" s="23" t="s">
+      <c r="A277" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B277" s="21"/>
@@ -11616,10 +11616,10 @@
       </c>
       <c r="E277" s="21"/>
       <c r="F277" s="21"/>
-      <c r="G277" s="24" t="s">
+      <c r="G277" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I277" s="23" t="s">
+      <c r="I277" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J277" s="21"/>
@@ -11629,13 +11629,13 @@
       </c>
       <c r="M277" s="21"/>
       <c r="N277" s="21"/>
-      <c r="O277" s="24" t="s">
+      <c r="O277" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$23</f>
       </c>
       <c r="B278" s="21"/>
       <c r="C278" s="21"/>
@@ -11643,10 +11643,10 @@
       <c r="E278" s="21"/>
       <c r="F278" s="21"/>
       <c r="G278" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$22</f>
       </c>
       <c r="I278" s="21" t="str">
-        <f>data!$B$67</f>
+        <f>data!$B$68</f>
       </c>
       <c r="J278" s="21"/>
       <c r="K278" s="21"/>
@@ -11654,7 +11654,7 @@
       <c r="M278" s="21"/>
       <c r="N278" s="21"/>
       <c r="O278" s="21" t="str">
-        <f>data!$B$68</f>
+        <f>data!$B$67</f>
       </c>
     </row>
     <row r="279">
@@ -11779,7 +11779,7 @@
     </row>
     <row r="285">
       <c r="A285" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$23</f>
       </c>
       <c r="B285" s="21" t="s">
         <v>242</v>
@@ -11795,10 +11795,10 @@
         <v>242</v>
       </c>
       <c r="G285" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$22</f>
       </c>
       <c r="I285" s="21" t="str">
-        <f>data!$B$67</f>
+        <f>data!$B$68</f>
       </c>
       <c r="J285" s="21" t="s">
         <v>242</v>
@@ -11814,7 +11814,7 @@
         <v>242</v>
       </c>
       <c r="O285" s="21" t="str">
-        <f>data!$B$68</f>
+        <f>data!$B$67</f>
       </c>
     </row>
     <row r="286">
@@ -11842,7 +11842,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="23" t="s">
+      <c r="A290" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B290" s="21"/>
@@ -11852,10 +11852,10 @@
       </c>
       <c r="E290" s="21"/>
       <c r="F290" s="21"/>
-      <c r="G290" s="24" t="s">
+      <c r="G290" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I290" s="23" t="s">
+      <c r="I290" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J290" s="21"/>
@@ -11865,13 +11865,13 @@
       </c>
       <c r="M290" s="21"/>
       <c r="N290" s="21"/>
-      <c r="O290" s="24" t="s">
+      <c r="O290" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$24</f>
       </c>
       <c r="B291" s="21"/>
       <c r="C291" s="21"/>
@@ -11879,10 +11879,10 @@
       <c r="E291" s="21"/>
       <c r="F291" s="21"/>
       <c r="G291" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$22</f>
       </c>
       <c r="I291" s="21" t="str">
-        <f>data!$B$67</f>
+        <f>data!$B$69</f>
       </c>
       <c r="J291" s="21"/>
       <c r="K291" s="21"/>
@@ -11890,7 +11890,7 @@
       <c r="M291" s="21"/>
       <c r="N291" s="21"/>
       <c r="O291" s="21" t="str">
-        <f>data!$B$69</f>
+        <f>data!$B$67</f>
       </c>
     </row>
     <row r="292">
@@ -12015,7 +12015,7 @@
     </row>
     <row r="298">
       <c r="A298" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$24</f>
       </c>
       <c r="B298" s="21" t="s">
         <v>242</v>
@@ -12031,10 +12031,10 @@
         <v>242</v>
       </c>
       <c r="G298" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$22</f>
       </c>
       <c r="I298" s="21" t="str">
-        <f>data!$B$67</f>
+        <f>data!$B$69</f>
       </c>
       <c r="J298" s="21" t="s">
         <v>242</v>
@@ -12050,7 +12050,7 @@
         <v>242</v>
       </c>
       <c r="O298" s="21" t="str">
-        <f>data!$B$69</f>
+        <f>data!$B$67</f>
       </c>
     </row>
     <row r="299">
@@ -12078,7 +12078,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="23" t="s">
+      <c r="A303" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B303" s="21"/>
@@ -12088,10 +12088,10 @@
       </c>
       <c r="E303" s="21"/>
       <c r="F303" s="21"/>
-      <c r="G303" s="24" t="s">
+      <c r="G303" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I303" s="23" t="s">
+      <c r="I303" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J303" s="21"/>
@@ -12101,13 +12101,13 @@
       </c>
       <c r="M303" s="21"/>
       <c r="N303" s="21"/>
-      <c r="O303" s="24" t="s">
+      <c r="O303" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$24</f>
       </c>
       <c r="B304" s="21"/>
       <c r="C304" s="21"/>
@@ -12115,10 +12115,10 @@
       <c r="E304" s="21"/>
       <c r="F304" s="21"/>
       <c r="G304" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$23</f>
       </c>
       <c r="I304" s="21" t="str">
-        <f>data!$B$68</f>
+        <f>data!$B$69</f>
       </c>
       <c r="J304" s="21"/>
       <c r="K304" s="21"/>
@@ -12126,7 +12126,7 @@
       <c r="M304" s="21"/>
       <c r="N304" s="21"/>
       <c r="O304" s="21" t="str">
-        <f>data!$B$69</f>
+        <f>data!$B$68</f>
       </c>
     </row>
     <row r="305">
@@ -12251,7 +12251,7 @@
     </row>
     <row r="311">
       <c r="A311" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$24</f>
       </c>
       <c r="B311" s="21" t="s">
         <v>242</v>
@@ -12267,10 +12267,10 @@
         <v>242</v>
       </c>
       <c r="G311" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$23</f>
       </c>
       <c r="I311" s="21" t="str">
-        <f>data!$B$68</f>
+        <f>data!$B$69</f>
       </c>
       <c r="J311" s="21" t="s">
         <v>242</v>
@@ -12286,7 +12286,7 @@
         <v>242</v>
       </c>
       <c r="O311" s="21" t="str">
-        <f>data!$B$69</f>
+        <f>data!$B$68</f>
       </c>
     </row>
     <row r="312">
@@ -12364,7 +12364,7 @@
       <c r="O319" s="20"/>
     </row>
     <row r="320">
-      <c r="A320" s="23" t="s">
+      <c r="A320" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B320" s="21"/>
@@ -12374,10 +12374,10 @@
       </c>
       <c r="E320" s="21"/>
       <c r="F320" s="21"/>
-      <c r="G320" s="24" t="s">
+      <c r="G320" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I320" s="23" t="s">
+      <c r="I320" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J320" s="21"/>
@@ -12387,13 +12387,13 @@
       </c>
       <c r="M320" s="21"/>
       <c r="N320" s="21"/>
-      <c r="O320" s="24" t="s">
+      <c r="O320" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$26</f>
       </c>
       <c r="B321" s="21"/>
       <c r="C321" s="21"/>
@@ -12401,10 +12401,10 @@
       <c r="E321" s="21"/>
       <c r="F321" s="21"/>
       <c r="G321" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$25</f>
       </c>
       <c r="I321" s="21" t="str">
-        <f>data!$B$70</f>
+        <f>data!$B$71</f>
       </c>
       <c r="J321" s="21"/>
       <c r="K321" s="21"/>
@@ -12412,7 +12412,7 @@
       <c r="M321" s="21"/>
       <c r="N321" s="21"/>
       <c r="O321" s="21" t="str">
-        <f>data!$B$71</f>
+        <f>data!$B$70</f>
       </c>
     </row>
     <row r="322">
@@ -12537,7 +12537,7 @@
     </row>
     <row r="328">
       <c r="A328" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$26</f>
       </c>
       <c r="B328" s="21" t="s">
         <v>242</v>
@@ -12553,10 +12553,10 @@
         <v>242</v>
       </c>
       <c r="G328" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$25</f>
       </c>
       <c r="I328" s="21" t="str">
-        <f>data!$B$70</f>
+        <f>data!$B$71</f>
       </c>
       <c r="J328" s="21" t="s">
         <v>242</v>
@@ -12572,7 +12572,7 @@
         <v>242</v>
       </c>
       <c r="O328" s="21" t="str">
-        <f>data!$B$71</f>
+        <f>data!$B$70</f>
       </c>
     </row>
     <row r="329">
@@ -12600,7 +12600,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="23" t="s">
+      <c r="A333" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B333" s="21"/>
@@ -12610,10 +12610,10 @@
       </c>
       <c r="E333" s="21"/>
       <c r="F333" s="21"/>
-      <c r="G333" s="24" t="s">
+      <c r="G333" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I333" s="23" t="s">
+      <c r="I333" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J333" s="21"/>
@@ -12623,13 +12623,13 @@
       </c>
       <c r="M333" s="21"/>
       <c r="N333" s="21"/>
-      <c r="O333" s="24" t="s">
+      <c r="O333" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$27</f>
       </c>
       <c r="B334" s="21"/>
       <c r="C334" s="21"/>
@@ -12637,10 +12637,10 @@
       <c r="E334" s="21"/>
       <c r="F334" s="21"/>
       <c r="G334" s="21" t="str">
-        <f>data!$B$27</f>
+        <f>data!$B$25</f>
       </c>
       <c r="I334" s="21" t="str">
-        <f>data!$B$70</f>
+        <f>data!$B$72</f>
       </c>
       <c r="J334" s="21"/>
       <c r="K334" s="21"/>
@@ -12648,7 +12648,7 @@
       <c r="M334" s="21"/>
       <c r="N334" s="21"/>
       <c r="O334" s="21" t="str">
-        <f>data!$B$72</f>
+        <f>data!$B$70</f>
       </c>
     </row>
     <row r="335">
@@ -12773,7 +12773,7 @@
     </row>
     <row r="341">
       <c r="A341" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$27</f>
       </c>
       <c r="B341" s="21" t="s">
         <v>242</v>
@@ -12789,10 +12789,10 @@
         <v>242</v>
       </c>
       <c r="G341" s="21" t="str">
-        <f>data!$B$27</f>
+        <f>data!$B$25</f>
       </c>
       <c r="I341" s="21" t="str">
-        <f>data!$B$70</f>
+        <f>data!$B$72</f>
       </c>
       <c r="J341" s="21" t="s">
         <v>242</v>
@@ -12808,7 +12808,7 @@
         <v>242</v>
       </c>
       <c r="O341" s="21" t="str">
-        <f>data!$B$72</f>
+        <f>data!$B$70</f>
       </c>
     </row>
     <row r="342">
@@ -12836,7 +12836,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="23" t="s">
+      <c r="A346" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B346" s="21"/>
@@ -12846,10 +12846,10 @@
       </c>
       <c r="E346" s="21"/>
       <c r="F346" s="21"/>
-      <c r="G346" s="24" t="s">
+      <c r="G346" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I346" s="23" t="s">
+      <c r="I346" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J346" s="21"/>
@@ -12859,13 +12859,13 @@
       </c>
       <c r="M346" s="21"/>
       <c r="N346" s="21"/>
-      <c r="O346" s="24" t="s">
+      <c r="O346" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$27</f>
       </c>
       <c r="B347" s="21"/>
       <c r="C347" s="21"/>
@@ -12873,10 +12873,10 @@
       <c r="E347" s="21"/>
       <c r="F347" s="21"/>
       <c r="G347" s="21" t="str">
-        <f>data!$B$27</f>
+        <f>data!$B$26</f>
       </c>
       <c r="I347" s="21" t="str">
-        <f>data!$B$71</f>
+        <f>data!$B$72</f>
       </c>
       <c r="J347" s="21"/>
       <c r="K347" s="21"/>
@@ -12884,7 +12884,7 @@
       <c r="M347" s="21"/>
       <c r="N347" s="21"/>
       <c r="O347" s="21" t="str">
-        <f>data!$B$72</f>
+        <f>data!$B$71</f>
       </c>
     </row>
     <row r="348">
@@ -13009,7 +13009,7 @@
     </row>
     <row r="354">
       <c r="A354" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$27</f>
       </c>
       <c r="B354" s="21" t="s">
         <v>242</v>
@@ -13025,10 +13025,10 @@
         <v>242</v>
       </c>
       <c r="G354" s="21" t="str">
-        <f>data!$B$27</f>
+        <f>data!$B$26</f>
       </c>
       <c r="I354" s="21" t="str">
-        <f>data!$B$71</f>
+        <f>data!$B$72</f>
       </c>
       <c r="J354" s="21" t="s">
         <v>242</v>
@@ -13044,7 +13044,7 @@
         <v>242</v>
       </c>
       <c r="O354" s="21" t="str">
-        <f>data!$B$72</f>
+        <f>data!$B$71</f>
       </c>
     </row>
     <row r="355">
@@ -13122,7 +13122,7 @@
       <c r="O362" s="20"/>
     </row>
     <row r="363">
-      <c r="A363" s="23" t="s">
+      <c r="A363" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B363" s="21"/>
@@ -13132,10 +13132,10 @@
       </c>
       <c r="E363" s="21"/>
       <c r="F363" s="21"/>
-      <c r="G363" s="24" t="s">
+      <c r="G363" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I363" s="23" t="s">
+      <c r="I363" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J363" s="21"/>
@@ -13145,13 +13145,13 @@
       </c>
       <c r="M363" s="21"/>
       <c r="N363" s="21"/>
-      <c r="O363" s="24" t="s">
+      <c r="O363" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="21" t="str">
-        <f>data!$B$28</f>
+        <f>data!$B$29</f>
       </c>
       <c r="B364" s="21"/>
       <c r="C364" s="21"/>
@@ -13159,10 +13159,10 @@
       <c r="E364" s="21"/>
       <c r="F364" s="21"/>
       <c r="G364" s="21" t="str">
-        <f>data!$B$29</f>
+        <f>data!$B$28</f>
       </c>
       <c r="I364" s="21" t="str">
-        <f>data!$B$73</f>
+        <f>data!$B$74</f>
       </c>
       <c r="J364" s="21"/>
       <c r="K364" s="21"/>
@@ -13170,7 +13170,7 @@
       <c r="M364" s="21"/>
       <c r="N364" s="21"/>
       <c r="O364" s="21" t="str">
-        <f>data!$B$74</f>
+        <f>data!$B$73</f>
       </c>
     </row>
     <row r="365">
@@ -13295,7 +13295,7 @@
     </row>
     <row r="371">
       <c r="A371" s="21" t="str">
-        <f>data!$B$28</f>
+        <f>data!$B$29</f>
       </c>
       <c r="B371" s="21" t="s">
         <v>242</v>
@@ -13311,10 +13311,10 @@
         <v>242</v>
       </c>
       <c r="G371" s="21" t="str">
-        <f>data!$B$29</f>
+        <f>data!$B$28</f>
       </c>
       <c r="I371" s="21" t="str">
-        <f>data!$B$73</f>
+        <f>data!$B$74</f>
       </c>
       <c r="J371" s="21" t="s">
         <v>242</v>
@@ -13330,7 +13330,7 @@
         <v>242</v>
       </c>
       <c r="O371" s="21" t="str">
-        <f>data!$B$74</f>
+        <f>data!$B$73</f>
       </c>
     </row>
     <row r="372">
@@ -13358,7 +13358,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="23" t="s">
+      <c r="A376" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B376" s="21"/>
@@ -13368,10 +13368,10 @@
       </c>
       <c r="E376" s="21"/>
       <c r="F376" s="21"/>
-      <c r="G376" s="24" t="s">
+      <c r="G376" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I376" s="23" t="s">
+      <c r="I376" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J376" s="21"/>
@@ -13381,13 +13381,13 @@
       </c>
       <c r="M376" s="21"/>
       <c r="N376" s="21"/>
-      <c r="O376" s="24" t="s">
+      <c r="O376" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="21" t="str">
-        <f>data!$B$28</f>
+        <f>data!$B$30</f>
       </c>
       <c r="B377" s="21"/>
       <c r="C377" s="21"/>
@@ -13395,10 +13395,10 @@
       <c r="E377" s="21"/>
       <c r="F377" s="21"/>
       <c r="G377" s="21" t="str">
-        <f>data!$B$30</f>
+        <f>data!$B$28</f>
       </c>
       <c r="I377" s="21" t="str">
-        <f>data!$B$73</f>
+        <f>data!$B$75</f>
       </c>
       <c r="J377" s="21"/>
       <c r="K377" s="21"/>
@@ -13406,7 +13406,7 @@
       <c r="M377" s="21"/>
       <c r="N377" s="21"/>
       <c r="O377" s="21" t="str">
-        <f>data!$B$75</f>
+        <f>data!$B$73</f>
       </c>
     </row>
     <row r="378">
@@ -13531,7 +13531,7 @@
     </row>
     <row r="384">
       <c r="A384" s="21" t="str">
-        <f>data!$B$28</f>
+        <f>data!$B$30</f>
       </c>
       <c r="B384" s="21" t="s">
         <v>242</v>
@@ -13547,10 +13547,10 @@
         <v>242</v>
       </c>
       <c r="G384" s="21" t="str">
-        <f>data!$B$30</f>
+        <f>data!$B$28</f>
       </c>
       <c r="I384" s="21" t="str">
-        <f>data!$B$73</f>
+        <f>data!$B$75</f>
       </c>
       <c r="J384" s="21" t="s">
         <v>242</v>
@@ -13566,7 +13566,7 @@
         <v>242</v>
       </c>
       <c r="O384" s="21" t="str">
-        <f>data!$B$75</f>
+        <f>data!$B$73</f>
       </c>
     </row>
     <row r="385">
@@ -13594,7 +13594,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="23" t="s">
+      <c r="A389" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B389" s="21"/>
@@ -13604,10 +13604,10 @@
       </c>
       <c r="E389" s="21"/>
       <c r="F389" s="21"/>
-      <c r="G389" s="24" t="s">
+      <c r="G389" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I389" s="23" t="s">
+      <c r="I389" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J389" s="21"/>
@@ -13617,13 +13617,13 @@
       </c>
       <c r="M389" s="21"/>
       <c r="N389" s="21"/>
-      <c r="O389" s="24" t="s">
+      <c r="O389" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="21" t="str">
-        <f>data!$B$29</f>
+        <f>data!$B$30</f>
       </c>
       <c r="B390" s="21"/>
       <c r="C390" s="21"/>
@@ -13631,10 +13631,10 @@
       <c r="E390" s="21"/>
       <c r="F390" s="21"/>
       <c r="G390" s="21" t="str">
-        <f>data!$B$30</f>
+        <f>data!$B$29</f>
       </c>
       <c r="I390" s="21" t="str">
-        <f>data!$B$74</f>
+        <f>data!$B$75</f>
       </c>
       <c r="J390" s="21"/>
       <c r="K390" s="21"/>
@@ -13642,7 +13642,7 @@
       <c r="M390" s="21"/>
       <c r="N390" s="21"/>
       <c r="O390" s="21" t="str">
-        <f>data!$B$75</f>
+        <f>data!$B$74</f>
       </c>
     </row>
     <row r="391">
@@ -13767,7 +13767,7 @@
     </row>
     <row r="397">
       <c r="A397" s="21" t="str">
-        <f>data!$B$29</f>
+        <f>data!$B$30</f>
       </c>
       <c r="B397" s="21" t="s">
         <v>242</v>
@@ -13783,10 +13783,10 @@
         <v>242</v>
       </c>
       <c r="G397" s="21" t="str">
-        <f>data!$B$30</f>
+        <f>data!$B$29</f>
       </c>
       <c r="I397" s="21" t="str">
-        <f>data!$B$74</f>
+        <f>data!$B$75</f>
       </c>
       <c r="J397" s="21" t="s">
         <v>242</v>
@@ -13802,7 +13802,7 @@
         <v>242</v>
       </c>
       <c r="O397" s="21" t="str">
-        <f>data!$B$75</f>
+        <f>data!$B$74</f>
       </c>
     </row>
     <row r="398">
@@ -13880,7 +13880,7 @@
       <c r="O405" s="20"/>
     </row>
     <row r="406">
-      <c r="A406" s="23" t="s">
+      <c r="A406" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B406" s="21"/>
@@ -13890,10 +13890,10 @@
       </c>
       <c r="E406" s="21"/>
       <c r="F406" s="21"/>
-      <c r="G406" s="24" t="s">
+      <c r="G406" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I406" s="23" t="s">
+      <c r="I406" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J406" s="21"/>
@@ -13903,13 +13903,13 @@
       </c>
       <c r="M406" s="21"/>
       <c r="N406" s="21"/>
-      <c r="O406" s="24" t="s">
+      <c r="O406" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="21" t="str">
-        <f>data!$B$31</f>
+        <f>data!$B$32</f>
       </c>
       <c r="B407" s="21"/>
       <c r="C407" s="21"/>
@@ -13917,10 +13917,10 @@
       <c r="E407" s="21"/>
       <c r="F407" s="21"/>
       <c r="G407" s="21" t="str">
-        <f>data!$B$32</f>
+        <f>data!$B$31</f>
       </c>
       <c r="I407" s="21" t="str">
-        <f>data!$B$76</f>
+        <f>data!$B$77</f>
       </c>
       <c r="J407" s="21"/>
       <c r="K407" s="21"/>
@@ -13928,7 +13928,7 @@
       <c r="M407" s="21"/>
       <c r="N407" s="21"/>
       <c r="O407" s="21" t="str">
-        <f>data!$B$77</f>
+        <f>data!$B$76</f>
       </c>
     </row>
     <row r="408">
@@ -14053,7 +14053,7 @@
     </row>
     <row r="414">
       <c r="A414" s="21" t="str">
-        <f>data!$B$31</f>
+        <f>data!$B$32</f>
       </c>
       <c r="B414" s="21" t="s">
         <v>242</v>
@@ -14069,10 +14069,10 @@
         <v>242</v>
       </c>
       <c r="G414" s="21" t="str">
-        <f>data!$B$32</f>
+        <f>data!$B$31</f>
       </c>
       <c r="I414" s="21" t="str">
-        <f>data!$B$76</f>
+        <f>data!$B$77</f>
       </c>
       <c r="J414" s="21" t="s">
         <v>242</v>
@@ -14088,7 +14088,7 @@
         <v>242</v>
       </c>
       <c r="O414" s="21" t="str">
-        <f>data!$B$77</f>
+        <f>data!$B$76</f>
       </c>
     </row>
     <row r="415">
@@ -14116,7 +14116,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="23" t="s">
+      <c r="A419" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B419" s="21"/>
@@ -14126,10 +14126,10 @@
       </c>
       <c r="E419" s="21"/>
       <c r="F419" s="21"/>
-      <c r="G419" s="24" t="s">
+      <c r="G419" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I419" s="23" t="s">
+      <c r="I419" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J419" s="21"/>
@@ -14139,13 +14139,13 @@
       </c>
       <c r="M419" s="21"/>
       <c r="N419" s="21"/>
-      <c r="O419" s="24" t="s">
+      <c r="O419" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="21" t="str">
-        <f>data!$B$31</f>
+        <f>data!$B$33</f>
       </c>
       <c r="B420" s="21"/>
       <c r="C420" s="21"/>
@@ -14153,10 +14153,10 @@
       <c r="E420" s="21"/>
       <c r="F420" s="21"/>
       <c r="G420" s="21" t="str">
-        <f>data!$B$33</f>
+        <f>data!$B$31</f>
       </c>
       <c r="I420" s="21" t="str">
-        <f>data!$B$76</f>
+        <f>data!$B$78</f>
       </c>
       <c r="J420" s="21"/>
       <c r="K420" s="21"/>
@@ -14164,7 +14164,7 @@
       <c r="M420" s="21"/>
       <c r="N420" s="21"/>
       <c r="O420" s="21" t="str">
-        <f>data!$B$78</f>
+        <f>data!$B$76</f>
       </c>
     </row>
     <row r="421">
@@ -14289,7 +14289,7 @@
     </row>
     <row r="427">
       <c r="A427" s="21" t="str">
-        <f>data!$B$31</f>
+        <f>data!$B$33</f>
       </c>
       <c r="B427" s="21" t="s">
         <v>242</v>
@@ -14305,10 +14305,10 @@
         <v>242</v>
       </c>
       <c r="G427" s="21" t="str">
-        <f>data!$B$33</f>
+        <f>data!$B$31</f>
       </c>
       <c r="I427" s="21" t="str">
-        <f>data!$B$76</f>
+        <f>data!$B$78</f>
       </c>
       <c r="J427" s="21" t="s">
         <v>242</v>
@@ -14324,7 +14324,7 @@
         <v>242</v>
       </c>
       <c r="O427" s="21" t="str">
-        <f>data!$B$78</f>
+        <f>data!$B$76</f>
       </c>
     </row>
     <row r="428">
@@ -14352,7 +14352,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="23" t="s">
+      <c r="A432" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B432" s="21"/>
@@ -14362,10 +14362,10 @@
       </c>
       <c r="E432" s="21"/>
       <c r="F432" s="21"/>
-      <c r="G432" s="24" t="s">
+      <c r="G432" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I432" s="23" t="s">
+      <c r="I432" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J432" s="21"/>
@@ -14375,13 +14375,13 @@
       </c>
       <c r="M432" s="21"/>
       <c r="N432" s="21"/>
-      <c r="O432" s="24" t="s">
+      <c r="O432" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="21" t="str">
-        <f>data!$B$32</f>
+        <f>data!$B$33</f>
       </c>
       <c r="B433" s="21"/>
       <c r="C433" s="21"/>
@@ -14389,10 +14389,10 @@
       <c r="E433" s="21"/>
       <c r="F433" s="21"/>
       <c r="G433" s="21" t="str">
-        <f>data!$B$33</f>
+        <f>data!$B$32</f>
       </c>
       <c r="I433" s="21" t="str">
-        <f>data!$B$77</f>
+        <f>data!$B$78</f>
       </c>
       <c r="J433" s="21"/>
       <c r="K433" s="21"/>
@@ -14400,7 +14400,7 @@
       <c r="M433" s="21"/>
       <c r="N433" s="21"/>
       <c r="O433" s="21" t="str">
-        <f>data!$B$78</f>
+        <f>data!$B$77</f>
       </c>
     </row>
     <row r="434">
@@ -14525,7 +14525,7 @@
     </row>
     <row r="440">
       <c r="A440" s="21" t="str">
-        <f>data!$B$32</f>
+        <f>data!$B$33</f>
       </c>
       <c r="B440" s="21" t="s">
         <v>242</v>
@@ -14541,10 +14541,10 @@
         <v>242</v>
       </c>
       <c r="G440" s="21" t="str">
-        <f>data!$B$33</f>
+        <f>data!$B$32</f>
       </c>
       <c r="I440" s="21" t="str">
-        <f>data!$B$77</f>
+        <f>data!$B$78</f>
       </c>
       <c r="J440" s="21" t="s">
         <v>242</v>
@@ -14560,7 +14560,7 @@
         <v>242</v>
       </c>
       <c r="O440" s="21" t="str">
-        <f>data!$B$78</f>
+        <f>data!$B$77</f>
       </c>
     </row>
     <row r="441">
@@ -14638,7 +14638,7 @@
       <c r="O448" s="20"/>
     </row>
     <row r="449">
-      <c r="A449" s="23" t="s">
+      <c r="A449" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B449" s="21"/>
@@ -14648,10 +14648,10 @@
       </c>
       <c r="E449" s="21"/>
       <c r="F449" s="21"/>
-      <c r="G449" s="24" t="s">
+      <c r="G449" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I449" s="23" t="s">
+      <c r="I449" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J449" s="21"/>
@@ -14661,13 +14661,13 @@
       </c>
       <c r="M449" s="21"/>
       <c r="N449" s="21"/>
-      <c r="O449" s="24" t="s">
+      <c r="O449" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="21" t="str">
-        <f>data!$B$34</f>
+        <f>data!$B$35</f>
       </c>
       <c r="B450" s="21"/>
       <c r="C450" s="21"/>
@@ -14675,10 +14675,10 @@
       <c r="E450" s="21"/>
       <c r="F450" s="21"/>
       <c r="G450" s="21" t="str">
-        <f>data!$B$35</f>
+        <f>data!$B$34</f>
       </c>
       <c r="I450" s="21" t="str">
-        <f>data!$B$79</f>
+        <f>data!$B$80</f>
       </c>
       <c r="J450" s="21"/>
       <c r="K450" s="21"/>
@@ -14686,7 +14686,7 @@
       <c r="M450" s="21"/>
       <c r="N450" s="21"/>
       <c r="O450" s="21" t="str">
-        <f>data!$B$80</f>
+        <f>data!$B$79</f>
       </c>
     </row>
     <row r="451">
@@ -14811,7 +14811,7 @@
     </row>
     <row r="457">
       <c r="A457" s="21" t="str">
-        <f>data!$B$34</f>
+        <f>data!$B$35</f>
       </c>
       <c r="B457" s="21" t="s">
         <v>242</v>
@@ -14827,10 +14827,10 @@
         <v>242</v>
       </c>
       <c r="G457" s="21" t="str">
-        <f>data!$B$35</f>
+        <f>data!$B$34</f>
       </c>
       <c r="I457" s="21" t="str">
-        <f>data!$B$79</f>
+        <f>data!$B$80</f>
       </c>
       <c r="J457" s="21" t="s">
         <v>242</v>
@@ -14846,7 +14846,7 @@
         <v>242</v>
       </c>
       <c r="O457" s="21" t="str">
-        <f>data!$B$80</f>
+        <f>data!$B$79</f>
       </c>
     </row>
     <row r="458">
@@ -14874,7 +14874,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="23" t="s">
+      <c r="A462" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B462" s="21"/>
@@ -14884,10 +14884,10 @@
       </c>
       <c r="E462" s="21"/>
       <c r="F462" s="21"/>
-      <c r="G462" s="24" t="s">
+      <c r="G462" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I462" s="23" t="s">
+      <c r="I462" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J462" s="21"/>
@@ -14897,13 +14897,13 @@
       </c>
       <c r="M462" s="21"/>
       <c r="N462" s="21"/>
-      <c r="O462" s="24" t="s">
+      <c r="O462" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="21" t="str">
-        <f>data!$B$34</f>
+        <f>data!$B$36</f>
       </c>
       <c r="B463" s="21"/>
       <c r="C463" s="21"/>
@@ -14911,10 +14911,10 @@
       <c r="E463" s="21"/>
       <c r="F463" s="21"/>
       <c r="G463" s="21" t="str">
-        <f>data!$B$36</f>
+        <f>data!$B$34</f>
       </c>
       <c r="I463" s="21" t="str">
-        <f>data!$B$79</f>
+        <f>data!$B$81</f>
       </c>
       <c r="J463" s="21"/>
       <c r="K463" s="21"/>
@@ -14922,7 +14922,7 @@
       <c r="M463" s="21"/>
       <c r="N463" s="21"/>
       <c r="O463" s="21" t="str">
-        <f>data!$B$81</f>
+        <f>data!$B$79</f>
       </c>
     </row>
     <row r="464">
@@ -15047,7 +15047,7 @@
     </row>
     <row r="470">
       <c r="A470" s="21" t="str">
-        <f>data!$B$34</f>
+        <f>data!$B$36</f>
       </c>
       <c r="B470" s="21" t="s">
         <v>242</v>
@@ -15063,10 +15063,10 @@
         <v>242</v>
       </c>
       <c r="G470" s="21" t="str">
-        <f>data!$B$36</f>
+        <f>data!$B$34</f>
       </c>
       <c r="I470" s="21" t="str">
-        <f>data!$B$79</f>
+        <f>data!$B$81</f>
       </c>
       <c r="J470" s="21" t="s">
         <v>242</v>
@@ -15082,7 +15082,7 @@
         <v>242</v>
       </c>
       <c r="O470" s="21" t="str">
-        <f>data!$B$81</f>
+        <f>data!$B$79</f>
       </c>
     </row>
     <row r="471">
@@ -15110,7 +15110,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="23" t="s">
+      <c r="A475" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B475" s="21"/>
@@ -15120,10 +15120,10 @@
       </c>
       <c r="E475" s="21"/>
       <c r="F475" s="21"/>
-      <c r="G475" s="24" t="s">
+      <c r="G475" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I475" s="23" t="s">
+      <c r="I475" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J475" s="21"/>
@@ -15133,13 +15133,13 @@
       </c>
       <c r="M475" s="21"/>
       <c r="N475" s="21"/>
-      <c r="O475" s="24" t="s">
+      <c r="O475" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="21" t="str">
-        <f>data!$B$35</f>
+        <f>data!$B$36</f>
       </c>
       <c r="B476" s="21"/>
       <c r="C476" s="21"/>
@@ -15147,10 +15147,10 @@
       <c r="E476" s="21"/>
       <c r="F476" s="21"/>
       <c r="G476" s="21" t="str">
-        <f>data!$B$36</f>
+        <f>data!$B$35</f>
       </c>
       <c r="I476" s="21" t="str">
-        <f>data!$B$80</f>
+        <f>data!$B$81</f>
       </c>
       <c r="J476" s="21"/>
       <c r="K476" s="21"/>
@@ -15158,7 +15158,7 @@
       <c r="M476" s="21"/>
       <c r="N476" s="21"/>
       <c r="O476" s="21" t="str">
-        <f>data!$B$81</f>
+        <f>data!$B$80</f>
       </c>
     </row>
     <row r="477">
@@ -15283,7 +15283,7 @@
     </row>
     <row r="483">
       <c r="A483" s="21" t="str">
-        <f>data!$B$35</f>
+        <f>data!$B$36</f>
       </c>
       <c r="B483" s="21" t="s">
         <v>242</v>
@@ -15299,10 +15299,10 @@
         <v>242</v>
       </c>
       <c r="G483" s="21" t="str">
-        <f>data!$B$36</f>
+        <f>data!$B$35</f>
       </c>
       <c r="I483" s="21" t="str">
-        <f>data!$B$80</f>
+        <f>data!$B$81</f>
       </c>
       <c r="J483" s="21" t="s">
         <v>242</v>
@@ -15318,7 +15318,7 @@
         <v>242</v>
       </c>
       <c r="O483" s="21" t="str">
-        <f>data!$B$81</f>
+        <f>data!$B$80</f>
       </c>
     </row>
     <row r="484">
@@ -15396,7 +15396,7 @@
       <c r="O491" s="20"/>
     </row>
     <row r="492">
-      <c r="A492" s="23" t="s">
+      <c r="A492" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B492" s="21"/>
@@ -15406,10 +15406,10 @@
       </c>
       <c r="E492" s="21"/>
       <c r="F492" s="21"/>
-      <c r="G492" s="24" t="s">
+      <c r="G492" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I492" s="23" t="s">
+      <c r="I492" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J492" s="21"/>
@@ -15419,13 +15419,13 @@
       </c>
       <c r="M492" s="21"/>
       <c r="N492" s="21"/>
-      <c r="O492" s="24" t="s">
+      <c r="O492" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="21" t="str">
-        <f>data!$B$37</f>
+        <f>data!$B$38</f>
       </c>
       <c r="B493" s="21"/>
       <c r="C493" s="21"/>
@@ -15433,10 +15433,10 @@
       <c r="E493" s="21"/>
       <c r="F493" s="21"/>
       <c r="G493" s="21" t="str">
-        <f>data!$B$38</f>
+        <f>data!$B$37</f>
       </c>
       <c r="I493" s="21" t="str">
-        <f>data!$B$82</f>
+        <f>data!$B$83</f>
       </c>
       <c r="J493" s="21"/>
       <c r="K493" s="21"/>
@@ -15444,7 +15444,7 @@
       <c r="M493" s="21"/>
       <c r="N493" s="21"/>
       <c r="O493" s="21" t="str">
-        <f>data!$B$83</f>
+        <f>data!$B$82</f>
       </c>
     </row>
     <row r="494">
@@ -15569,7 +15569,7 @@
     </row>
     <row r="500">
       <c r="A500" s="21" t="str">
-        <f>data!$B$37</f>
+        <f>data!$B$38</f>
       </c>
       <c r="B500" s="21" t="s">
         <v>242</v>
@@ -15585,10 +15585,10 @@
         <v>242</v>
       </c>
       <c r="G500" s="21" t="str">
-        <f>data!$B$38</f>
+        <f>data!$B$37</f>
       </c>
       <c r="I500" s="21" t="str">
-        <f>data!$B$82</f>
+        <f>data!$B$83</f>
       </c>
       <c r="J500" s="21" t="s">
         <v>242</v>
@@ -15604,7 +15604,7 @@
         <v>242</v>
       </c>
       <c r="O500" s="21" t="str">
-        <f>data!$B$83</f>
+        <f>data!$B$82</f>
       </c>
     </row>
     <row r="501">
@@ -15632,7 +15632,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="23" t="s">
+      <c r="A505" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B505" s="21"/>
@@ -15642,10 +15642,10 @@
       </c>
       <c r="E505" s="21"/>
       <c r="F505" s="21"/>
-      <c r="G505" s="24" t="s">
+      <c r="G505" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I505" s="23" t="s">
+      <c r="I505" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J505" s="21"/>
@@ -15655,13 +15655,13 @@
       </c>
       <c r="M505" s="21"/>
       <c r="N505" s="21"/>
-      <c r="O505" s="24" t="s">
+      <c r="O505" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="21" t="str">
-        <f>data!$B$37</f>
+        <f>data!$B$39</f>
       </c>
       <c r="B506" s="21"/>
       <c r="C506" s="21"/>
@@ -15669,10 +15669,10 @@
       <c r="E506" s="21"/>
       <c r="F506" s="21"/>
       <c r="G506" s="21" t="str">
-        <f>data!$B$39</f>
+        <f>data!$B$37</f>
       </c>
       <c r="I506" s="21" t="str">
-        <f>data!$B$82</f>
+        <f>data!$B$84</f>
       </c>
       <c r="J506" s="21"/>
       <c r="K506" s="21"/>
@@ -15680,7 +15680,7 @@
       <c r="M506" s="21"/>
       <c r="N506" s="21"/>
       <c r="O506" s="21" t="str">
-        <f>data!$B$84</f>
+        <f>data!$B$82</f>
       </c>
     </row>
     <row r="507">
@@ -15805,7 +15805,7 @@
     </row>
     <row r="513">
       <c r="A513" s="21" t="str">
-        <f>data!$B$37</f>
+        <f>data!$B$39</f>
       </c>
       <c r="B513" s="21" t="s">
         <v>242</v>
@@ -15821,10 +15821,10 @@
         <v>242</v>
       </c>
       <c r="G513" s="21" t="str">
-        <f>data!$B$39</f>
+        <f>data!$B$37</f>
       </c>
       <c r="I513" s="21" t="str">
-        <f>data!$B$82</f>
+        <f>data!$B$84</f>
       </c>
       <c r="J513" s="21" t="s">
         <v>242</v>
@@ -15840,7 +15840,7 @@
         <v>242</v>
       </c>
       <c r="O513" s="21" t="str">
-        <f>data!$B$84</f>
+        <f>data!$B$82</f>
       </c>
     </row>
     <row r="514">
@@ -15868,7 +15868,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="23" t="s">
+      <c r="A518" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B518" s="21"/>
@@ -15878,10 +15878,10 @@
       </c>
       <c r="E518" s="21"/>
       <c r="F518" s="21"/>
-      <c r="G518" s="24" t="s">
+      <c r="G518" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I518" s="23" t="s">
+      <c r="I518" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J518" s="21"/>
@@ -15891,13 +15891,13 @@
       </c>
       <c r="M518" s="21"/>
       <c r="N518" s="21"/>
-      <c r="O518" s="24" t="s">
+      <c r="O518" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="21" t="str">
-        <f>data!$B$38</f>
+        <f>data!$B$39</f>
       </c>
       <c r="B519" s="21"/>
       <c r="C519" s="21"/>
@@ -15905,10 +15905,10 @@
       <c r="E519" s="21"/>
       <c r="F519" s="21"/>
       <c r="G519" s="21" t="str">
-        <f>data!$B$39</f>
+        <f>data!$B$38</f>
       </c>
       <c r="I519" s="21" t="str">
-        <f>data!$B$83</f>
+        <f>data!$B$84</f>
       </c>
       <c r="J519" s="21"/>
       <c r="K519" s="21"/>
@@ -15916,7 +15916,7 @@
       <c r="M519" s="21"/>
       <c r="N519" s="21"/>
       <c r="O519" s="21" t="str">
-        <f>data!$B$84</f>
+        <f>data!$B$83</f>
       </c>
     </row>
     <row r="520">
@@ -16041,7 +16041,7 @@
     </row>
     <row r="526">
       <c r="A526" s="21" t="str">
-        <f>data!$B$38</f>
+        <f>data!$B$39</f>
       </c>
       <c r="B526" s="21" t="s">
         <v>242</v>
@@ -16057,10 +16057,10 @@
         <v>242</v>
       </c>
       <c r="G526" s="21" t="str">
-        <f>data!$B$39</f>
+        <f>data!$B$38</f>
       </c>
       <c r="I526" s="21" t="str">
-        <f>data!$B$83</f>
+        <f>data!$B$84</f>
       </c>
       <c r="J526" s="21" t="s">
         <v>242</v>
@@ -16076,7 +16076,7 @@
         <v>242</v>
       </c>
       <c r="O526" s="21" t="str">
-        <f>data!$B$84</f>
+        <f>data!$B$83</f>
       </c>
     </row>
     <row r="527">
@@ -16154,7 +16154,7 @@
       <c r="O534" s="20"/>
     </row>
     <row r="535">
-      <c r="A535" s="23" t="s">
+      <c r="A535" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B535" s="21"/>
@@ -16164,10 +16164,10 @@
       </c>
       <c r="E535" s="21"/>
       <c r="F535" s="21"/>
-      <c r="G535" s="24" t="s">
+      <c r="G535" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I535" s="23" t="s">
+      <c r="I535" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J535" s="21"/>
@@ -16177,13 +16177,13 @@
       </c>
       <c r="M535" s="21"/>
       <c r="N535" s="21"/>
-      <c r="O535" s="24" t="s">
+      <c r="O535" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="21" t="str">
-        <f>data!$B$40</f>
+        <f>data!$B$41</f>
       </c>
       <c r="B536" s="21"/>
       <c r="C536" s="21"/>
@@ -16191,10 +16191,10 @@
       <c r="E536" s="21"/>
       <c r="F536" s="21"/>
       <c r="G536" s="21" t="str">
-        <f>data!$B$41</f>
+        <f>data!$B$40</f>
       </c>
       <c r="I536" s="21" t="str">
-        <f>data!$B$85</f>
+        <f>data!$B$86</f>
       </c>
       <c r="J536" s="21"/>
       <c r="K536" s="21"/>
@@ -16202,7 +16202,7 @@
       <c r="M536" s="21"/>
       <c r="N536" s="21"/>
       <c r="O536" s="21" t="str">
-        <f>data!$B$86</f>
+        <f>data!$B$85</f>
       </c>
     </row>
     <row r="537">
@@ -16327,7 +16327,7 @@
     </row>
     <row r="543">
       <c r="A543" s="21" t="str">
-        <f>data!$B$40</f>
+        <f>data!$B$41</f>
       </c>
       <c r="B543" s="21" t="s">
         <v>242</v>
@@ -16343,10 +16343,10 @@
         <v>242</v>
       </c>
       <c r="G543" s="21" t="str">
-        <f>data!$B$41</f>
+        <f>data!$B$40</f>
       </c>
       <c r="I543" s="21" t="str">
-        <f>data!$B$85</f>
+        <f>data!$B$86</f>
       </c>
       <c r="J543" s="21" t="s">
         <v>242</v>
@@ -16362,7 +16362,7 @@
         <v>242</v>
       </c>
       <c r="O543" s="21" t="str">
-        <f>data!$B$86</f>
+        <f>data!$B$85</f>
       </c>
     </row>
     <row r="544">
@@ -16390,7 +16390,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="23" t="s">
+      <c r="A548" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B548" s="21"/>
@@ -16400,10 +16400,10 @@
       </c>
       <c r="E548" s="21"/>
       <c r="F548" s="21"/>
-      <c r="G548" s="24" t="s">
+      <c r="G548" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I548" s="23" t="s">
+      <c r="I548" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J548" s="21"/>
@@ -16413,13 +16413,13 @@
       </c>
       <c r="M548" s="21"/>
       <c r="N548" s="21"/>
-      <c r="O548" s="24" t="s">
+      <c r="O548" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="21" t="str">
-        <f>data!$B$40</f>
+        <f>data!$B$42</f>
       </c>
       <c r="B549" s="21"/>
       <c r="C549" s="21"/>
@@ -16427,10 +16427,10 @@
       <c r="E549" s="21"/>
       <c r="F549" s="21"/>
       <c r="G549" s="21" t="str">
-        <f>data!$B$42</f>
+        <f>data!$B$40</f>
       </c>
       <c r="I549" s="21" t="str">
-        <f>data!$B$85</f>
+        <f>data!$B$87</f>
       </c>
       <c r="J549" s="21"/>
       <c r="K549" s="21"/>
@@ -16438,7 +16438,7 @@
       <c r="M549" s="21"/>
       <c r="N549" s="21"/>
       <c r="O549" s="21" t="str">
-        <f>data!$B$87</f>
+        <f>data!$B$85</f>
       </c>
     </row>
     <row r="550">
@@ -16563,7 +16563,7 @@
     </row>
     <row r="556">
       <c r="A556" s="21" t="str">
-        <f>data!$B$40</f>
+        <f>data!$B$42</f>
       </c>
       <c r="B556" s="21" t="s">
         <v>242</v>
@@ -16579,10 +16579,10 @@
         <v>242</v>
       </c>
       <c r="G556" s="21" t="str">
-        <f>data!$B$42</f>
+        <f>data!$B$40</f>
       </c>
       <c r="I556" s="21" t="str">
-        <f>data!$B$85</f>
+        <f>data!$B$87</f>
       </c>
       <c r="J556" s="21" t="s">
         <v>242</v>
@@ -16598,7 +16598,7 @@
         <v>242</v>
       </c>
       <c r="O556" s="21" t="str">
-        <f>data!$B$87</f>
+        <f>data!$B$85</f>
       </c>
     </row>
     <row r="557">
@@ -16626,7 +16626,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="23" t="s">
+      <c r="A561" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B561" s="21"/>
@@ -16636,10 +16636,10 @@
       </c>
       <c r="E561" s="21"/>
       <c r="F561" s="21"/>
-      <c r="G561" s="24" t="s">
+      <c r="G561" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I561" s="23" t="s">
+      <c r="I561" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J561" s="21"/>
@@ -16649,13 +16649,13 @@
       </c>
       <c r="M561" s="21"/>
       <c r="N561" s="21"/>
-      <c r="O561" s="24" t="s">
+      <c r="O561" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="21" t="str">
-        <f>data!$B$41</f>
+        <f>data!$B$42</f>
       </c>
       <c r="B562" s="21"/>
       <c r="C562" s="21"/>
@@ -16663,10 +16663,10 @@
       <c r="E562" s="21"/>
       <c r="F562" s="21"/>
       <c r="G562" s="21" t="str">
-        <f>data!$B$42</f>
+        <f>data!$B$41</f>
       </c>
       <c r="I562" s="21" t="str">
-        <f>data!$B$86</f>
+        <f>data!$B$87</f>
       </c>
       <c r="J562" s="21"/>
       <c r="K562" s="21"/>
@@ -16674,7 +16674,7 @@
       <c r="M562" s="21"/>
       <c r="N562" s="21"/>
       <c r="O562" s="21" t="str">
-        <f>data!$B$87</f>
+        <f>data!$B$86</f>
       </c>
     </row>
     <row r="563">
@@ -16799,7 +16799,7 @@
     </row>
     <row r="569">
       <c r="A569" s="21" t="str">
-        <f>data!$B$41</f>
+        <f>data!$B$42</f>
       </c>
       <c r="B569" s="21" t="s">
         <v>242</v>
@@ -16815,10 +16815,10 @@
         <v>242</v>
       </c>
       <c r="G569" s="21" t="str">
-        <f>data!$B$42</f>
+        <f>data!$B$41</f>
       </c>
       <c r="I569" s="21" t="str">
-        <f>data!$B$86</f>
+        <f>data!$B$87</f>
       </c>
       <c r="J569" s="21" t="s">
         <v>242</v>
@@ -16834,7 +16834,7 @@
         <v>242</v>
       </c>
       <c r="O569" s="21" t="str">
-        <f>data!$B$87</f>
+        <f>data!$B$86</f>
       </c>
     </row>
     <row r="570">
@@ -16912,7 +16912,7 @@
       <c r="O577" s="20"/>
     </row>
     <row r="578">
-      <c r="A578" s="23" t="s">
+      <c r="A578" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B578" s="21"/>
@@ -16922,10 +16922,10 @@
       </c>
       <c r="E578" s="21"/>
       <c r="F578" s="21"/>
-      <c r="G578" s="24" t="s">
+      <c r="G578" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I578" s="23" t="s">
+      <c r="I578" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J578" s="21"/>
@@ -16935,13 +16935,13 @@
       </c>
       <c r="M578" s="21"/>
       <c r="N578" s="21"/>
-      <c r="O578" s="24" t="s">
+      <c r="O578" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="21" t="str">
-        <f>data!$B$43</f>
+        <f>data!$B$44</f>
       </c>
       <c r="B579" s="21"/>
       <c r="C579" s="21"/>
@@ -16949,10 +16949,10 @@
       <c r="E579" s="21"/>
       <c r="F579" s="21"/>
       <c r="G579" s="21" t="str">
-        <f>data!$B$44</f>
+        <f>data!$B$43</f>
       </c>
       <c r="I579" s="21" t="str">
-        <f>data!$B$88</f>
+        <f>data!$B$89</f>
       </c>
       <c r="J579" s="21"/>
       <c r="K579" s="21"/>
@@ -16960,7 +16960,7 @@
       <c r="M579" s="21"/>
       <c r="N579" s="21"/>
       <c r="O579" s="21" t="str">
-        <f>data!$B$89</f>
+        <f>data!$B$88</f>
       </c>
     </row>
     <row r="580">
@@ -17085,7 +17085,7 @@
     </row>
     <row r="586">
       <c r="A586" s="21" t="str">
-        <f>data!$B$43</f>
+        <f>data!$B$44</f>
       </c>
       <c r="B586" s="21" t="s">
         <v>242</v>
@@ -17101,10 +17101,10 @@
         <v>242</v>
       </c>
       <c r="G586" s="21" t="str">
-        <f>data!$B$44</f>
+        <f>data!$B$43</f>
       </c>
       <c r="I586" s="21" t="str">
-        <f>data!$B$88</f>
+        <f>data!$B$89</f>
       </c>
       <c r="J586" s="21" t="s">
         <v>242</v>
@@ -17120,7 +17120,7 @@
         <v>242</v>
       </c>
       <c r="O586" s="21" t="str">
-        <f>data!$B$89</f>
+        <f>data!$B$88</f>
       </c>
     </row>
     <row r="587">
@@ -17148,7 +17148,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="23" t="s">
+      <c r="A591" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B591" s="21"/>
@@ -17158,10 +17158,10 @@
       </c>
       <c r="E591" s="21"/>
       <c r="F591" s="21"/>
-      <c r="G591" s="24" t="s">
+      <c r="G591" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I591" s="23" t="s">
+      <c r="I591" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J591" s="21"/>
@@ -17171,13 +17171,13 @@
       </c>
       <c r="M591" s="21"/>
       <c r="N591" s="21"/>
-      <c r="O591" s="24" t="s">
+      <c r="O591" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="21" t="str">
-        <f>data!$B$43</f>
+        <f>data!$B$45</f>
       </c>
       <c r="B592" s="21"/>
       <c r="C592" s="21"/>
@@ -17185,10 +17185,10 @@
       <c r="E592" s="21"/>
       <c r="F592" s="21"/>
       <c r="G592" s="21" t="str">
-        <f>data!$B$45</f>
+        <f>data!$B$43</f>
       </c>
       <c r="I592" s="21" t="str">
-        <f>data!$B$88</f>
+        <f>data!$B$90</f>
       </c>
       <c r="J592" s="21"/>
       <c r="K592" s="21"/>
@@ -17196,7 +17196,7 @@
       <c r="M592" s="21"/>
       <c r="N592" s="21"/>
       <c r="O592" s="21" t="str">
-        <f>data!$B$90</f>
+        <f>data!$B$88</f>
       </c>
     </row>
     <row r="593">
@@ -17321,7 +17321,7 @@
     </row>
     <row r="599">
       <c r="A599" s="21" t="str">
-        <f>data!$B$43</f>
+        <f>data!$B$45</f>
       </c>
       <c r="B599" s="21" t="s">
         <v>242</v>
@@ -17337,10 +17337,10 @@
         <v>242</v>
       </c>
       <c r="G599" s="21" t="str">
-        <f>data!$B$45</f>
+        <f>data!$B$43</f>
       </c>
       <c r="I599" s="21" t="str">
-        <f>data!$B$88</f>
+        <f>data!$B$90</f>
       </c>
       <c r="J599" s="21" t="s">
         <v>242</v>
@@ -17356,7 +17356,7 @@
         <v>242</v>
       </c>
       <c r="O599" s="21" t="str">
-        <f>data!$B$90</f>
+        <f>data!$B$88</f>
       </c>
     </row>
     <row r="600">
@@ -17384,7 +17384,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="23" t="s">
+      <c r="A604" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B604" s="21"/>
@@ -17394,10 +17394,10 @@
       </c>
       <c r="E604" s="21"/>
       <c r="F604" s="21"/>
-      <c r="G604" s="24" t="s">
+      <c r="G604" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I604" s="23" t="s">
+      <c r="I604" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J604" s="21"/>
@@ -17407,13 +17407,13 @@
       </c>
       <c r="M604" s="21"/>
       <c r="N604" s="21"/>
-      <c r="O604" s="24" t="s">
+      <c r="O604" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="21" t="str">
-        <f>data!$B$44</f>
+        <f>data!$B$45</f>
       </c>
       <c r="B605" s="21"/>
       <c r="C605" s="21"/>
@@ -17421,10 +17421,10 @@
       <c r="E605" s="21"/>
       <c r="F605" s="21"/>
       <c r="G605" s="21" t="str">
-        <f>data!$B$45</f>
+        <f>data!$B$44</f>
       </c>
       <c r="I605" s="21" t="str">
-        <f>data!$B$89</f>
+        <f>data!$B$90</f>
       </c>
       <c r="J605" s="21"/>
       <c r="K605" s="21"/>
@@ -17432,7 +17432,7 @@
       <c r="M605" s="21"/>
       <c r="N605" s="21"/>
       <c r="O605" s="21" t="str">
-        <f>data!$B$90</f>
+        <f>data!$B$89</f>
       </c>
     </row>
     <row r="606">
@@ -17557,7 +17557,7 @@
     </row>
     <row r="612">
       <c r="A612" s="21" t="str">
-        <f>data!$B$44</f>
+        <f>data!$B$45</f>
       </c>
       <c r="B612" s="21" t="s">
         <v>242</v>
@@ -17573,10 +17573,10 @@
         <v>242</v>
       </c>
       <c r="G612" s="21" t="str">
-        <f>data!$B$45</f>
+        <f>data!$B$44</f>
       </c>
       <c r="I612" s="21" t="str">
-        <f>data!$B$89</f>
+        <f>data!$B$90</f>
       </c>
       <c r="J612" s="21" t="s">
         <v>242</v>
@@ -17592,7 +17592,7 @@
         <v>242</v>
       </c>
       <c r="O612" s="21" t="str">
-        <f>data!$B$90</f>
+        <f>data!$B$89</f>
       </c>
     </row>
     <row r="613">
@@ -17670,7 +17670,7 @@
       <c r="O620" s="20"/>
     </row>
     <row r="621">
-      <c r="A621" s="23" t="s">
+      <c r="A621" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B621" s="21"/>
@@ -17680,10 +17680,10 @@
       </c>
       <c r="E621" s="21"/>
       <c r="F621" s="21"/>
-      <c r="G621" s="24" t="s">
+      <c r="G621" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I621" s="23" t="s">
+      <c r="I621" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J621" s="21"/>
@@ -17693,13 +17693,13 @@
       </c>
       <c r="M621" s="21"/>
       <c r="N621" s="21"/>
-      <c r="O621" s="24" t="s">
+      <c r="O621" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="21" t="str">
-        <f>data!$B$46</f>
+        <f>data!$B$47</f>
       </c>
       <c r="B622" s="21"/>
       <c r="C622" s="21"/>
@@ -17707,10 +17707,10 @@
       <c r="E622" s="21"/>
       <c r="F622" s="21"/>
       <c r="G622" s="21" t="str">
-        <f>data!$B$47</f>
+        <f>data!$B$46</f>
       </c>
       <c r="I622" s="21" t="str">
-        <f>data!$B$91</f>
+        <f>data!$B$92</f>
       </c>
       <c r="J622" s="21"/>
       <c r="K622" s="21"/>
@@ -17718,7 +17718,7 @@
       <c r="M622" s="21"/>
       <c r="N622" s="21"/>
       <c r="O622" s="21" t="str">
-        <f>data!$B$92</f>
+        <f>data!$B$91</f>
       </c>
     </row>
     <row r="623">
@@ -17843,7 +17843,7 @@
     </row>
     <row r="629">
       <c r="A629" s="21" t="str">
-        <f>data!$B$46</f>
+        <f>data!$B$47</f>
       </c>
       <c r="B629" s="21" t="s">
         <v>242</v>
@@ -17859,10 +17859,10 @@
         <v>242</v>
       </c>
       <c r="G629" s="21" t="str">
-        <f>data!$B$47</f>
+        <f>data!$B$46</f>
       </c>
       <c r="I629" s="21" t="str">
-        <f>data!$B$91</f>
+        <f>data!$B$92</f>
       </c>
       <c r="J629" s="21" t="s">
         <v>242</v>
@@ -17878,7 +17878,7 @@
         <v>242</v>
       </c>
       <c r="O629" s="21" t="str">
-        <f>data!$B$92</f>
+        <f>data!$B$91</f>
       </c>
     </row>
     <row r="630">
@@ -17906,7 +17906,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="23" t="s">
+      <c r="A634" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B634" s="21"/>
@@ -17916,10 +17916,10 @@
       </c>
       <c r="E634" s="21"/>
       <c r="F634" s="21"/>
-      <c r="G634" s="24" t="s">
+      <c r="G634" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I634" s="23" t="s">
+      <c r="I634" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J634" s="21"/>
@@ -17929,13 +17929,13 @@
       </c>
       <c r="M634" s="21"/>
       <c r="N634" s="21"/>
-      <c r="O634" s="24" t="s">
+      <c r="O634" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="21" t="str">
-        <f>data!$B$46</f>
+        <f>data!$B$48</f>
       </c>
       <c r="B635" s="21"/>
       <c r="C635" s="21"/>
@@ -17943,10 +17943,10 @@
       <c r="E635" s="21"/>
       <c r="F635" s="21"/>
       <c r="G635" s="21" t="str">
-        <f>data!$B$48</f>
+        <f>data!$B$46</f>
       </c>
       <c r="I635" s="21" t="str">
-        <f>data!$B$91</f>
+        <f>data!$B$93</f>
       </c>
       <c r="J635" s="21"/>
       <c r="K635" s="21"/>
@@ -17954,7 +17954,7 @@
       <c r="M635" s="21"/>
       <c r="N635" s="21"/>
       <c r="O635" s="21" t="str">
-        <f>data!$B$93</f>
+        <f>data!$B$91</f>
       </c>
     </row>
     <row r="636">
@@ -18079,7 +18079,7 @@
     </row>
     <row r="642">
       <c r="A642" s="21" t="str">
-        <f>data!$B$46</f>
+        <f>data!$B$48</f>
       </c>
       <c r="B642" s="21" t="s">
         <v>242</v>
@@ -18095,10 +18095,10 @@
         <v>242</v>
       </c>
       <c r="G642" s="21" t="str">
-        <f>data!$B$48</f>
+        <f>data!$B$46</f>
       </c>
       <c r="I642" s="21" t="str">
-        <f>data!$B$91</f>
+        <f>data!$B$93</f>
       </c>
       <c r="J642" s="21" t="s">
         <v>242</v>
@@ -18114,7 +18114,7 @@
         <v>242</v>
       </c>
       <c r="O642" s="21" t="str">
-        <f>data!$B$93</f>
+        <f>data!$B$91</f>
       </c>
     </row>
     <row r="643">
@@ -18142,7 +18142,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="23" t="s">
+      <c r="A647" s="24" t="s">
         <v>239</v>
       </c>
       <c r="B647" s="21"/>
@@ -18152,10 +18152,10 @@
       </c>
       <c r="E647" s="21"/>
       <c r="F647" s="21"/>
-      <c r="G647" s="24" t="s">
+      <c r="G647" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I647" s="23" t="s">
+      <c r="I647" s="24" t="s">
         <v>239</v>
       </c>
       <c r="J647" s="21"/>
@@ -18165,13 +18165,13 @@
       </c>
       <c r="M647" s="21"/>
       <c r="N647" s="21"/>
-      <c r="O647" s="24" t="s">
+      <c r="O647" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="21" t="str">
-        <f>data!$B$47</f>
+        <f>data!$B$48</f>
       </c>
       <c r="B648" s="21"/>
       <c r="C648" s="21"/>
@@ -18179,10 +18179,10 @@
       <c r="E648" s="21"/>
       <c r="F648" s="21"/>
       <c r="G648" s="21" t="str">
-        <f>data!$B$48</f>
+        <f>data!$B$47</f>
       </c>
       <c r="I648" s="21" t="str">
-        <f>data!$B$92</f>
+        <f>data!$B$93</f>
       </c>
       <c r="J648" s="21"/>
       <c r="K648" s="21"/>
@@ -18190,7 +18190,7 @@
       <c r="M648" s="21"/>
       <c r="N648" s="21"/>
       <c r="O648" s="21" t="str">
-        <f>data!$B$93</f>
+        <f>data!$B$92</f>
       </c>
     </row>
     <row r="649">
@@ -18315,7 +18315,7 @@
     </row>
     <row r="655">
       <c r="A655" s="21" t="str">
-        <f>data!$B$47</f>
+        <f>data!$B$48</f>
       </c>
       <c r="B655" s="21" t="s">
         <v>242</v>
@@ -18331,10 +18331,10 @@
         <v>242</v>
       </c>
       <c r="G655" s="21" t="str">
-        <f>data!$B$48</f>
+        <f>data!$B$47</f>
       </c>
       <c r="I655" s="21" t="str">
-        <f>data!$B$92</f>
+        <f>data!$B$93</f>
       </c>
       <c r="J655" s="21" t="s">
         <v>242</v>
@@ -18350,7 +18350,7 @@
         <v>242</v>
       </c>
       <c r="O655" s="21" t="str">
-        <f>data!$B$93</f>
+        <f>data!$B$92</f>
       </c>
     </row>
     <row r="656">
@@ -18532,28 +18532,28 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L4" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O4" s="24" t="s">
+      <c r="O4" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G142)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G100)</f>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -18561,10 +18561,10 @@
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="G5" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G100)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G142)</f>
       </c>
       <c r="I5" s="21" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G228)</f>
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G186)</f>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
@@ -18572,7 +18572,7 @@
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G186)</f>
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G228)</f>
       </c>
     </row>
     <row r="6">
@@ -18697,7 +18697,7 @@
     </row>
     <row r="12">
       <c r="A12" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G142)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G100)</f>
       </c>
       <c r="B12" s="21" t="s">
         <v>242</v>
@@ -18713,10 +18713,10 @@
         <v>242</v>
       </c>
       <c r="G12" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G100)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G142)</f>
       </c>
       <c r="I12" s="21" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G228)</f>
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G186)</f>
       </c>
       <c r="J12" s="21" t="s">
         <v>242</v>
@@ -18732,7 +18732,7 @@
         <v>242</v>
       </c>
       <c r="O12" s="21" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G186)</f>
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G228)</f>
       </c>
     </row>
     <row r="13">
@@ -18800,28 +18800,28 @@
       <c r="O19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L20" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O20" s="24" t="s">
+      <c r="O20" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G314)</f>
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!G272)</f>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -18829,10 +18829,10 @@
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!G272)</f>
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G314)</f>
       </c>
       <c r="I21" s="21" t="str">
-        <f>CONCATENATE("Pool I.1 ",'Pool Matches'!G400)</f>
+        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!G358)</f>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
@@ -18840,7 +18840,7 @@
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
       <c r="O21" s="21" t="str">
-        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!G358)</f>
+        <f>CONCATENATE("Pool I.1 ",'Pool Matches'!G400)</f>
       </c>
     </row>
     <row r="22">
@@ -18965,7 +18965,7 @@
     </row>
     <row r="28">
       <c r="A28" s="21" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G314)</f>
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!G272)</f>
       </c>
       <c r="B28" s="21" t="s">
         <v>242</v>
@@ -18981,10 +18981,10 @@
         <v>242</v>
       </c>
       <c r="G28" s="21" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!G272)</f>
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G314)</f>
       </c>
       <c r="I28" s="21" t="str">
-        <f>CONCATENATE("Pool I.1 ",'Pool Matches'!G400)</f>
+        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!G358)</f>
       </c>
       <c r="J28" s="21" t="s">
         <v>242</v>
@@ -19000,7 +19000,7 @@
         <v>242</v>
       </c>
       <c r="O28" s="21" t="str">
-        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!G358)</f>
+        <f>CONCATENATE("Pool I.1 ",'Pool Matches'!G400)</f>
       </c>
     </row>
     <row r="29">
@@ -19068,28 +19068,28 @@
       <c r="O35" s="20"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D36" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G36" s="24" t="s">
+      <c r="G36" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L36" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O36" s="24" t="s">
+      <c r="O36" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="str">
-        <f>CONCATENATE("Pool K.1 ",'Pool Matches'!G486)</f>
+        <f>CONCATENATE("Pool J.2 ",'Pool Matches'!G444)</f>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -19097,10 +19097,10 @@
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21" t="str">
-        <f>CONCATENATE("Pool J.2 ",'Pool Matches'!G444)</f>
+        <f>CONCATENATE("Pool K.1 ",'Pool Matches'!G486)</f>
       </c>
       <c r="I37" s="21" t="str">
-        <f>CONCATENATE("Pool M.1 ",'Pool Matches'!G572)</f>
+        <f>CONCATENATE("Pool L.2 ",'Pool Matches'!G530)</f>
       </c>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
@@ -19108,7 +19108,7 @@
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
       <c r="O37" s="21" t="str">
-        <f>CONCATENATE("Pool L.2 ",'Pool Matches'!G530)</f>
+        <f>CONCATENATE("Pool M.1 ",'Pool Matches'!G572)</f>
       </c>
     </row>
     <row r="38">
@@ -19233,7 +19233,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="str">
-        <f>CONCATENATE("Pool K.1 ",'Pool Matches'!G486)</f>
+        <f>CONCATENATE("Pool J.2 ",'Pool Matches'!G444)</f>
       </c>
       <c r="B44" s="21" t="s">
         <v>242</v>
@@ -19249,10 +19249,10 @@
         <v>242</v>
       </c>
       <c r="G44" s="21" t="str">
-        <f>CONCATENATE("Pool J.2 ",'Pool Matches'!G444)</f>
+        <f>CONCATENATE("Pool K.1 ",'Pool Matches'!G486)</f>
       </c>
       <c r="I44" s="21" t="str">
-        <f>CONCATENATE("Pool M.1 ",'Pool Matches'!G572)</f>
+        <f>CONCATENATE("Pool L.2 ",'Pool Matches'!G530)</f>
       </c>
       <c r="J44" s="21" t="s">
         <v>242</v>
@@ -19268,7 +19268,7 @@
         <v>242</v>
       </c>
       <c r="O44" s="21" t="str">
-        <f>CONCATENATE("Pool L.2 ",'Pool Matches'!G530)</f>
+        <f>CONCATENATE("Pool M.1 ",'Pool Matches'!G572)</f>
       </c>
     </row>
     <row r="45">
@@ -19336,28 +19336,28 @@
       <c r="O51" s="20"/>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D52" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G52" s="24" t="s">
+      <c r="G52" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I52" s="23" t="s">
+      <c r="I52" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L52" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O52" s="24" t="s">
+      <c r="O52" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="str">
-        <f>CONCATENATE("Pool O.1 ",'Pool Matches'!G658)</f>
+        <f>CONCATENATE("Pool N.2 ",'Pool Matches'!G616)</f>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -19365,10 +19365,10 @@
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
       <c r="G53" s="21" t="str">
-        <f>CONCATENATE("Pool N.2 ",'Pool Matches'!G616)</f>
+        <f>CONCATENATE("Pool O.1 ",'Pool Matches'!G658)</f>
       </c>
       <c r="I53" s="21" t="str">
-        <f>CONCATENATE("Pool P.2 ",'Pool Matches'!O56)</f>
+        <f>CONCATENATE("Pool R.2 ",'Pool Matches'!O143)</f>
       </c>
       <c r="J53" s="21"/>
       <c r="K53" s="21"/>
@@ -19376,7 +19376,7 @@
       <c r="M53" s="21"/>
       <c r="N53" s="21"/>
       <c r="O53" s="21" t="str">
-        <f>CONCATENATE("Pool R.2 ",'Pool Matches'!O143)</f>
+        <f>CONCATENATE("Pool P.2 ",'Pool Matches'!O56)</f>
       </c>
     </row>
     <row r="54">
@@ -19501,7 +19501,7 @@
     </row>
     <row r="60">
       <c r="A60" s="21" t="str">
-        <f>CONCATENATE("Pool O.1 ",'Pool Matches'!G658)</f>
+        <f>CONCATENATE("Pool N.2 ",'Pool Matches'!G616)</f>
       </c>
       <c r="B60" s="21" t="s">
         <v>242</v>
@@ -19517,10 +19517,10 @@
         <v>242</v>
       </c>
       <c r="G60" s="21" t="str">
-        <f>CONCATENATE("Pool N.2 ",'Pool Matches'!G616)</f>
+        <f>CONCATENATE("Pool O.1 ",'Pool Matches'!G658)</f>
       </c>
       <c r="I60" s="21" t="str">
-        <f>CONCATENATE("Pool P.2 ",'Pool Matches'!O56)</f>
+        <f>CONCATENATE("Pool R.2 ",'Pool Matches'!O143)</f>
       </c>
       <c r="J60" s="21" t="s">
         <v>242</v>
@@ -19536,7 +19536,7 @@
         <v>242</v>
       </c>
       <c r="O60" s="21" t="str">
-        <f>CONCATENATE("Pool R.2 ",'Pool Matches'!O143)</f>
+        <f>CONCATENATE("Pool P.2 ",'Pool Matches'!O56)</f>
       </c>
     </row>
     <row r="61">
@@ -19604,28 +19604,28 @@
       <c r="O67" s="20"/>
     </row>
     <row r="68">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G68" s="24" t="s">
+      <c r="G68" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I68" s="23" t="s">
+      <c r="I68" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L68" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O68" s="24" t="s">
+      <c r="O68" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="str">
-        <f>CONCATENATE("Pool S.1 ",'Pool Matches'!O185)</f>
+        <f>CONCATENATE("Pool T.2 ",'Pool Matches'!O229)</f>
       </c>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
@@ -19633,10 +19633,10 @@
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
       <c r="G69" s="21" t="str">
-        <f>CONCATENATE("Pool T.2 ",'Pool Matches'!O229)</f>
+        <f>CONCATENATE("Pool S.1 ",'Pool Matches'!O185)</f>
       </c>
       <c r="I69" s="21" t="str">
-        <f>CONCATENATE("Pool U.1 ",'Pool Matches'!O271)</f>
+        <f>CONCATENATE("Pool V.2 ",'Pool Matches'!O315)</f>
       </c>
       <c r="J69" s="21"/>
       <c r="K69" s="21"/>
@@ -19644,7 +19644,7 @@
       <c r="M69" s="21"/>
       <c r="N69" s="21"/>
       <c r="O69" s="21" t="str">
-        <f>CONCATENATE("Pool V.2 ",'Pool Matches'!O315)</f>
+        <f>CONCATENATE("Pool U.1 ",'Pool Matches'!O271)</f>
       </c>
     </row>
     <row r="70">
@@ -19769,7 +19769,7 @@
     </row>
     <row r="76">
       <c r="A76" s="21" t="str">
-        <f>CONCATENATE("Pool S.1 ",'Pool Matches'!O185)</f>
+        <f>CONCATENATE("Pool T.2 ",'Pool Matches'!O229)</f>
       </c>
       <c r="B76" s="21" t="s">
         <v>242</v>
@@ -19785,10 +19785,10 @@
         <v>242</v>
       </c>
       <c r="G76" s="21" t="str">
-        <f>CONCATENATE("Pool T.2 ",'Pool Matches'!O229)</f>
+        <f>CONCATENATE("Pool S.1 ",'Pool Matches'!O185)</f>
       </c>
       <c r="I76" s="21" t="str">
-        <f>CONCATENATE("Pool U.1 ",'Pool Matches'!O271)</f>
+        <f>CONCATENATE("Pool V.2 ",'Pool Matches'!O315)</f>
       </c>
       <c r="J76" s="21" t="s">
         <v>242</v>
@@ -19804,7 +19804,7 @@
         <v>242</v>
       </c>
       <c r="O76" s="21" t="str">
-        <f>CONCATENATE("Pool V.2 ",'Pool Matches'!O315)</f>
+        <f>CONCATENATE("Pool U.1 ",'Pool Matches'!O271)</f>
       </c>
     </row>
     <row r="77">
@@ -19872,28 +19872,28 @@
       <c r="O83" s="20"/>
     </row>
     <row r="84">
-      <c r="A84" s="23" t="s">
+      <c r="A84" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D84" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G84" s="24" t="s">
+      <c r="G84" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I84" s="23" t="s">
+      <c r="I84" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L84" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O84" s="24" t="s">
+      <c r="O84" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="21" t="str">
-        <f>CONCATENATE("Pool W.1 ",'Pool Matches'!O357)</f>
+        <f>CONCATENATE("Pool X.2 ",'Pool Matches'!O401)</f>
       </c>
       <c r="B85" s="21"/>
       <c r="C85" s="21"/>
@@ -19901,10 +19901,10 @@
       <c r="E85" s="21"/>
       <c r="F85" s="21"/>
       <c r="G85" s="21" t="str">
-        <f>CONCATENATE("Pool X.2 ",'Pool Matches'!O401)</f>
+        <f>CONCATENATE("Pool W.1 ",'Pool Matches'!O357)</f>
       </c>
       <c r="I85" s="21" t="str">
-        <f>CONCATENATE("Pool Y.1 ",'Pool Matches'!O443)</f>
+        <f>CONCATENATE("Pool Z.2 ",'Pool Matches'!O487)</f>
       </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
@@ -19912,7 +19912,7 @@
       <c r="M85" s="21"/>
       <c r="N85" s="21"/>
       <c r="O85" s="21" t="str">
-        <f>CONCATENATE("Pool Z.2 ",'Pool Matches'!O487)</f>
+        <f>CONCATENATE("Pool Y.1 ",'Pool Matches'!O443)</f>
       </c>
     </row>
     <row r="86">
@@ -20037,7 +20037,7 @@
     </row>
     <row r="92">
       <c r="A92" s="21" t="str">
-        <f>CONCATENATE("Pool W.1 ",'Pool Matches'!O357)</f>
+        <f>CONCATENATE("Pool X.2 ",'Pool Matches'!O401)</f>
       </c>
       <c r="B92" s="21" t="s">
         <v>242</v>
@@ -20053,10 +20053,10 @@
         <v>242</v>
       </c>
       <c r="G92" s="21" t="str">
-        <f>CONCATENATE("Pool X.2 ",'Pool Matches'!O401)</f>
+        <f>CONCATENATE("Pool W.1 ",'Pool Matches'!O357)</f>
       </c>
       <c r="I92" s="21" t="str">
-        <f>CONCATENATE("Pool Y.1 ",'Pool Matches'!O443)</f>
+        <f>CONCATENATE("Pool Z.2 ",'Pool Matches'!O487)</f>
       </c>
       <c r="J92" s="21" t="s">
         <v>242</v>
@@ -20072,7 +20072,7 @@
         <v>242</v>
       </c>
       <c r="O92" s="21" t="str">
-        <f>CONCATENATE("Pool Z.2 ",'Pool Matches'!O487)</f>
+        <f>CONCATENATE("Pool Y.1 ",'Pool Matches'!O443)</f>
       </c>
     </row>
     <row r="93">
@@ -20140,28 +20140,28 @@
       <c r="O99" s="20"/>
     </row>
     <row r="100">
-      <c r="A100" s="23" t="s">
+      <c r="A100" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D100" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G100" s="24" t="s">
+      <c r="G100" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I100" s="23" t="s">
+      <c r="I100" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L100" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O100" s="24" t="s">
+      <c r="O100" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="21" t="str">
-        <f>CONCATENATE("Pool AA.1 ",'Pool Matches'!O529)</f>
+        <f>CONCATENATE("Pool BB.2 ",'Pool Matches'!O573)</f>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="21"/>
@@ -20169,10 +20169,10 @@
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
       <c r="G101" s="21" t="str">
-        <f>CONCATENATE("Pool BB.2 ",'Pool Matches'!O573)</f>
+        <f>CONCATENATE("Pool AA.1 ",'Pool Matches'!O529)</f>
       </c>
       <c r="I101" s="21" t="str">
-        <f>CONCATENATE("Pool CC.1 ",'Pool Matches'!O615)</f>
+        <f>CONCATENATE("Pool DD.2 ",'Pool Matches'!O659)</f>
       </c>
       <c r="J101" s="21"/>
       <c r="K101" s="21"/>
@@ -20180,7 +20180,7 @@
       <c r="M101" s="21"/>
       <c r="N101" s="21"/>
       <c r="O101" s="21" t="str">
-        <f>CONCATENATE("Pool DD.2 ",'Pool Matches'!O659)</f>
+        <f>CONCATENATE("Pool CC.1 ",'Pool Matches'!O615)</f>
       </c>
     </row>
     <row r="102">
@@ -20305,7 +20305,7 @@
     </row>
     <row r="108">
       <c r="A108" s="21" t="str">
-        <f>CONCATENATE("Pool AA.1 ",'Pool Matches'!O529)</f>
+        <f>CONCATENATE("Pool BB.2 ",'Pool Matches'!O573)</f>
       </c>
       <c r="B108" s="21" t="s">
         <v>242</v>
@@ -20321,10 +20321,10 @@
         <v>242</v>
       </c>
       <c r="G108" s="21" t="str">
-        <f>CONCATENATE("Pool BB.2 ",'Pool Matches'!O573)</f>
+        <f>CONCATENATE("Pool AA.1 ",'Pool Matches'!O529)</f>
       </c>
       <c r="I108" s="21" t="str">
-        <f>CONCATENATE("Pool CC.1 ",'Pool Matches'!O615)</f>
+        <f>CONCATENATE("Pool DD.2 ",'Pool Matches'!O659)</f>
       </c>
       <c r="J108" s="21" t="s">
         <v>242</v>
@@ -20340,7 +20340,7 @@
         <v>242</v>
       </c>
       <c r="O108" s="21" t="str">
-        <f>CONCATENATE("Pool DD.2 ",'Pool Matches'!O659)</f>
+        <f>CONCATENATE("Pool CC.1 ",'Pool Matches'!O615)</f>
       </c>
     </row>
     <row r="109">
@@ -20408,28 +20408,28 @@
       <c r="O115" s="20"/>
     </row>
     <row r="116">
-      <c r="A116" s="23" t="s">
+      <c r="A116" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D116" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G116" s="24" t="s">
+      <c r="G116" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I116" s="23" t="s">
+      <c r="I116" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L116" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O116" s="24" t="s">
+      <c r="O116" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="21" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G56)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G143)</f>
       </c>
       <c r="B117" s="21"/>
       <c r="C117" s="21"/>
@@ -20437,10 +20437,10 @@
       <c r="E117" s="21"/>
       <c r="F117" s="21"/>
       <c r="G117" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G143)</f>
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G56)</f>
       </c>
       <c r="I117" s="21" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G185)</f>
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G229)</f>
       </c>
       <c r="J117" s="21"/>
       <c r="K117" s="21"/>
@@ -20448,7 +20448,7 @@
       <c r="M117" s="21"/>
       <c r="N117" s="21"/>
       <c r="O117" s="21" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G229)</f>
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G185)</f>
       </c>
     </row>
     <row r="118">
@@ -20573,7 +20573,7 @@
     </row>
     <row r="124">
       <c r="A124" s="21" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G56)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G143)</f>
       </c>
       <c r="B124" s="21" t="s">
         <v>242</v>
@@ -20589,10 +20589,10 @@
         <v>242</v>
       </c>
       <c r="G124" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G143)</f>
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G56)</f>
       </c>
       <c r="I124" s="21" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G185)</f>
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G229)</f>
       </c>
       <c r="J124" s="21" t="s">
         <v>242</v>
@@ -20608,7 +20608,7 @@
         <v>242</v>
       </c>
       <c r="O124" s="21" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G229)</f>
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G185)</f>
       </c>
     </row>
     <row r="125">
@@ -20676,28 +20676,28 @@
       <c r="O131" s="20"/>
     </row>
     <row r="132">
-      <c r="A132" s="23" t="s">
+      <c r="A132" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D132" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G132" s="24" t="s">
+      <c r="G132" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I132" s="23" t="s">
+      <c r="I132" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L132" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O132" s="24" t="s">
+      <c r="O132" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="21" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!G271)</f>
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G315)</f>
       </c>
       <c r="B133" s="21"/>
       <c r="C133" s="21"/>
@@ -20705,10 +20705,10 @@
       <c r="E133" s="21"/>
       <c r="F133" s="21"/>
       <c r="G133" s="21" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G315)</f>
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!G271)</f>
       </c>
       <c r="I133" s="21" t="str">
-        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!G357)</f>
+        <f>CONCATENATE("Pool I.2 ",'Pool Matches'!G401)</f>
       </c>
       <c r="J133" s="21"/>
       <c r="K133" s="21"/>
@@ -20716,7 +20716,7 @@
       <c r="M133" s="21"/>
       <c r="N133" s="21"/>
       <c r="O133" s="21" t="str">
-        <f>CONCATENATE("Pool I.2 ",'Pool Matches'!G401)</f>
+        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!G357)</f>
       </c>
     </row>
     <row r="134">
@@ -20841,7 +20841,7 @@
     </row>
     <row r="140">
       <c r="A140" s="21" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!G271)</f>
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G315)</f>
       </c>
       <c r="B140" s="21" t="s">
         <v>242</v>
@@ -20857,10 +20857,10 @@
         <v>242</v>
       </c>
       <c r="G140" s="21" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G315)</f>
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!G271)</f>
       </c>
       <c r="I140" s="21" t="str">
-        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!G357)</f>
+        <f>CONCATENATE("Pool I.2 ",'Pool Matches'!G401)</f>
       </c>
       <c r="J140" s="21" t="s">
         <v>242</v>
@@ -20876,7 +20876,7 @@
         <v>242</v>
       </c>
       <c r="O140" s="21" t="str">
-        <f>CONCATENATE("Pool I.2 ",'Pool Matches'!G401)</f>
+        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!G357)</f>
       </c>
     </row>
     <row r="141">
@@ -20944,28 +20944,28 @@
       <c r="O147" s="20"/>
     </row>
     <row r="148">
-      <c r="A148" s="23" t="s">
+      <c r="A148" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D148" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G148" s="24" t="s">
+      <c r="G148" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I148" s="23" t="s">
+      <c r="I148" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L148" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O148" s="24" t="s">
+      <c r="O148" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="21" t="str">
-        <f>CONCATENATE("Pool J.1 ",'Pool Matches'!G443)</f>
+        <f>CONCATENATE("Pool K.2 ",'Pool Matches'!G487)</f>
       </c>
       <c r="B149" s="21"/>
       <c r="C149" s="21"/>
@@ -20973,10 +20973,10 @@
       <c r="E149" s="21"/>
       <c r="F149" s="21"/>
       <c r="G149" s="21" t="str">
-        <f>CONCATENATE("Pool K.2 ",'Pool Matches'!G487)</f>
+        <f>CONCATENATE("Pool J.1 ",'Pool Matches'!G443)</f>
       </c>
       <c r="I149" s="21" t="str">
-        <f>CONCATENATE("Pool L.1 ",'Pool Matches'!G529)</f>
+        <f>CONCATENATE("Pool M.2 ",'Pool Matches'!G573)</f>
       </c>
       <c r="J149" s="21"/>
       <c r="K149" s="21"/>
@@ -20984,7 +20984,7 @@
       <c r="M149" s="21"/>
       <c r="N149" s="21"/>
       <c r="O149" s="21" t="str">
-        <f>CONCATENATE("Pool M.2 ",'Pool Matches'!G573)</f>
+        <f>CONCATENATE("Pool L.1 ",'Pool Matches'!G529)</f>
       </c>
     </row>
     <row r="150">
@@ -21109,7 +21109,7 @@
     </row>
     <row r="156">
       <c r="A156" s="21" t="str">
-        <f>CONCATENATE("Pool J.1 ",'Pool Matches'!G443)</f>
+        <f>CONCATENATE("Pool K.2 ",'Pool Matches'!G487)</f>
       </c>
       <c r="B156" s="21" t="s">
         <v>242</v>
@@ -21125,10 +21125,10 @@
         <v>242</v>
       </c>
       <c r="G156" s="21" t="str">
-        <f>CONCATENATE("Pool K.2 ",'Pool Matches'!G487)</f>
+        <f>CONCATENATE("Pool J.1 ",'Pool Matches'!G443)</f>
       </c>
       <c r="I156" s="21" t="str">
-        <f>CONCATENATE("Pool L.1 ",'Pool Matches'!G529)</f>
+        <f>CONCATENATE("Pool M.2 ",'Pool Matches'!G573)</f>
       </c>
       <c r="J156" s="21" t="s">
         <v>242</v>
@@ -21144,7 +21144,7 @@
         <v>242</v>
       </c>
       <c r="O156" s="21" t="str">
-        <f>CONCATENATE("Pool M.2 ",'Pool Matches'!G573)</f>
+        <f>CONCATENATE("Pool L.1 ",'Pool Matches'!G529)</f>
       </c>
     </row>
     <row r="157">
@@ -21212,28 +21212,28 @@
       <c r="O163" s="20"/>
     </row>
     <row r="164">
-      <c r="A164" s="23" t="s">
+      <c r="A164" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D164" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G164" s="24" t="s">
+      <c r="G164" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I164" s="23" t="s">
+      <c r="I164" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L164" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O164" s="24" t="s">
+      <c r="O164" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="21" t="str">
-        <f>CONCATENATE("Pool N.1 ",'Pool Matches'!G615)</f>
+        <f>CONCATENATE("Pool O.2 ",'Pool Matches'!G659)</f>
       </c>
       <c r="B165" s="21"/>
       <c r="C165" s="21"/>
@@ -21241,10 +21241,10 @@
       <c r="E165" s="21"/>
       <c r="F165" s="21"/>
       <c r="G165" s="21" t="str">
-        <f>CONCATENATE("Pool O.2 ",'Pool Matches'!G659)</f>
+        <f>CONCATENATE("Pool N.1 ",'Pool Matches'!G615)</f>
       </c>
       <c r="I165" s="21" t="str">
-        <f>CONCATENATE("Pool R.1 ",'Pool Matches'!O142)</f>
+        <f>CONCATENATE("Pool Q.2 ",'Pool Matches'!O100)</f>
       </c>
       <c r="J165" s="21"/>
       <c r="K165" s="21"/>
@@ -21252,7 +21252,7 @@
       <c r="M165" s="21"/>
       <c r="N165" s="21"/>
       <c r="O165" s="21" t="str">
-        <f>CONCATENATE("Pool Q.2 ",'Pool Matches'!O100)</f>
+        <f>CONCATENATE("Pool R.1 ",'Pool Matches'!O142)</f>
       </c>
     </row>
     <row r="166">
@@ -21377,7 +21377,7 @@
     </row>
     <row r="172">
       <c r="A172" s="21" t="str">
-        <f>CONCATENATE("Pool N.1 ",'Pool Matches'!G615)</f>
+        <f>CONCATENATE("Pool O.2 ",'Pool Matches'!G659)</f>
       </c>
       <c r="B172" s="21" t="s">
         <v>242</v>
@@ -21393,10 +21393,10 @@
         <v>242</v>
       </c>
       <c r="G172" s="21" t="str">
-        <f>CONCATENATE("Pool O.2 ",'Pool Matches'!G659)</f>
+        <f>CONCATENATE("Pool N.1 ",'Pool Matches'!G615)</f>
       </c>
       <c r="I172" s="21" t="str">
-        <f>CONCATENATE("Pool R.1 ",'Pool Matches'!O142)</f>
+        <f>CONCATENATE("Pool Q.2 ",'Pool Matches'!O100)</f>
       </c>
       <c r="J172" s="21" t="s">
         <v>242</v>
@@ -21412,7 +21412,7 @@
         <v>242</v>
       </c>
       <c r="O172" s="21" t="str">
-        <f>CONCATENATE("Pool Q.2 ",'Pool Matches'!O100)</f>
+        <f>CONCATENATE("Pool R.1 ",'Pool Matches'!O142)</f>
       </c>
     </row>
     <row r="173">
@@ -21480,28 +21480,28 @@
       <c r="O179" s="20"/>
     </row>
     <row r="180">
-      <c r="A180" s="23" t="s">
+      <c r="A180" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D180" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G180" s="24" t="s">
+      <c r="G180" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I180" s="23" t="s">
+      <c r="I180" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L180" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O180" s="24" t="s">
+      <c r="O180" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="21" t="str">
-        <f>CONCATENATE("Pool T.1 ",'Pool Matches'!O228)</f>
+        <f>CONCATENATE("Pool S.2 ",'Pool Matches'!O186)</f>
       </c>
       <c r="B181" s="21"/>
       <c r="C181" s="21"/>
@@ -21509,10 +21509,10 @@
       <c r="E181" s="21"/>
       <c r="F181" s="21"/>
       <c r="G181" s="21" t="str">
-        <f>CONCATENATE("Pool S.2 ",'Pool Matches'!O186)</f>
+        <f>CONCATENATE("Pool T.1 ",'Pool Matches'!O228)</f>
       </c>
       <c r="I181" s="21" t="str">
-        <f>CONCATENATE("Pool V.1 ",'Pool Matches'!O314)</f>
+        <f>CONCATENATE("Pool U.2 ",'Pool Matches'!O272)</f>
       </c>
       <c r="J181" s="21"/>
       <c r="K181" s="21"/>
@@ -21520,7 +21520,7 @@
       <c r="M181" s="21"/>
       <c r="N181" s="21"/>
       <c r="O181" s="21" t="str">
-        <f>CONCATENATE("Pool U.2 ",'Pool Matches'!O272)</f>
+        <f>CONCATENATE("Pool V.1 ",'Pool Matches'!O314)</f>
       </c>
     </row>
     <row r="182">
@@ -21645,7 +21645,7 @@
     </row>
     <row r="188">
       <c r="A188" s="21" t="str">
-        <f>CONCATENATE("Pool T.1 ",'Pool Matches'!O228)</f>
+        <f>CONCATENATE("Pool S.2 ",'Pool Matches'!O186)</f>
       </c>
       <c r="B188" s="21" t="s">
         <v>242</v>
@@ -21661,10 +21661,10 @@
         <v>242</v>
       </c>
       <c r="G188" s="21" t="str">
-        <f>CONCATENATE("Pool S.2 ",'Pool Matches'!O186)</f>
+        <f>CONCATENATE("Pool T.1 ",'Pool Matches'!O228)</f>
       </c>
       <c r="I188" s="21" t="str">
-        <f>CONCATENATE("Pool V.1 ",'Pool Matches'!O314)</f>
+        <f>CONCATENATE("Pool U.2 ",'Pool Matches'!O272)</f>
       </c>
       <c r="J188" s="21" t="s">
         <v>242</v>
@@ -21680,7 +21680,7 @@
         <v>242</v>
       </c>
       <c r="O188" s="21" t="str">
-        <f>CONCATENATE("Pool U.2 ",'Pool Matches'!O272)</f>
+        <f>CONCATENATE("Pool V.1 ",'Pool Matches'!O314)</f>
       </c>
     </row>
     <row r="189">
@@ -21748,28 +21748,28 @@
       <c r="O195" s="20"/>
     </row>
     <row r="196">
-      <c r="A196" s="23" t="s">
+      <c r="A196" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D196" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G196" s="24" t="s">
+      <c r="G196" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I196" s="23" t="s">
+      <c r="I196" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L196" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O196" s="24" t="s">
+      <c r="O196" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="21" t="str">
-        <f>CONCATENATE("Pool X.1 ",'Pool Matches'!O400)</f>
+        <f>CONCATENATE("Pool W.2 ",'Pool Matches'!O358)</f>
       </c>
       <c r="B197" s="21"/>
       <c r="C197" s="21"/>
@@ -21777,10 +21777,10 @@
       <c r="E197" s="21"/>
       <c r="F197" s="21"/>
       <c r="G197" s="21" t="str">
-        <f>CONCATENATE("Pool W.2 ",'Pool Matches'!O358)</f>
+        <f>CONCATENATE("Pool X.1 ",'Pool Matches'!O400)</f>
       </c>
       <c r="I197" s="21" t="str">
-        <f>CONCATENATE("Pool Z.1 ",'Pool Matches'!O486)</f>
+        <f>CONCATENATE("Pool Y.2 ",'Pool Matches'!O444)</f>
       </c>
       <c r="J197" s="21"/>
       <c r="K197" s="21"/>
@@ -21788,7 +21788,7 @@
       <c r="M197" s="21"/>
       <c r="N197" s="21"/>
       <c r="O197" s="21" t="str">
-        <f>CONCATENATE("Pool Y.2 ",'Pool Matches'!O444)</f>
+        <f>CONCATENATE("Pool Z.1 ",'Pool Matches'!O486)</f>
       </c>
     </row>
     <row r="198">
@@ -21913,7 +21913,7 @@
     </row>
     <row r="204">
       <c r="A204" s="21" t="str">
-        <f>CONCATENATE("Pool X.1 ",'Pool Matches'!O400)</f>
+        <f>CONCATENATE("Pool W.2 ",'Pool Matches'!O358)</f>
       </c>
       <c r="B204" s="21" t="s">
         <v>242</v>
@@ -21929,10 +21929,10 @@
         <v>242</v>
       </c>
       <c r="G204" s="21" t="str">
-        <f>CONCATENATE("Pool W.2 ",'Pool Matches'!O358)</f>
+        <f>CONCATENATE("Pool X.1 ",'Pool Matches'!O400)</f>
       </c>
       <c r="I204" s="21" t="str">
-        <f>CONCATENATE("Pool Z.1 ",'Pool Matches'!O486)</f>
+        <f>CONCATENATE("Pool Y.2 ",'Pool Matches'!O444)</f>
       </c>
       <c r="J204" s="21" t="s">
         <v>242</v>
@@ -21948,7 +21948,7 @@
         <v>242</v>
       </c>
       <c r="O204" s="21" t="str">
-        <f>CONCATENATE("Pool Y.2 ",'Pool Matches'!O444)</f>
+        <f>CONCATENATE("Pool Z.1 ",'Pool Matches'!O486)</f>
       </c>
     </row>
     <row r="205">
@@ -22016,28 +22016,28 @@
       <c r="O211" s="20"/>
     </row>
     <row r="212">
-      <c r="A212" s="23" t="s">
+      <c r="A212" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D212" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G212" s="24" t="s">
+      <c r="G212" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I212" s="23" t="s">
+      <c r="I212" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L212" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O212" s="24" t="s">
+      <c r="O212" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="21" t="str">
-        <f>CONCATENATE("Pool BB.1 ",'Pool Matches'!O572)</f>
+        <f>CONCATENATE("Pool AA.2 ",'Pool Matches'!O530)</f>
       </c>
       <c r="B213" s="21"/>
       <c r="C213" s="21"/>
@@ -22045,10 +22045,10 @@
       <c r="E213" s="21"/>
       <c r="F213" s="21"/>
       <c r="G213" s="21" t="str">
-        <f>CONCATENATE("Pool AA.2 ",'Pool Matches'!O530)</f>
+        <f>CONCATENATE("Pool BB.1 ",'Pool Matches'!O572)</f>
       </c>
       <c r="I213" s="21" t="str">
-        <f>CONCATENATE("Pool DD.1 ",'Pool Matches'!O658)</f>
+        <f>CONCATENATE("Pool CC.2 ",'Pool Matches'!O616)</f>
       </c>
       <c r="J213" s="21"/>
       <c r="K213" s="21"/>
@@ -22056,7 +22056,7 @@
       <c r="M213" s="21"/>
       <c r="N213" s="21"/>
       <c r="O213" s="21" t="str">
-        <f>CONCATENATE("Pool CC.2 ",'Pool Matches'!O616)</f>
+        <f>CONCATENATE("Pool DD.1 ",'Pool Matches'!O658)</f>
       </c>
     </row>
     <row r="214">
@@ -22181,7 +22181,7 @@
     </row>
     <row r="220">
       <c r="A220" s="21" t="str">
-        <f>CONCATENATE("Pool BB.1 ",'Pool Matches'!O572)</f>
+        <f>CONCATENATE("Pool AA.2 ",'Pool Matches'!O530)</f>
       </c>
       <c r="B220" s="21" t="s">
         <v>242</v>
@@ -22197,10 +22197,10 @@
         <v>242</v>
       </c>
       <c r="G220" s="21" t="str">
-        <f>CONCATENATE("Pool AA.2 ",'Pool Matches'!O530)</f>
+        <f>CONCATENATE("Pool BB.1 ",'Pool Matches'!O572)</f>
       </c>
       <c r="I220" s="21" t="str">
-        <f>CONCATENATE("Pool DD.1 ",'Pool Matches'!O658)</f>
+        <f>CONCATENATE("Pool CC.2 ",'Pool Matches'!O616)</f>
       </c>
       <c r="J220" s="21" t="s">
         <v>242</v>
@@ -22216,7 +22216,7 @@
         <v>242</v>
       </c>
       <c r="O220" s="21" t="str">
-        <f>CONCATENATE("Pool CC.2 ",'Pool Matches'!O616)</f>
+        <f>CONCATENATE("Pool DD.1 ",'Pool Matches'!O658)</f>
       </c>
     </row>
     <row r="221">
@@ -22303,28 +22303,28 @@
       <c r="O234" s="20"/>
     </row>
     <row r="235">
-      <c r="A235" s="23" t="s">
+      <c r="A235" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D235" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G235" s="24" t="s">
+      <c r="G235" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I235" s="23" t="s">
+      <c r="I235" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L235" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O235" s="24" t="s">
+      <c r="O235" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="21" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="B236" s="21"/>
       <c r="C236" s="21"/>
@@ -22332,10 +22332,10 @@
       <c r="E236" s="21"/>
       <c r="F236" s="21"/>
       <c r="G236" s="21" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G55)</f>
       </c>
       <c r="I236" s="21" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G31)</f>
       </c>
       <c r="J236" s="21"/>
       <c r="K236" s="21"/>
@@ -22343,7 +22343,7 @@
       <c r="M236" s="21"/>
       <c r="N236" s="21"/>
       <c r="O236" s="21" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G31)</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
     <row r="237">
@@ -22468,7 +22468,7 @@
     </row>
     <row r="243">
       <c r="A243" s="21" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="B243" s="21" t="s">
         <v>242</v>
@@ -22484,10 +22484,10 @@
         <v>242</v>
       </c>
       <c r="G243" s="21" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G55)</f>
       </c>
       <c r="I243" s="21" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G31)</f>
       </c>
       <c r="J243" s="21" t="s">
         <v>242</v>
@@ -22503,7 +22503,7 @@
         <v>242</v>
       </c>
       <c r="O243" s="21" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G31)</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
     <row r="244">
@@ -22571,28 +22571,28 @@
       <c r="O250" s="20"/>
     </row>
     <row r="251">
-      <c r="A251" s="23" t="s">
+      <c r="A251" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D251" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G251" s="24" t="s">
+      <c r="G251" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I251" s="23" t="s">
+      <c r="I251" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L251" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O251" s="24" t="s">
+      <c r="O251" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="21" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O31)</f>
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G47)</f>
       </c>
       <c r="B252" s="21"/>
       <c r="C252" s="21"/>
@@ -22600,10 +22600,10 @@
       <c r="E252" s="21"/>
       <c r="F252" s="21"/>
       <c r="G252" s="21" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G47)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O31)</f>
       </c>
       <c r="I252" s="21" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O47)</f>
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G63)</f>
       </c>
       <c r="J252" s="21"/>
       <c r="K252" s="21"/>
@@ -22611,7 +22611,7 @@
       <c r="M252" s="21"/>
       <c r="N252" s="21"/>
       <c r="O252" s="21" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G63)</f>
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O47)</f>
       </c>
     </row>
     <row r="253">
@@ -22736,7 +22736,7 @@
     </row>
     <row r="259">
       <c r="A259" s="21" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O31)</f>
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G47)</f>
       </c>
       <c r="B259" s="21" t="s">
         <v>242</v>
@@ -22752,10 +22752,10 @@
         <v>242</v>
       </c>
       <c r="G259" s="21" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G47)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O31)</f>
       </c>
       <c r="I259" s="21" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O47)</f>
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G63)</f>
       </c>
       <c r="J259" s="21" t="s">
         <v>242</v>
@@ -22771,7 +22771,7 @@
         <v>242</v>
       </c>
       <c r="O259" s="21" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G63)</f>
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O47)</f>
       </c>
     </row>
     <row r="260">
@@ -22839,28 +22839,28 @@
       <c r="O266" s="20"/>
     </row>
     <row r="267">
-      <c r="A267" s="23" t="s">
+      <c r="A267" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D267" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G267" s="24" t="s">
+      <c r="G267" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I267" s="23" t="s">
+      <c r="I267" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L267" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O267" s="24" t="s">
+      <c r="O267" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="21" t="str">
-        <f>CONCATENATE("Pool Q.1 ",'Pool Matches'!O99)</f>
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O63)</f>
       </c>
       <c r="B268" s="21"/>
       <c r="C268" s="21"/>
@@ -22868,10 +22868,10 @@
       <c r="E268" s="21"/>
       <c r="F268" s="21"/>
       <c r="G268" s="21" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O63)</f>
+        <f>CONCATENATE("Pool Q.1 ",'Pool Matches'!O99)</f>
       </c>
       <c r="I268" s="21" t="str">
-        <f>CONCATENATE("M 9 ",'Elimination Matches'!G79)</f>
+        <f>CONCATENATE("M 10 ",'Elimination Matches'!O79)</f>
       </c>
       <c r="J268" s="21"/>
       <c r="K268" s="21"/>
@@ -22879,7 +22879,7 @@
       <c r="M268" s="21"/>
       <c r="N268" s="21"/>
       <c r="O268" s="21" t="str">
-        <f>CONCATENATE("M 10 ",'Elimination Matches'!O79)</f>
+        <f>CONCATENATE("M 9 ",'Elimination Matches'!G79)</f>
       </c>
     </row>
     <row r="269">
@@ -23004,7 +23004,7 @@
     </row>
     <row r="275">
       <c r="A275" s="21" t="str">
-        <f>CONCATENATE("Pool Q.1 ",'Pool Matches'!O99)</f>
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O63)</f>
       </c>
       <c r="B275" s="21" t="s">
         <v>242</v>
@@ -23020,10 +23020,10 @@
         <v>242</v>
       </c>
       <c r="G275" s="21" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O63)</f>
+        <f>CONCATENATE("Pool Q.1 ",'Pool Matches'!O99)</f>
       </c>
       <c r="I275" s="21" t="str">
-        <f>CONCATENATE("M 9 ",'Elimination Matches'!G79)</f>
+        <f>CONCATENATE("M 10 ",'Elimination Matches'!O79)</f>
       </c>
       <c r="J275" s="21" t="s">
         <v>242</v>
@@ -23039,7 +23039,7 @@
         <v>242</v>
       </c>
       <c r="O275" s="21" t="str">
-        <f>CONCATENATE("M 10 ",'Elimination Matches'!O79)</f>
+        <f>CONCATENATE("M 9 ",'Elimination Matches'!G79)</f>
       </c>
     </row>
     <row r="276">
@@ -23107,28 +23107,28 @@
       <c r="O282" s="20"/>
     </row>
     <row r="283">
-      <c r="A283" s="23" t="s">
+      <c r="A283" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D283" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G283" s="24" t="s">
+      <c r="G283" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I283" s="23" t="s">
+      <c r="I283" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L283" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O283" s="24" t="s">
+      <c r="O283" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="21" t="str">
-        <f>CONCATENATE("M 11 ",'Elimination Matches'!G95)</f>
+        <f>CONCATENATE("M 12 ",'Elimination Matches'!O95)</f>
       </c>
       <c r="B284" s="21"/>
       <c r="C284" s="21"/>
@@ -23136,10 +23136,10 @@
       <c r="E284" s="21"/>
       <c r="F284" s="21"/>
       <c r="G284" s="21" t="str">
-        <f>CONCATENATE("M 12 ",'Elimination Matches'!O95)</f>
+        <f>CONCATENATE("M 11 ",'Elimination Matches'!G95)</f>
       </c>
       <c r="I284" s="21" t="str">
-        <f>CONCATENATE("M 13 ",'Elimination Matches'!G111)</f>
+        <f>CONCATENATE("M 14 ",'Elimination Matches'!O111)</f>
       </c>
       <c r="J284" s="21"/>
       <c r="K284" s="21"/>
@@ -23147,7 +23147,7 @@
       <c r="M284" s="21"/>
       <c r="N284" s="21"/>
       <c r="O284" s="21" t="str">
-        <f>CONCATENATE("M 14 ",'Elimination Matches'!O111)</f>
+        <f>CONCATENATE("M 13 ",'Elimination Matches'!G111)</f>
       </c>
     </row>
     <row r="285">
@@ -23272,7 +23272,7 @@
     </row>
     <row r="291">
       <c r="A291" s="21" t="str">
-        <f>CONCATENATE("M 11 ",'Elimination Matches'!G95)</f>
+        <f>CONCATENATE("M 12 ",'Elimination Matches'!O95)</f>
       </c>
       <c r="B291" s="21" t="s">
         <v>242</v>
@@ -23288,10 +23288,10 @@
         <v>242</v>
       </c>
       <c r="G291" s="21" t="str">
-        <f>CONCATENATE("M 12 ",'Elimination Matches'!O95)</f>
+        <f>CONCATENATE("M 11 ",'Elimination Matches'!G95)</f>
       </c>
       <c r="I291" s="21" t="str">
-        <f>CONCATENATE("M 13 ",'Elimination Matches'!G111)</f>
+        <f>CONCATENATE("M 14 ",'Elimination Matches'!O111)</f>
       </c>
       <c r="J291" s="21" t="s">
         <v>242</v>
@@ -23307,7 +23307,7 @@
         <v>242</v>
       </c>
       <c r="O291" s="21" t="str">
-        <f>CONCATENATE("M 14 ",'Elimination Matches'!O111)</f>
+        <f>CONCATENATE("M 13 ",'Elimination Matches'!G111)</f>
       </c>
     </row>
     <row r="292">
@@ -23375,28 +23375,28 @@
       <c r="O298" s="20"/>
     </row>
     <row r="299">
-      <c r="A299" s="23" t="s">
+      <c r="A299" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D299" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G299" s="24" t="s">
+      <c r="G299" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I299" s="23" t="s">
+      <c r="I299" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L299" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O299" s="24" t="s">
+      <c r="O299" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G99)</f>
+        <f>CONCATENATE("M 15 ",'Elimination Matches'!G127)</f>
       </c>
       <c r="B300" s="21"/>
       <c r="C300" s="21"/>
@@ -23404,10 +23404,10 @@
       <c r="E300" s="21"/>
       <c r="F300" s="21"/>
       <c r="G300" s="21" t="str">
-        <f>CONCATENATE("M 15 ",'Elimination Matches'!G127)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G99)</f>
       </c>
       <c r="I300" s="21" t="str">
-        <f>CONCATENATE("M 16 ",'Elimination Matches'!O127)</f>
+        <f>CONCATENATE("M 17 ",'Elimination Matches'!G143)</f>
       </c>
       <c r="J300" s="21"/>
       <c r="K300" s="21"/>
@@ -23415,7 +23415,7 @@
       <c r="M300" s="21"/>
       <c r="N300" s="21"/>
       <c r="O300" s="21" t="str">
-        <f>CONCATENATE("M 17 ",'Elimination Matches'!G143)</f>
+        <f>CONCATENATE("M 16 ",'Elimination Matches'!O127)</f>
       </c>
     </row>
     <row r="301">
@@ -23540,7 +23540,7 @@
     </row>
     <row r="307">
       <c r="A307" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G99)</f>
+        <f>CONCATENATE("M 15 ",'Elimination Matches'!G127)</f>
       </c>
       <c r="B307" s="21" t="s">
         <v>242</v>
@@ -23556,10 +23556,10 @@
         <v>242</v>
       </c>
       <c r="G307" s="21" t="str">
-        <f>CONCATENATE("M 15 ",'Elimination Matches'!G127)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G99)</f>
       </c>
       <c r="I307" s="21" t="str">
-        <f>CONCATENATE("M 16 ",'Elimination Matches'!O127)</f>
+        <f>CONCATENATE("M 17 ",'Elimination Matches'!G143)</f>
       </c>
       <c r="J307" s="21" t="s">
         <v>242</v>
@@ -23575,7 +23575,7 @@
         <v>242</v>
       </c>
       <c r="O307" s="21" t="str">
-        <f>CONCATENATE("M 17 ",'Elimination Matches'!G143)</f>
+        <f>CONCATENATE("M 16 ",'Elimination Matches'!O127)</f>
       </c>
     </row>
     <row r="308">
@@ -23643,28 +23643,28 @@
       <c r="O314" s="20"/>
     </row>
     <row r="315">
-      <c r="A315" s="23" t="s">
+      <c r="A315" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D315" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G315" s="24" t="s">
+      <c r="G315" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I315" s="23" t="s">
+      <c r="I315" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L315" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O315" s="24" t="s">
+      <c r="O315" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="21" t="str">
-        <f>CONCATENATE("M 18 ",'Elimination Matches'!O143)</f>
+        <f>CONCATENATE("M 19 ",'Elimination Matches'!G159)</f>
       </c>
       <c r="B316" s="21"/>
       <c r="C316" s="21"/>
@@ -23672,10 +23672,10 @@
       <c r="E316" s="21"/>
       <c r="F316" s="21"/>
       <c r="G316" s="21" t="str">
-        <f>CONCATENATE("M 19 ",'Elimination Matches'!G159)</f>
+        <f>CONCATENATE("M 18 ",'Elimination Matches'!O143)</f>
       </c>
       <c r="I316" s="21" t="str">
-        <f>CONCATENATE("M 20 ",'Elimination Matches'!O159)</f>
+        <f>CONCATENATE("M 21 ",'Elimination Matches'!G175)</f>
       </c>
       <c r="J316" s="21"/>
       <c r="K316" s="21"/>
@@ -23683,7 +23683,7 @@
       <c r="M316" s="21"/>
       <c r="N316" s="21"/>
       <c r="O316" s="21" t="str">
-        <f>CONCATENATE("M 21 ",'Elimination Matches'!G175)</f>
+        <f>CONCATENATE("M 20 ",'Elimination Matches'!O159)</f>
       </c>
     </row>
     <row r="317">
@@ -23808,7 +23808,7 @@
     </row>
     <row r="323">
       <c r="A323" s="21" t="str">
-        <f>CONCATENATE("M 18 ",'Elimination Matches'!O143)</f>
+        <f>CONCATENATE("M 19 ",'Elimination Matches'!G159)</f>
       </c>
       <c r="B323" s="21" t="s">
         <v>242</v>
@@ -23824,10 +23824,10 @@
         <v>242</v>
       </c>
       <c r="G323" s="21" t="str">
-        <f>CONCATENATE("M 19 ",'Elimination Matches'!G159)</f>
+        <f>CONCATENATE("M 18 ",'Elimination Matches'!O143)</f>
       </c>
       <c r="I323" s="21" t="str">
-        <f>CONCATENATE("M 20 ",'Elimination Matches'!O159)</f>
+        <f>CONCATENATE("M 21 ",'Elimination Matches'!G175)</f>
       </c>
       <c r="J323" s="21" t="s">
         <v>242</v>
@@ -23843,7 +23843,7 @@
         <v>242</v>
       </c>
       <c r="O323" s="21" t="str">
-        <f>CONCATENATE("M 21 ",'Elimination Matches'!G175)</f>
+        <f>CONCATENATE("M 20 ",'Elimination Matches'!O159)</f>
       </c>
     </row>
     <row r="324">
@@ -23911,28 +23911,28 @@
       <c r="O330" s="20"/>
     </row>
     <row r="331">
-      <c r="A331" s="23" t="s">
+      <c r="A331" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D331" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G331" s="24" t="s">
+      <c r="G331" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I331" s="23" t="s">
+      <c r="I331" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L331" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O331" s="24" t="s">
+      <c r="O331" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="21" t="str">
-        <f>CONCATENATE("Pool P.1 ",'Pool Matches'!O55)</f>
+        <f>CONCATENATE("M 22 ",'Elimination Matches'!O175)</f>
       </c>
       <c r="B332" s="21"/>
       <c r="C332" s="21"/>
@@ -23940,10 +23940,10 @@
       <c r="E332" s="21"/>
       <c r="F332" s="21"/>
       <c r="G332" s="21" t="str">
-        <f>CONCATENATE("M 22 ",'Elimination Matches'!O175)</f>
+        <f>CONCATENATE("Pool P.1 ",'Pool Matches'!O55)</f>
       </c>
       <c r="I332" s="21" t="str">
-        <f>CONCATENATE("M 23 ",'Elimination Matches'!G191)</f>
+        <f>CONCATENATE("M 24 ",'Elimination Matches'!O191)</f>
       </c>
       <c r="J332" s="21"/>
       <c r="K332" s="21"/>
@@ -23951,7 +23951,7 @@
       <c r="M332" s="21"/>
       <c r="N332" s="21"/>
       <c r="O332" s="21" t="str">
-        <f>CONCATENATE("M 24 ",'Elimination Matches'!O191)</f>
+        <f>CONCATENATE("M 23 ",'Elimination Matches'!G191)</f>
       </c>
     </row>
     <row r="333">
@@ -24076,7 +24076,7 @@
     </row>
     <row r="339">
       <c r="A339" s="21" t="str">
-        <f>CONCATENATE("Pool P.1 ",'Pool Matches'!O55)</f>
+        <f>CONCATENATE("M 22 ",'Elimination Matches'!O175)</f>
       </c>
       <c r="B339" s="21" t="s">
         <v>242</v>
@@ -24092,10 +24092,10 @@
         <v>242</v>
       </c>
       <c r="G339" s="21" t="str">
-        <f>CONCATENATE("M 22 ",'Elimination Matches'!O175)</f>
+        <f>CONCATENATE("Pool P.1 ",'Pool Matches'!O55)</f>
       </c>
       <c r="I339" s="21" t="str">
-        <f>CONCATENATE("M 23 ",'Elimination Matches'!G191)</f>
+        <f>CONCATENATE("M 24 ",'Elimination Matches'!O191)</f>
       </c>
       <c r="J339" s="21" t="s">
         <v>242</v>
@@ -24111,7 +24111,7 @@
         <v>242</v>
       </c>
       <c r="O339" s="21" t="str">
-        <f>CONCATENATE("M 24 ",'Elimination Matches'!O191)</f>
+        <f>CONCATENATE("M 23 ",'Elimination Matches'!G191)</f>
       </c>
     </row>
     <row r="340">
@@ -24179,28 +24179,28 @@
       <c r="O346" s="20"/>
     </row>
     <row r="347">
-      <c r="A347" s="23" t="s">
+      <c r="A347" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D347" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G347" s="24" t="s">
+      <c r="G347" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I347" s="23" t="s">
+      <c r="I347" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L347" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O347" s="24" t="s">
+      <c r="O347" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="21" t="str">
-        <f>CONCATENATE("M 25 ",'Elimination Matches'!G207)</f>
+        <f>CONCATENATE("M 26 ",'Elimination Matches'!O207)</f>
       </c>
       <c r="B348" s="21"/>
       <c r="C348" s="21"/>
@@ -24208,10 +24208,10 @@
       <c r="E348" s="21"/>
       <c r="F348" s="21"/>
       <c r="G348" s="21" t="str">
-        <f>CONCATENATE("M 26 ",'Elimination Matches'!O207)</f>
+        <f>CONCATENATE("M 25 ",'Elimination Matches'!G207)</f>
       </c>
       <c r="I348" s="21" t="str">
-        <f>CONCATENATE("M 27 ",'Elimination Matches'!G223)</f>
+        <f>CONCATENATE("M 28 ",'Elimination Matches'!O223)</f>
       </c>
       <c r="J348" s="21"/>
       <c r="K348" s="21"/>
@@ -24219,7 +24219,7 @@
       <c r="M348" s="21"/>
       <c r="N348" s="21"/>
       <c r="O348" s="21" t="str">
-        <f>CONCATENATE("M 28 ",'Elimination Matches'!O223)</f>
+        <f>CONCATENATE("M 27 ",'Elimination Matches'!G223)</f>
       </c>
     </row>
     <row r="349">
@@ -24344,7 +24344,7 @@
     </row>
     <row r="355">
       <c r="A355" s="21" t="str">
-        <f>CONCATENATE("M 25 ",'Elimination Matches'!G207)</f>
+        <f>CONCATENATE("M 26 ",'Elimination Matches'!O207)</f>
       </c>
       <c r="B355" s="21" t="s">
         <v>242</v>
@@ -24360,10 +24360,10 @@
         <v>242</v>
       </c>
       <c r="G355" s="21" t="str">
-        <f>CONCATENATE("M 26 ",'Elimination Matches'!O207)</f>
+        <f>CONCATENATE("M 25 ",'Elimination Matches'!G207)</f>
       </c>
       <c r="I355" s="21" t="str">
-        <f>CONCATENATE("M 27 ",'Elimination Matches'!G223)</f>
+        <f>CONCATENATE("M 28 ",'Elimination Matches'!O223)</f>
       </c>
       <c r="J355" s="21" t="s">
         <v>242</v>
@@ -24379,7 +24379,7 @@
         <v>242</v>
       </c>
       <c r="O355" s="21" t="str">
-        <f>CONCATENATE("M 28 ",'Elimination Matches'!O223)</f>
+        <f>CONCATENATE("M 27 ",'Elimination Matches'!G223)</f>
       </c>
     </row>
     <row r="356">
@@ -24466,28 +24466,28 @@
       <c r="O369" s="20"/>
     </row>
     <row r="370">
-      <c r="A370" s="23" t="s">
+      <c r="A370" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D370" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G370" s="24" t="s">
+      <c r="G370" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I370" s="23" t="s">
+      <c r="I370" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L370" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O370" s="24" t="s">
+      <c r="O370" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="21" t="str">
-        <f>CONCATENATE("M 29 ",'Elimination Matches'!G246)</f>
+        <f>CONCATENATE("M 30 ",'Elimination Matches'!O246)</f>
       </c>
       <c r="B371" s="21"/>
       <c r="C371" s="21"/>
@@ -24495,10 +24495,10 @@
       <c r="E371" s="21"/>
       <c r="F371" s="21"/>
       <c r="G371" s="21" t="str">
-        <f>CONCATENATE("M 30 ",'Elimination Matches'!O246)</f>
+        <f>CONCATENATE("M 29 ",'Elimination Matches'!G246)</f>
       </c>
       <c r="I371" s="21" t="str">
-        <f>CONCATENATE("M 31 ",'Elimination Matches'!G262)</f>
+        <f>CONCATENATE("M 32 ",'Elimination Matches'!O262)</f>
       </c>
       <c r="J371" s="21"/>
       <c r="K371" s="21"/>
@@ -24506,7 +24506,7 @@
       <c r="M371" s="21"/>
       <c r="N371" s="21"/>
       <c r="O371" s="21" t="str">
-        <f>CONCATENATE("M 32 ",'Elimination Matches'!O262)</f>
+        <f>CONCATENATE("M 31 ",'Elimination Matches'!G262)</f>
       </c>
     </row>
     <row r="372">
@@ -24631,7 +24631,7 @@
     </row>
     <row r="378">
       <c r="A378" s="21" t="str">
-        <f>CONCATENATE("M 29 ",'Elimination Matches'!G246)</f>
+        <f>CONCATENATE("M 30 ",'Elimination Matches'!O246)</f>
       </c>
       <c r="B378" s="21" t="s">
         <v>242</v>
@@ -24647,10 +24647,10 @@
         <v>242</v>
       </c>
       <c r="G378" s="21" t="str">
-        <f>CONCATENATE("M 30 ",'Elimination Matches'!O246)</f>
+        <f>CONCATENATE("M 29 ",'Elimination Matches'!G246)</f>
       </c>
       <c r="I378" s="21" t="str">
-        <f>CONCATENATE("M 31 ",'Elimination Matches'!G262)</f>
+        <f>CONCATENATE("M 32 ",'Elimination Matches'!O262)</f>
       </c>
       <c r="J378" s="21" t="s">
         <v>242</v>
@@ -24666,7 +24666,7 @@
         <v>242</v>
       </c>
       <c r="O378" s="21" t="str">
-        <f>CONCATENATE("M 32 ",'Elimination Matches'!O262)</f>
+        <f>CONCATENATE("M 31 ",'Elimination Matches'!G262)</f>
       </c>
     </row>
     <row r="379">
@@ -24734,28 +24734,28 @@
       <c r="O385" s="20"/>
     </row>
     <row r="386">
-      <c r="A386" s="23" t="s">
+      <c r="A386" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D386" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G386" s="24" t="s">
+      <c r="G386" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I386" s="23" t="s">
+      <c r="I386" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L386" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O386" s="24" t="s">
+      <c r="O386" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="21" t="str">
-        <f>CONCATENATE("M 33 ",'Elimination Matches'!G278)</f>
+        <f>CONCATENATE("M 34 ",'Elimination Matches'!O278)</f>
       </c>
       <c r="B387" s="21"/>
       <c r="C387" s="21"/>
@@ -24763,10 +24763,10 @@
       <c r="E387" s="21"/>
       <c r="F387" s="21"/>
       <c r="G387" s="21" t="str">
-        <f>CONCATENATE("M 34 ",'Elimination Matches'!O278)</f>
+        <f>CONCATENATE("M 33 ",'Elimination Matches'!G278)</f>
       </c>
       <c r="I387" s="21" t="str">
-        <f>CONCATENATE("M 35 ",'Elimination Matches'!G294)</f>
+        <f>CONCATENATE("M 36 ",'Elimination Matches'!O294)</f>
       </c>
       <c r="J387" s="21"/>
       <c r="K387" s="21"/>
@@ -24774,7 +24774,7 @@
       <c r="M387" s="21"/>
       <c r="N387" s="21"/>
       <c r="O387" s="21" t="str">
-        <f>CONCATENATE("M 36 ",'Elimination Matches'!O294)</f>
+        <f>CONCATENATE("M 35 ",'Elimination Matches'!G294)</f>
       </c>
     </row>
     <row r="388">
@@ -24899,7 +24899,7 @@
     </row>
     <row r="394">
       <c r="A394" s="21" t="str">
-        <f>CONCATENATE("M 33 ",'Elimination Matches'!G278)</f>
+        <f>CONCATENATE("M 34 ",'Elimination Matches'!O278)</f>
       </c>
       <c r="B394" s="21" t="s">
         <v>242</v>
@@ -24915,10 +24915,10 @@
         <v>242</v>
       </c>
       <c r="G394" s="21" t="str">
-        <f>CONCATENATE("M 34 ",'Elimination Matches'!O278)</f>
+        <f>CONCATENATE("M 33 ",'Elimination Matches'!G278)</f>
       </c>
       <c r="I394" s="21" t="str">
-        <f>CONCATENATE("M 35 ",'Elimination Matches'!G294)</f>
+        <f>CONCATENATE("M 36 ",'Elimination Matches'!O294)</f>
       </c>
       <c r="J394" s="21" t="s">
         <v>242</v>
@@ -24934,7 +24934,7 @@
         <v>242</v>
       </c>
       <c r="O394" s="21" t="str">
-        <f>CONCATENATE("M 36 ",'Elimination Matches'!O294)</f>
+        <f>CONCATENATE("M 35 ",'Elimination Matches'!G294)</f>
       </c>
     </row>
     <row r="395">
@@ -25002,28 +25002,28 @@
       <c r="O401" s="20"/>
     </row>
     <row r="402">
-      <c r="A402" s="23" t="s">
+      <c r="A402" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D402" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G402" s="24" t="s">
+      <c r="G402" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I402" s="23" t="s">
+      <c r="I402" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L402" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O402" s="24" t="s">
+      <c r="O402" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="21" t="str">
-        <f>CONCATENATE("M 37 ",'Elimination Matches'!G310)</f>
+        <f>CONCATENATE("M 38 ",'Elimination Matches'!O310)</f>
       </c>
       <c r="B403" s="21"/>
       <c r="C403" s="21"/>
@@ -25031,10 +25031,10 @@
       <c r="E403" s="21"/>
       <c r="F403" s="21"/>
       <c r="G403" s="21" t="str">
-        <f>CONCATENATE("M 38 ",'Elimination Matches'!O310)</f>
+        <f>CONCATENATE("M 37 ",'Elimination Matches'!G310)</f>
       </c>
       <c r="I403" s="21" t="str">
-        <f>CONCATENATE("M 39 ",'Elimination Matches'!G326)</f>
+        <f>CONCATENATE("M 40 ",'Elimination Matches'!O326)</f>
       </c>
       <c r="J403" s="21"/>
       <c r="K403" s="21"/>
@@ -25042,7 +25042,7 @@
       <c r="M403" s="21"/>
       <c r="N403" s="21"/>
       <c r="O403" s="21" t="str">
-        <f>CONCATENATE("M 40 ",'Elimination Matches'!O326)</f>
+        <f>CONCATENATE("M 39 ",'Elimination Matches'!G326)</f>
       </c>
     </row>
     <row r="404">
@@ -25167,7 +25167,7 @@
     </row>
     <row r="410">
       <c r="A410" s="21" t="str">
-        <f>CONCATENATE("M 37 ",'Elimination Matches'!G310)</f>
+        <f>CONCATENATE("M 38 ",'Elimination Matches'!O310)</f>
       </c>
       <c r="B410" s="21" t="s">
         <v>242</v>
@@ -25183,10 +25183,10 @@
         <v>242</v>
       </c>
       <c r="G410" s="21" t="str">
-        <f>CONCATENATE("M 38 ",'Elimination Matches'!O310)</f>
+        <f>CONCATENATE("M 37 ",'Elimination Matches'!G310)</f>
       </c>
       <c r="I410" s="21" t="str">
-        <f>CONCATENATE("M 39 ",'Elimination Matches'!G326)</f>
+        <f>CONCATENATE("M 40 ",'Elimination Matches'!O326)</f>
       </c>
       <c r="J410" s="21" t="s">
         <v>242</v>
@@ -25202,7 +25202,7 @@
         <v>242</v>
       </c>
       <c r="O410" s="21" t="str">
-        <f>CONCATENATE("M 40 ",'Elimination Matches'!O326)</f>
+        <f>CONCATENATE("M 39 ",'Elimination Matches'!G326)</f>
       </c>
     </row>
     <row r="411">
@@ -25270,28 +25270,28 @@
       <c r="O417" s="20"/>
     </row>
     <row r="418">
-      <c r="A418" s="23" t="s">
+      <c r="A418" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D418" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G418" s="24" t="s">
+      <c r="G418" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I418" s="23" t="s">
+      <c r="I418" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L418" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O418" s="24" t="s">
+      <c r="O418" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="21" t="str">
-        <f>CONCATENATE("M 41 ",'Elimination Matches'!G342)</f>
+        <f>CONCATENATE("M 42 ",'Elimination Matches'!O342)</f>
       </c>
       <c r="B419" s="21"/>
       <c r="C419" s="21"/>
@@ -25299,10 +25299,10 @@
       <c r="E419" s="21"/>
       <c r="F419" s="21"/>
       <c r="G419" s="21" t="str">
-        <f>CONCATENATE("M 42 ",'Elimination Matches'!O342)</f>
+        <f>CONCATENATE("M 41 ",'Elimination Matches'!G342)</f>
       </c>
       <c r="I419" s="21" t="str">
-        <f>CONCATENATE("M 43 ",'Elimination Matches'!G358)</f>
+        <f>CONCATENATE("M 44 ",'Elimination Matches'!O358)</f>
       </c>
       <c r="J419" s="21"/>
       <c r="K419" s="21"/>
@@ -25310,7 +25310,7 @@
       <c r="M419" s="21"/>
       <c r="N419" s="21"/>
       <c r="O419" s="21" t="str">
-        <f>CONCATENATE("M 44 ",'Elimination Matches'!O358)</f>
+        <f>CONCATENATE("M 43 ",'Elimination Matches'!G358)</f>
       </c>
     </row>
     <row r="420">
@@ -25435,7 +25435,7 @@
     </row>
     <row r="426">
       <c r="A426" s="21" t="str">
-        <f>CONCATENATE("M 41 ",'Elimination Matches'!G342)</f>
+        <f>CONCATENATE("M 42 ",'Elimination Matches'!O342)</f>
       </c>
       <c r="B426" s="21" t="s">
         <v>242</v>
@@ -25451,10 +25451,10 @@
         <v>242</v>
       </c>
       <c r="G426" s="21" t="str">
-        <f>CONCATENATE("M 42 ",'Elimination Matches'!O342)</f>
+        <f>CONCATENATE("M 41 ",'Elimination Matches'!G342)</f>
       </c>
       <c r="I426" s="21" t="str">
-        <f>CONCATENATE("M 43 ",'Elimination Matches'!G358)</f>
+        <f>CONCATENATE("M 44 ",'Elimination Matches'!O358)</f>
       </c>
       <c r="J426" s="21" t="s">
         <v>242</v>
@@ -25470,7 +25470,7 @@
         <v>242</v>
       </c>
       <c r="O426" s="21" t="str">
-        <f>CONCATENATE("M 44 ",'Elimination Matches'!O358)</f>
+        <f>CONCATENATE("M 43 ",'Elimination Matches'!G358)</f>
       </c>
     </row>
     <row r="427">
@@ -25557,28 +25557,28 @@
       <c r="O440" s="20"/>
     </row>
     <row r="441">
-      <c r="A441" s="23" t="s">
+      <c r="A441" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D441" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G441" s="24" t="s">
+      <c r="G441" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I441" s="23" t="s">
+      <c r="I441" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L441" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O441" s="24" t="s">
+      <c r="O441" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="21" t="str">
-        <f>CONCATENATE("M 45 ",'Elimination Matches'!G381)</f>
+        <f>CONCATENATE("M 46 ",'Elimination Matches'!O381)</f>
       </c>
       <c r="B442" s="21"/>
       <c r="C442" s="21"/>
@@ -25586,10 +25586,10 @@
       <c r="E442" s="21"/>
       <c r="F442" s="21"/>
       <c r="G442" s="21" t="str">
-        <f>CONCATENATE("M 46 ",'Elimination Matches'!O381)</f>
+        <f>CONCATENATE("M 45 ",'Elimination Matches'!G381)</f>
       </c>
       <c r="I442" s="21" t="str">
-        <f>CONCATENATE("M 47 ",'Elimination Matches'!G397)</f>
+        <f>CONCATENATE("M 48 ",'Elimination Matches'!O397)</f>
       </c>
       <c r="J442" s="21"/>
       <c r="K442" s="21"/>
@@ -25597,7 +25597,7 @@
       <c r="M442" s="21"/>
       <c r="N442" s="21"/>
       <c r="O442" s="21" t="str">
-        <f>CONCATENATE("M 48 ",'Elimination Matches'!O397)</f>
+        <f>CONCATENATE("M 47 ",'Elimination Matches'!G397)</f>
       </c>
     </row>
     <row r="443">
@@ -25722,7 +25722,7 @@
     </row>
     <row r="449">
       <c r="A449" s="21" t="str">
-        <f>CONCATENATE("M 45 ",'Elimination Matches'!G381)</f>
+        <f>CONCATENATE("M 46 ",'Elimination Matches'!O381)</f>
       </c>
       <c r="B449" s="21" t="s">
         <v>242</v>
@@ -25738,10 +25738,10 @@
         <v>242</v>
       </c>
       <c r="G449" s="21" t="str">
-        <f>CONCATENATE("M 46 ",'Elimination Matches'!O381)</f>
+        <f>CONCATENATE("M 45 ",'Elimination Matches'!G381)</f>
       </c>
       <c r="I449" s="21" t="str">
-        <f>CONCATENATE("M 47 ",'Elimination Matches'!G397)</f>
+        <f>CONCATENATE("M 48 ",'Elimination Matches'!O397)</f>
       </c>
       <c r="J449" s="21" t="s">
         <v>242</v>
@@ -25757,7 +25757,7 @@
         <v>242</v>
       </c>
       <c r="O449" s="21" t="str">
-        <f>CONCATENATE("M 48 ",'Elimination Matches'!O397)</f>
+        <f>CONCATENATE("M 47 ",'Elimination Matches'!G397)</f>
       </c>
     </row>
     <row r="450">
@@ -25825,28 +25825,28 @@
       <c r="O456" s="20"/>
     </row>
     <row r="457">
-      <c r="A457" s="23" t="s">
+      <c r="A457" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D457" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G457" s="24" t="s">
+      <c r="G457" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I457" s="23" t="s">
+      <c r="I457" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L457" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O457" s="24" t="s">
+      <c r="O457" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="21" t="str">
-        <f>CONCATENATE("M 49 ",'Elimination Matches'!G413)</f>
+        <f>CONCATENATE("M 50 ",'Elimination Matches'!O413)</f>
       </c>
       <c r="B458" s="21"/>
       <c r="C458" s="21"/>
@@ -25854,10 +25854,10 @@
       <c r="E458" s="21"/>
       <c r="F458" s="21"/>
       <c r="G458" s="21" t="str">
-        <f>CONCATENATE("M 50 ",'Elimination Matches'!O413)</f>
+        <f>CONCATENATE("M 49 ",'Elimination Matches'!G413)</f>
       </c>
       <c r="I458" s="21" t="str">
-        <f>CONCATENATE("M 51 ",'Elimination Matches'!G429)</f>
+        <f>CONCATENATE("M 52 ",'Elimination Matches'!O429)</f>
       </c>
       <c r="J458" s="21"/>
       <c r="K458" s="21"/>
@@ -25865,7 +25865,7 @@
       <c r="M458" s="21"/>
       <c r="N458" s="21"/>
       <c r="O458" s="21" t="str">
-        <f>CONCATENATE("M 52 ",'Elimination Matches'!O429)</f>
+        <f>CONCATENATE("M 51 ",'Elimination Matches'!G429)</f>
       </c>
     </row>
     <row r="459">
@@ -25990,7 +25990,7 @@
     </row>
     <row r="465">
       <c r="A465" s="21" t="str">
-        <f>CONCATENATE("M 49 ",'Elimination Matches'!G413)</f>
+        <f>CONCATENATE("M 50 ",'Elimination Matches'!O413)</f>
       </c>
       <c r="B465" s="21" t="s">
         <v>242</v>
@@ -26006,10 +26006,10 @@
         <v>242</v>
       </c>
       <c r="G465" s="21" t="str">
-        <f>CONCATENATE("M 50 ",'Elimination Matches'!O413)</f>
+        <f>CONCATENATE("M 49 ",'Elimination Matches'!G413)</f>
       </c>
       <c r="I465" s="21" t="str">
-        <f>CONCATENATE("M 51 ",'Elimination Matches'!G429)</f>
+        <f>CONCATENATE("M 52 ",'Elimination Matches'!O429)</f>
       </c>
       <c r="J465" s="21" t="s">
         <v>242</v>
@@ -26025,7 +26025,7 @@
         <v>242</v>
       </c>
       <c r="O465" s="21" t="str">
-        <f>CONCATENATE("M 52 ",'Elimination Matches'!O429)</f>
+        <f>CONCATENATE("M 51 ",'Elimination Matches'!G429)</f>
       </c>
     </row>
     <row r="466">
@@ -26112,28 +26112,28 @@
       <c r="O479" s="20"/>
     </row>
     <row r="480">
-      <c r="A480" s="23" t="s">
+      <c r="A480" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D480" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G480" s="24" t="s">
+      <c r="G480" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="I480" s="23" t="s">
+      <c r="I480" s="24" t="s">
         <v>239</v>
       </c>
       <c r="L480" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="O480" s="24" t="s">
+      <c r="O480" s="23" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="21" t="str">
-        <f>CONCATENATE("M 53 ",'Elimination Matches'!G452)</f>
+        <f>CONCATENATE("M 54 ",'Elimination Matches'!O452)</f>
       </c>
       <c r="B481" s="21"/>
       <c r="C481" s="21"/>
@@ -26141,10 +26141,10 @@
       <c r="E481" s="21"/>
       <c r="F481" s="21"/>
       <c r="G481" s="21" t="str">
-        <f>CONCATENATE("M 54 ",'Elimination Matches'!O452)</f>
+        <f>CONCATENATE("M 53 ",'Elimination Matches'!G452)</f>
       </c>
       <c r="I481" s="21" t="str">
-        <f>CONCATENATE("M 55 ",'Elimination Matches'!G468)</f>
+        <f>CONCATENATE("M 56 ",'Elimination Matches'!O468)</f>
       </c>
       <c r="J481" s="21"/>
       <c r="K481" s="21"/>
@@ -26152,7 +26152,7 @@
       <c r="M481" s="21"/>
       <c r="N481" s="21"/>
       <c r="O481" s="21" t="str">
-        <f>CONCATENATE("M 56 ",'Elimination Matches'!O468)</f>
+        <f>CONCATENATE("M 55 ",'Elimination Matches'!G468)</f>
       </c>
     </row>
     <row r="482">
@@ -26277,7 +26277,7 @@
     </row>
     <row r="488">
       <c r="A488" s="21" t="str">
-        <f>CONCATENATE("M 53 ",'Elimination Matches'!G452)</f>
+        <f>CONCATENATE("M 54 ",'Elimination Matches'!O452)</f>
       </c>
       <c r="B488" s="21" t="s">
         <v>242</v>
@@ -26293,10 +26293,10 @@
         <v>242</v>
       </c>
       <c r="G488" s="21" t="str">
-        <f>CONCATENATE("M 54 ",'Elimination Matches'!O452)</f>
+        <f>CONCATENATE("M 53 ",'Elimination Matches'!G452)</f>
       </c>
       <c r="I488" s="21" t="str">
-        <f>CONCATENATE("M 55 ",'Elimination Matches'!G468)</f>
+        <f>CONCATENATE("M 56 ",'Elimination Matches'!O468)</f>
       </c>
       <c r="J488" s="21" t="s">
         <v>242</v>
@@ -26312,7 +26312,7 @@
         <v>242</v>
       </c>
       <c r="O488" s="21" t="str">
-        <f>CONCATENATE("M 56 ",'Elimination Matches'!O468)</f>
+        <f>CONCATENATE("M 55 ",'Elimination Matches'!G468)</f>
       </c>
     </row>
     <row r="489">
@@ -26390,13 +26390,13 @@
       <c r="G502" s="20"/>
     </row>
     <row r="503">
-      <c r="A503" s="23" t="s">
+      <c r="A503" s="24" t="s">
         <v>239</v>
       </c>
       <c r="D503" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G503" s="24" t="s">
+      <c r="G503" s="23" t="s">
         <v>241</v>
       </c>
     </row>

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -1825,11 +1825,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3132,7 +3136,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3140,7 +3145,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3525,7 +3530,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -26128,7 +26133,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -26518,7 +26523,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -12,17 +12,19 @@
     <sheet name="Pool Draw" sheetId="3" r:id="rId5"/>
     <sheet name="Pool Matches" sheetId="4" r:id="rId6"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
     <sheet name="Tree 3" sheetId="10" r:id="rId13"/>
     <sheet name="Tree 4" sheetId="11" r:id="rId14"/>
-    <sheet name="Tags" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print A" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print B" sheetId="13" r:id="rId16"/>
+    <sheet name="Tags" sheetId="14" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$66</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$614</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$91</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
+    <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$511</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
   <si>
     <t>Number of pools</t>
   </si>
@@ -1223,10 +1225,13 @@
     <t>Round 4 - Match 56</t>
   </si>
   <si>
-    <t>Round 5 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 6 - Match 0</t>
+    <t>Round 5 - Match 57</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 58</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 59</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -3892,6 +3897,798 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D27</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D28</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D29</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D30</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D31</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D32</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D33</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D34</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D35</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D36</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D37</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D38</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D39</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D40</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D41</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D42</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D43</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D44</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D45</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D46</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B45" s="27" t="str">
+        <f>data!D47</f>
+      </c>
+    </row>
+    <row r="46" ht="270" customHeight="true">
+      <c r="A46" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="B46" s="27" t="str">
+        <f>data!D48</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D49</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D50</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D51</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D52</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D53</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D54</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D55</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D56</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D57</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D58</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D59</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D60</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D61</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D62</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D63</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D64</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D65</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D66</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D67</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D68</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D69</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D70</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D71</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D72</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D73</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D74</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D75</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D76</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D77</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D78</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D79</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D80</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D81</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D82</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D83</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D84</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D85</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D86</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D87</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D88</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D89</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D90</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D91</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D92</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="26" t="s">
+        <v>338</v>
+      </c>
+      <c r="B45" s="27" t="str">
+        <f>data!D93</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
@@ -5105,7 +5902,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -5116,7 +5913,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
@@ -5126,7 +5923,7 @@
     </row>
     <row r="15">
       <c r="E15" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
@@ -5136,7 +5933,7 @@
     </row>
     <row r="16">
       <c r="E16" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
@@ -5146,7 +5943,7 @@
     </row>
     <row r="17">
       <c r="E17" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -5156,7 +5953,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -5166,7 +5963,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -24863,7 +25660,7 @@
       <c r="F470" s="13"/>
       <c r="G470" s="13"/>
       <c r="I470" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J470" s="13"/>
       <c r="K470" s="13"/>
@@ -25122,7 +25919,7 @@
     </row>
     <row r="491">
       <c r="A491" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B491" s="13"/>
       <c r="C491" s="13"/>
@@ -25144,7 +25941,7 @@
     </row>
     <row r="493">
       <c r="A493" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O482)</f>
+        <f>CONCATENATE("M 58 ",O482)</f>
       </c>
       <c r="B493" s="14"/>
       <c r="C493" s="14"/>
@@ -25152,7 +25949,7 @@
       <c r="E493" s="14"/>
       <c r="F493" s="14"/>
       <c r="G493" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O482)</f>
+        <f>CONCATENATE("M 57 ",G482)</f>
       </c>
     </row>
     <row r="494">
@@ -25222,7 +26019,7 @@
     </row>
     <row r="500">
       <c r="A500" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O482)</f>
+        <f>CONCATENATE("M 58 ",O482)</f>
       </c>
       <c r="B500" s="14" t="s">
         <v>241</v>
@@ -25238,7 +26035,7 @@
         <v>241</v>
       </c>
       <c r="G500" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O482)</f>
+        <f>CONCATENATE("M 57 ",G482)</f>
       </c>
     </row>
     <row r="501">
@@ -25354,781 +26151,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="B1" s="27" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="27" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="B17" s="27" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="B18" s="27" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="B19" s="27" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="B20" s="27" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="B21" s="27" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="B22" s="27" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-    <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="B25" s="27" t="str">
-        <f>data!D27</f>
-      </c>
-    </row>
-    <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="B26" s="27" t="str">
-        <f>data!D28</f>
-      </c>
-    </row>
-    <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="B27" s="27" t="str">
-        <f>data!D29</f>
-      </c>
-    </row>
-    <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="B28" s="27" t="str">
-        <f>data!D30</f>
-      </c>
-    </row>
-    <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="B29" s="27" t="str">
-        <f>data!D31</f>
-      </c>
-    </row>
-    <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B30" s="27" t="str">
-        <f>data!D32</f>
-      </c>
-    </row>
-    <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="B31" s="27" t="str">
-        <f>data!D33</f>
-      </c>
-    </row>
-    <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="B32" s="27" t="str">
-        <f>data!D34</f>
-      </c>
-    </row>
-    <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="B33" s="27" t="str">
-        <f>data!D35</f>
-      </c>
-    </row>
-    <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="B34" s="27" t="str">
-        <f>data!D36</f>
-      </c>
-    </row>
-    <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="B35" s="27" t="str">
-        <f>data!D37</f>
-      </c>
-    </row>
-    <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="B36" s="27" t="str">
-        <f>data!D38</f>
-      </c>
-    </row>
-    <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="B37" s="27" t="str">
-        <f>data!D39</f>
-      </c>
-    </row>
-    <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="B38" s="27" t="str">
-        <f>data!D40</f>
-      </c>
-    </row>
-    <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="B39" s="27" t="str">
-        <f>data!D41</f>
-      </c>
-    </row>
-    <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="B40" s="27" t="str">
-        <f>data!D42</f>
-      </c>
-    </row>
-    <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="B41" s="27" t="str">
-        <f>data!D43</f>
-      </c>
-    </row>
-    <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="B42" s="27" t="str">
-        <f>data!D44</f>
-      </c>
-    </row>
-    <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" s="27" t="str">
-        <f>data!D45</f>
-      </c>
-    </row>
-    <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="B44" s="27" t="str">
-        <f>data!D46</f>
-      </c>
-    </row>
-    <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="B45" s="27" t="str">
-        <f>data!D47</f>
-      </c>
-    </row>
-    <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="B46" s="27" t="str">
-        <f>data!D48</f>
-      </c>
-    </row>
-    <row r="47" ht="270" customHeight="true">
-      <c r="A47" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="B47" s="27" t="str">
-        <f>data!D49</f>
-      </c>
-    </row>
-    <row r="48" ht="270" customHeight="true">
-      <c r="A48" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="B48" s="27" t="str">
-        <f>data!D50</f>
-      </c>
-    </row>
-    <row r="49" ht="270" customHeight="true">
-      <c r="A49" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="B49" s="27" t="str">
-        <f>data!D51</f>
-      </c>
-    </row>
-    <row r="50" ht="270" customHeight="true">
-      <c r="A50" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="B50" s="27" t="str">
-        <f>data!D52</f>
-      </c>
-    </row>
-    <row r="51" ht="270" customHeight="true">
-      <c r="A51" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="B51" s="27" t="str">
-        <f>data!D53</f>
-      </c>
-    </row>
-    <row r="52" ht="270" customHeight="true">
-      <c r="A52" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="B52" s="27" t="str">
-        <f>data!D54</f>
-      </c>
-    </row>
-    <row r="53" ht="270" customHeight="true">
-      <c r="A53" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B53" s="27" t="str">
-        <f>data!D55</f>
-      </c>
-    </row>
-    <row r="54" ht="270" customHeight="true">
-      <c r="A54" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="B54" s="27" t="str">
-        <f>data!D56</f>
-      </c>
-    </row>
-    <row r="55" ht="270" customHeight="true">
-      <c r="A55" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B55" s="27" t="str">
-        <f>data!D57</f>
-      </c>
-    </row>
-    <row r="56" ht="270" customHeight="true">
-      <c r="A56" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="B56" s="27" t="str">
-        <f>data!D58</f>
-      </c>
-    </row>
-    <row r="57" ht="270" customHeight="true">
-      <c r="A57" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="B57" s="27" t="str">
-        <f>data!D59</f>
-      </c>
-    </row>
-    <row r="58" ht="270" customHeight="true">
-      <c r="A58" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="B58" s="27" t="str">
-        <f>data!D60</f>
-      </c>
-    </row>
-    <row r="59" ht="270" customHeight="true">
-      <c r="A59" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="B59" s="27" t="str">
-        <f>data!D61</f>
-      </c>
-    </row>
-    <row r="60" ht="270" customHeight="true">
-      <c r="A60" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="B60" s="27" t="str">
-        <f>data!D62</f>
-      </c>
-    </row>
-    <row r="61" ht="270" customHeight="true">
-      <c r="A61" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="B61" s="27" t="str">
-        <f>data!D63</f>
-      </c>
-    </row>
-    <row r="62" ht="270" customHeight="true">
-      <c r="A62" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="B62" s="27" t="str">
-        <f>data!D64</f>
-      </c>
-    </row>
-    <row r="63" ht="270" customHeight="true">
-      <c r="A63" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="B63" s="27" t="str">
-        <f>data!D65</f>
-      </c>
-    </row>
-    <row r="64" ht="270" customHeight="true">
-      <c r="A64" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="B64" s="27" t="str">
-        <f>data!D66</f>
-      </c>
-    </row>
-    <row r="65" ht="270" customHeight="true">
-      <c r="A65" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="B65" s="27" t="str">
-        <f>data!D67</f>
-      </c>
-    </row>
-    <row r="66" ht="270" customHeight="true">
-      <c r="A66" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="B66" s="27" t="str">
-        <f>data!D68</f>
-      </c>
-    </row>
-    <row r="67" ht="270" customHeight="true">
-      <c r="A67" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="B67" s="27" t="str">
-        <f>data!D69</f>
-      </c>
-    </row>
-    <row r="68" ht="270" customHeight="true">
-      <c r="A68" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="B68" s="27" t="str">
-        <f>data!D70</f>
-      </c>
-    </row>
-    <row r="69" ht="270" customHeight="true">
-      <c r="A69" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="B69" s="27" t="str">
-        <f>data!D71</f>
-      </c>
-    </row>
-    <row r="70" ht="270" customHeight="true">
-      <c r="A70" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="B70" s="27" t="str">
-        <f>data!D72</f>
-      </c>
-    </row>
-    <row r="71" ht="270" customHeight="true">
-      <c r="A71" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="B71" s="27" t="str">
-        <f>data!D73</f>
-      </c>
-    </row>
-    <row r="72" ht="270" customHeight="true">
-      <c r="A72" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="B72" s="27" t="str">
-        <f>data!D74</f>
-      </c>
-    </row>
-    <row r="73" ht="270" customHeight="true">
-      <c r="A73" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="B73" s="27" t="str">
-        <f>data!D75</f>
-      </c>
-    </row>
-    <row r="74" ht="270" customHeight="true">
-      <c r="A74" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="B74" s="27" t="str">
-        <f>data!D76</f>
-      </c>
-    </row>
-    <row r="75" ht="270" customHeight="true">
-      <c r="A75" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="B75" s="27" t="str">
-        <f>data!D77</f>
-      </c>
-    </row>
-    <row r="76" ht="270" customHeight="true">
-      <c r="A76" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="B76" s="27" t="str">
-        <f>data!D78</f>
-      </c>
-    </row>
-    <row r="77" ht="270" customHeight="true">
-      <c r="A77" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="B77" s="27" t="str">
-        <f>data!D79</f>
-      </c>
-    </row>
-    <row r="78" ht="270" customHeight="true">
-      <c r="A78" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="B78" s="27" t="str">
-        <f>data!D80</f>
-      </c>
-    </row>
-    <row r="79" ht="270" customHeight="true">
-      <c r="A79" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="B79" s="27" t="str">
-        <f>data!D81</f>
-      </c>
-    </row>
-    <row r="80" ht="270" customHeight="true">
-      <c r="A80" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="B80" s="27" t="str">
-        <f>data!D82</f>
-      </c>
-    </row>
-    <row r="81" ht="270" customHeight="true">
-      <c r="A81" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="B81" s="27" t="str">
-        <f>data!D83</f>
-      </c>
-    </row>
-    <row r="82" ht="270" customHeight="true">
-      <c r="A82" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="B82" s="27" t="str">
-        <f>data!D84</f>
-      </c>
-    </row>
-    <row r="83" ht="270" customHeight="true">
-      <c r="A83" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B83" s="27" t="str">
-        <f>data!D85</f>
-      </c>
-    </row>
-    <row r="84" ht="270" customHeight="true">
-      <c r="A84" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B84" s="27" t="str">
-        <f>data!D86</f>
-      </c>
-    </row>
-    <row r="85" ht="270" customHeight="true">
-      <c r="A85" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="B85" s="27" t="str">
-        <f>data!D87</f>
-      </c>
-    </row>
-    <row r="86" ht="270" customHeight="true">
-      <c r="A86" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="B86" s="27" t="str">
-        <f>data!D88</f>
-      </c>
-    </row>
-    <row r="87" ht="270" customHeight="true">
-      <c r="A87" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="B87" s="27" t="str">
-        <f>data!D89</f>
-      </c>
-    </row>
-    <row r="88" ht="270" customHeight="true">
-      <c r="A88" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B88" s="27" t="str">
-        <f>data!D90</f>
-      </c>
-    </row>
-    <row r="89" ht="270" customHeight="true">
-      <c r="A89" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="B89" s="27" t="str">
-        <f>data!D91</f>
-      </c>
-    </row>
-    <row r="90" ht="270" customHeight="true">
-      <c r="A90" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="B90" s="27" t="str">
-        <f>data!D92</f>
-      </c>
-    </row>
-    <row r="91" ht="270" customHeight="true">
-      <c r="A91" s="26" t="s">
-        <v>338</v>
-      </c>
-      <c r="B91" s="27" t="str">
-        <f>data!D93</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="30" manualBreakCount="30">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-    <brk id="27" max="16383" man="true"/>
-    <brk id="30" max="16383" man="true"/>
-    <brk id="33" max="16383" man="true"/>
-    <brk id="36" max="16383" man="true"/>
-    <brk id="39" max="16383" man="true"/>
-    <brk id="42" max="16383" man="true"/>
-    <brk id="45" max="16383" man="true"/>
-    <brk id="48" max="16383" man="true"/>
-    <brk id="51" max="16383" man="true"/>
-    <brk id="54" max="16383" man="true"/>
-    <brk id="57" max="16383" man="true"/>
-    <brk id="60" max="16383" man="true"/>
-    <brk id="63" max="16383" man="true"/>
-    <brk id="66" max="16383" man="true"/>
-    <brk id="69" max="16383" man="true"/>
-    <brk id="72" max="16383" man="true"/>
-    <brk id="75" max="16383" man="true"/>
-    <brk id="78" max="16383" man="true"/>
-    <brk id="81" max="16383" man="true"/>
-    <brk id="84" max="16383" man="true"/>
-    <brk id="87" max="16383" man="true"/>
-    <brk id="90" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -3227,7 +3227,7 @@
         <f>"2. " &amp; data!$B$50</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G96)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G93)</f>
       </c>
     </row>
     <row r="7">
@@ -3248,7 +3248,7 @@
         <f>'data'!$A$54</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G51)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3271,7 +3271,7 @@
         <f>"2. " &amp; data!$B$53</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G140)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G137)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3288,7 +3288,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G182)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G179)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3310,7 +3310,7 @@
         <f>"1. " &amp; data!$B$55</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G226)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G223)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3335,7 +3335,7 @@
         <f>"3. " &amp; data!$B$57</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G268)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G265)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3355,7 +3355,7 @@
         <f>'data'!$A$60</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G312)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G309)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3374,7 +3374,7 @@
         <f>"2. " &amp; data!$B$59</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G354)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G351)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3391,7 +3391,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G398)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G395)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3413,7 +3413,7 @@
         <f>"1. " &amp; data!$B$61</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G440)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G437)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3438,7 +3438,7 @@
         <f>"3. " &amp; data!$B$63</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G484)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G481)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3458,7 +3458,7 @@
         <f>'data'!$A$66</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G526)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G523)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3477,7 +3477,7 @@
         <f>"2. " &amp; data!$B$65</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G570)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G567)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3498,7 +3498,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G612)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G609)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3518,7 +3518,7 @@
         <f>"1. " &amp; data!$B$67</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G656)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -3613,7 +3613,7 @@
         <f>"2. " &amp; data!$B$74</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O51)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O48)</f>
       </c>
     </row>
     <row r="7">
@@ -3634,7 +3634,7 @@
         <f>'data'!$A$78</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O139)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O136)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3657,7 +3657,7 @@
         <f>"2. " &amp; data!$B$77</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O97)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O94)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3674,7 +3674,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O225)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O222)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3696,7 +3696,7 @@
         <f>"1. " &amp; data!$B$79</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O183)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O180)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3721,7 +3721,7 @@
         <f>"3. " &amp; data!$B$81</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O311)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O308)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3741,7 +3741,7 @@
         <f>'data'!$A$84</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O269)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O266)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3760,7 +3760,7 @@
         <f>"2. " &amp; data!$B$83</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O397)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O394)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3777,7 +3777,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O355)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O352)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3799,7 +3799,7 @@
         <f>"1. " &amp; data!$B$85</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O483)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O480)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3824,7 +3824,7 @@
         <f>"3. " &amp; data!$B$87</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O441)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O438)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3844,7 +3844,7 @@
         <f>'data'!$A$90</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O569)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O566)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3863,7 +3863,7 @@
         <f>"2. " &amp; data!$B$89</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O527)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O524)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3884,7 +3884,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O655)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O652)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3904,7 +3904,7 @@
         <f>"1. " &amp; data!$B$91</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O613)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O610)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -20886,7 +20886,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G97)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G94)</f>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -20894,10 +20894,10 @@
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G139)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G136)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G140)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G137)</f>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -20905,7 +20905,7 @@
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G51)</f>
       </c>
     </row>
     <row r="5">
@@ -21030,7 +21030,7 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G97)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G94)</f>
       </c>
       <c r="B11" s="14" t="s">
         <v>246</v>
@@ -21046,10 +21046,10 @@
         <v>246</v>
       </c>
       <c r="G11" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G139)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G136)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G140)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G137)</f>
       </c>
       <c r="J11" s="14" t="s">
         <v>246</v>
@@ -21065,7 +21065,7 @@
         <v>246</v>
       </c>
       <c r="O11" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G51)</f>
       </c>
     </row>
     <row r="12">
@@ -21170,7 +21170,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G183)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G180)</f>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -21178,10 +21178,10 @@
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G225)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G222)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G226)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G223)</f>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
@@ -21189,7 +21189,7 @@
       <c r="M20" s="14"/>
       <c r="N20" s="14"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G182)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G179)</f>
       </c>
     </row>
     <row r="21">
@@ -21314,7 +21314,7 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G183)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G180)</f>
       </c>
       <c r="B27" s="14" t="s">
         <v>246</v>
@@ -21330,10 +21330,10 @@
         <v>246</v>
       </c>
       <c r="G27" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G225)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G222)</f>
       </c>
       <c r="I27" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G226)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G223)</f>
       </c>
       <c r="J27" s="14" t="s">
         <v>246</v>
@@ -21349,7 +21349,7 @@
         <v>246</v>
       </c>
       <c r="O27" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G182)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G179)</f>
       </c>
     </row>
     <row r="28">
@@ -21454,7 +21454,7 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G269)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G266)</f>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -21462,10 +21462,10 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G311)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G308)</f>
       </c>
       <c r="I36" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G312)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G309)</f>
       </c>
       <c r="J36" s="14"/>
       <c r="K36" s="14"/>
@@ -21473,7 +21473,7 @@
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G268)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G265)</f>
       </c>
     </row>
     <row r="37">
@@ -21598,7 +21598,7 @@
     </row>
     <row r="43">
       <c r="A43" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G269)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G266)</f>
       </c>
       <c r="B43" s="14" t="s">
         <v>246</v>
@@ -21614,10 +21614,10 @@
         <v>246</v>
       </c>
       <c r="G43" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G311)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G308)</f>
       </c>
       <c r="I43" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G312)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G309)</f>
       </c>
       <c r="J43" s="14" t="s">
         <v>246</v>
@@ -21633,7 +21633,7 @@
         <v>246</v>
       </c>
       <c r="O43" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G268)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G265)</f>
       </c>
     </row>
     <row r="44">
@@ -21738,7 +21738,7 @@
     </row>
     <row r="52">
       <c r="A52" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G355)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G352)</f>
       </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -21746,10 +21746,10 @@
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
       <c r="G52" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G397)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G394)</f>
       </c>
       <c r="I52" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G398)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G395)</f>
       </c>
       <c r="J52" s="14"/>
       <c r="K52" s="14"/>
@@ -21757,7 +21757,7 @@
       <c r="M52" s="14"/>
       <c r="N52" s="14"/>
       <c r="O52" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G354)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G351)</f>
       </c>
     </row>
     <row r="53">
@@ -21882,7 +21882,7 @@
     </row>
     <row r="59">
       <c r="A59" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G355)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G352)</f>
       </c>
       <c r="B59" s="14" t="s">
         <v>246</v>
@@ -21898,10 +21898,10 @@
         <v>246</v>
       </c>
       <c r="G59" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G397)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G394)</f>
       </c>
       <c r="I59" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G398)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G395)</f>
       </c>
       <c r="J59" s="14" t="s">
         <v>246</v>
@@ -21917,7 +21917,7 @@
         <v>246</v>
       </c>
       <c r="O59" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G354)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G351)</f>
       </c>
     </row>
     <row r="60">
@@ -22022,7 +22022,7 @@
     </row>
     <row r="68">
       <c r="A68" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G441)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G438)</f>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -22030,10 +22030,10 @@
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
       <c r="G68" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G483)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G480)</f>
       </c>
       <c r="I68" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G484)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G481)</f>
       </c>
       <c r="J68" s="14"/>
       <c r="K68" s="14"/>
@@ -22041,7 +22041,7 @@
       <c r="M68" s="14"/>
       <c r="N68" s="14"/>
       <c r="O68" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G440)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G437)</f>
       </c>
     </row>
     <row r="69">
@@ -22166,7 +22166,7 @@
     </row>
     <row r="75">
       <c r="A75" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G441)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G438)</f>
       </c>
       <c r="B75" s="14" t="s">
         <v>246</v>
@@ -22182,10 +22182,10 @@
         <v>246</v>
       </c>
       <c r="G75" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G483)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G480)</f>
       </c>
       <c r="I75" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G484)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G481)</f>
       </c>
       <c r="J75" s="14" t="s">
         <v>246</v>
@@ -22201,7 +22201,7 @@
         <v>246</v>
       </c>
       <c r="O75" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G440)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G437)</f>
       </c>
     </row>
     <row r="76">
@@ -22306,7 +22306,7 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G527)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G524)</f>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -22314,10 +22314,10 @@
       <c r="E84" s="14"/>
       <c r="F84" s="14"/>
       <c r="G84" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G569)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G566)</f>
       </c>
       <c r="I84" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G570)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G567)</f>
       </c>
       <c r="J84" s="14"/>
       <c r="K84" s="14"/>
@@ -22325,7 +22325,7 @@
       <c r="M84" s="14"/>
       <c r="N84" s="14"/>
       <c r="O84" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G526)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G523)</f>
       </c>
     </row>
     <row r="85">
@@ -22450,7 +22450,7 @@
     </row>
     <row r="91">
       <c r="A91" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G527)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G524)</f>
       </c>
       <c r="B91" s="14" t="s">
         <v>246</v>
@@ -22466,10 +22466,10 @@
         <v>246</v>
       </c>
       <c r="G91" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G569)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G566)</f>
       </c>
       <c r="I91" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G570)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G567)</f>
       </c>
       <c r="J91" s="14" t="s">
         <v>246</v>
@@ -22485,7 +22485,7 @@
         <v>246</v>
       </c>
       <c r="O91" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G526)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G523)</f>
       </c>
     </row>
     <row r="92">
@@ -22590,7 +22590,7 @@
     </row>
     <row r="100">
       <c r="A100" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G613)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G610)</f>
       </c>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -22598,10 +22598,10 @@
       <c r="E100" s="14"/>
       <c r="F100" s="14"/>
       <c r="G100" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G655)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
       </c>
       <c r="I100" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G656)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
       </c>
       <c r="J100" s="14"/>
       <c r="K100" s="14"/>
@@ -22609,7 +22609,7 @@
       <c r="M100" s="14"/>
       <c r="N100" s="14"/>
       <c r="O100" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G612)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G609)</f>
       </c>
     </row>
     <row r="101">
@@ -22734,7 +22734,7 @@
     </row>
     <row r="107">
       <c r="A107" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G613)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G610)</f>
       </c>
       <c r="B107" s="14" t="s">
         <v>246</v>
@@ -22750,10 +22750,10 @@
         <v>246</v>
       </c>
       <c r="G107" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G655)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
       </c>
       <c r="I107" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G656)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G653)</f>
       </c>
       <c r="J107" s="14" t="s">
         <v>246</v>
@@ -22769,7 +22769,7 @@
         <v>246</v>
       </c>
       <c r="O107" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G612)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G609)</f>
       </c>
     </row>
     <row r="108">
@@ -22874,7 +22874,7 @@
     </row>
     <row r="116">
       <c r="A116" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O140)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O137)</f>
       </c>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -22882,10 +22882,10 @@
       <c r="E116" s="14"/>
       <c r="F116" s="14"/>
       <c r="G116" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O49)</f>
       </c>
       <c r="I116" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O97)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O94)</f>
       </c>
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
@@ -22893,7 +22893,7 @@
       <c r="M116" s="14"/>
       <c r="N116" s="14"/>
       <c r="O116" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O139)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O136)</f>
       </c>
     </row>
     <row r="117">
@@ -23018,7 +23018,7 @@
     </row>
     <row r="123">
       <c r="A123" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O140)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O137)</f>
       </c>
       <c r="B123" s="14" t="s">
         <v>246</v>
@@ -23034,10 +23034,10 @@
         <v>246</v>
       </c>
       <c r="G123" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O49)</f>
       </c>
       <c r="I123" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O97)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O94)</f>
       </c>
       <c r="J123" s="14" t="s">
         <v>246</v>
@@ -23053,7 +23053,7 @@
         <v>246</v>
       </c>
       <c r="O123" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O139)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O136)</f>
       </c>
     </row>
     <row r="124">
@@ -23158,7 +23158,7 @@
     </row>
     <row r="132">
       <c r="A132" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O226)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -23166,10 +23166,10 @@
       <c r="E132" s="14"/>
       <c r="F132" s="14"/>
       <c r="G132" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O182)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O179)</f>
       </c>
       <c r="I132" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O183)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O180)</f>
       </c>
       <c r="J132" s="14"/>
       <c r="K132" s="14"/>
@@ -23177,7 +23177,7 @@
       <c r="M132" s="14"/>
       <c r="N132" s="14"/>
       <c r="O132" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O225)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O222)</f>
       </c>
     </row>
     <row r="133">
@@ -23302,7 +23302,7 @@
     </row>
     <row r="139">
       <c r="A139" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O226)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="B139" s="14" t="s">
         <v>246</v>
@@ -23318,10 +23318,10 @@
         <v>246</v>
       </c>
       <c r="G139" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O182)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O179)</f>
       </c>
       <c r="I139" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O183)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O180)</f>
       </c>
       <c r="J139" s="14" t="s">
         <v>246</v>
@@ -23337,7 +23337,7 @@
         <v>246</v>
       </c>
       <c r="O139" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O225)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O222)</f>
       </c>
     </row>
     <row r="140">
@@ -23442,7 +23442,7 @@
     </row>
     <row r="148">
       <c r="A148" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O312)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O309)</f>
       </c>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -23450,10 +23450,10 @@
       <c r="E148" s="14"/>
       <c r="F148" s="14"/>
       <c r="G148" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O268)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O265)</f>
       </c>
       <c r="I148" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O269)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O266)</f>
       </c>
       <c r="J148" s="14"/>
       <c r="K148" s="14"/>
@@ -23461,7 +23461,7 @@
       <c r="M148" s="14"/>
       <c r="N148" s="14"/>
       <c r="O148" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O311)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O308)</f>
       </c>
     </row>
     <row r="149">
@@ -23586,7 +23586,7 @@
     </row>
     <row r="155">
       <c r="A155" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O312)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O309)</f>
       </c>
       <c r="B155" s="14" t="s">
         <v>246</v>
@@ -23602,10 +23602,10 @@
         <v>246</v>
       </c>
       <c r="G155" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O268)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O265)</f>
       </c>
       <c r="I155" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O269)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O266)</f>
       </c>
       <c r="J155" s="14" t="s">
         <v>246</v>
@@ -23621,7 +23621,7 @@
         <v>246</v>
       </c>
       <c r="O155" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O311)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O308)</f>
       </c>
     </row>
     <row r="156">
@@ -23726,7 +23726,7 @@
     </row>
     <row r="164">
       <c r="A164" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O398)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O395)</f>
       </c>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -23734,10 +23734,10 @@
       <c r="E164" s="14"/>
       <c r="F164" s="14"/>
       <c r="G164" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O354)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O351)</f>
       </c>
       <c r="I164" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O355)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O352)</f>
       </c>
       <c r="J164" s="14"/>
       <c r="K164" s="14"/>
@@ -23745,7 +23745,7 @@
       <c r="M164" s="14"/>
       <c r="N164" s="14"/>
       <c r="O164" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O397)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O394)</f>
       </c>
     </row>
     <row r="165">
@@ -23870,7 +23870,7 @@
     </row>
     <row r="171">
       <c r="A171" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O398)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O395)</f>
       </c>
       <c r="B171" s="14" t="s">
         <v>246</v>
@@ -23886,10 +23886,10 @@
         <v>246</v>
       </c>
       <c r="G171" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O354)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O351)</f>
       </c>
       <c r="I171" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O355)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O352)</f>
       </c>
       <c r="J171" s="14" t="s">
         <v>246</v>
@@ -23905,7 +23905,7 @@
         <v>246</v>
       </c>
       <c r="O171" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O397)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O394)</f>
       </c>
     </row>
     <row r="172">
@@ -24010,7 +24010,7 @@
     </row>
     <row r="180">
       <c r="A180" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O484)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O481)</f>
       </c>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -24018,10 +24018,10 @@
       <c r="E180" s="14"/>
       <c r="F180" s="14"/>
       <c r="G180" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O440)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O437)</f>
       </c>
       <c r="I180" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O441)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O438)</f>
       </c>
       <c r="J180" s="14"/>
       <c r="K180" s="14"/>
@@ -24029,7 +24029,7 @@
       <c r="M180" s="14"/>
       <c r="N180" s="14"/>
       <c r="O180" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O483)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O480)</f>
       </c>
     </row>
     <row r="181">
@@ -24154,7 +24154,7 @@
     </row>
     <row r="187">
       <c r="A187" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O484)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O481)</f>
       </c>
       <c r="B187" s="14" t="s">
         <v>246</v>
@@ -24170,10 +24170,10 @@
         <v>246</v>
       </c>
       <c r="G187" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O440)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O437)</f>
       </c>
       <c r="I187" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O441)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O438)</f>
       </c>
       <c r="J187" s="14" t="s">
         <v>246</v>
@@ -24189,7 +24189,7 @@
         <v>246</v>
       </c>
       <c r="O187" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O483)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O480)</f>
       </c>
     </row>
     <row r="188">
@@ -24294,7 +24294,7 @@
     </row>
     <row r="196">
       <c r="A196" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O570)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O567)</f>
       </c>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -24302,10 +24302,10 @@
       <c r="E196" s="14"/>
       <c r="F196" s="14"/>
       <c r="G196" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O526)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O523)</f>
       </c>
       <c r="I196" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O527)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O524)</f>
       </c>
       <c r="J196" s="14"/>
       <c r="K196" s="14"/>
@@ -24313,7 +24313,7 @@
       <c r="M196" s="14"/>
       <c r="N196" s="14"/>
       <c r="O196" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O569)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O566)</f>
       </c>
     </row>
     <row r="197">
@@ -24438,7 +24438,7 @@
     </row>
     <row r="203">
       <c r="A203" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O570)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O567)</f>
       </c>
       <c r="B203" s="14" t="s">
         <v>246</v>
@@ -24454,10 +24454,10 @@
         <v>246</v>
       </c>
       <c r="G203" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O526)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O523)</f>
       </c>
       <c r="I203" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O527)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O524)</f>
       </c>
       <c r="J203" s="14" t="s">
         <v>246</v>
@@ -24473,7 +24473,7 @@
         <v>246</v>
       </c>
       <c r="O203" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O569)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O566)</f>
       </c>
     </row>
     <row r="204">
@@ -24578,7 +24578,7 @@
     </row>
     <row r="212">
       <c r="A212" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O656)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O653)</f>
       </c>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -24586,10 +24586,10 @@
       <c r="E212" s="14"/>
       <c r="F212" s="14"/>
       <c r="G212" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O612)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O609)</f>
       </c>
       <c r="I212" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O613)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O610)</f>
       </c>
       <c r="J212" s="14"/>
       <c r="K212" s="14"/>
@@ -24597,7 +24597,7 @@
       <c r="M212" s="14"/>
       <c r="N212" s="14"/>
       <c r="O212" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O655)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O652)</f>
       </c>
     </row>
     <row r="213">
@@ -24722,7 +24722,7 @@
     </row>
     <row r="219">
       <c r="A219" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O656)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O653)</f>
       </c>
       <c r="B219" s="14" t="s">
         <v>246</v>
@@ -24738,10 +24738,10 @@
         <v>246</v>
       </c>
       <c r="G219" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O612)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O609)</f>
       </c>
       <c r="I219" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O613)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O610)</f>
       </c>
       <c r="J219" s="14" t="s">
         <v>246</v>
@@ -24757,7 +24757,7 @@
         <v>246</v>
       </c>
       <c r="O219" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O655)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O652)</f>
       </c>
     </row>
     <row r="220">
@@ -24870,7 +24870,7 @@
       <c r="E233" s="14"/>
       <c r="F233" s="14"/>
       <c r="G233" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G54)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G50)</f>
       </c>
       <c r="I233" s="14" t="str">
         <f>CONCATENATE("M 15 ",O15)</f>
@@ -24881,7 +24881,7 @@
       <c r="M233" s="14"/>
       <c r="N233" s="14"/>
       <c r="O233" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G96)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G93)</f>
       </c>
     </row>
     <row r="234">
@@ -25022,7 +25022,7 @@
         <v>246</v>
       </c>
       <c r="G240" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G54)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G50)</f>
       </c>
       <c r="I240" s="14" t="str">
         <f>CONCATENATE("M 15 ",O15)</f>
@@ -25041,7 +25041,7 @@
         <v>246</v>
       </c>
       <c r="O240" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G96)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G93)</f>
       </c>
     </row>
     <row r="241">
@@ -26006,7 +26006,7 @@
       <c r="E297" s="14"/>
       <c r="F297" s="14"/>
       <c r="G297" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O96)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O93)</f>
       </c>
       <c r="I297" s="14" t="str">
         <f>CONCATENATE("M 22 ",O127)</f>
@@ -26017,7 +26017,7 @@
       <c r="M297" s="14"/>
       <c r="N297" s="14"/>
       <c r="O297" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O51)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O48)</f>
       </c>
     </row>
     <row r="298">
@@ -26158,7 +26158,7 @@
         <v>246</v>
       </c>
       <c r="G304" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O96)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O93)</f>
       </c>
       <c r="I304" s="14" t="str">
         <f>CONCATENATE("M 22 ",O127)</f>
@@ -26177,7 +26177,7 @@
         <v>246</v>
       </c>
       <c r="O304" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O51)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O48)</f>
       </c>
     </row>
     <row r="305">
@@ -29367,7 +29367,7 @@
         <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G54)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G50)</f>
       </c>
     </row>
     <row r="7">
@@ -29388,7 +29388,7 @@
     <row r="9">
       <c r="A9" s="22"/>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G139)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G136)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -29411,7 +29411,7 @@
         <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G97)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G94)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -29430,7 +29430,7 @@
         <f>"3. " &amp; data!$B$9</f>
       </c>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G225)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G222)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -29450,7 +29450,7 @@
         <f>'data'!$A$12</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G183)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G180)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -29475,7 +29475,7 @@
         <f>"2. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G311)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G308)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -29495,7 +29495,7 @@
     <row r="19">
       <c r="A19" s="22"/>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G269)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G266)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -29514,7 +29514,7 @@
         <f>"1. " &amp; data!$B$13</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G397)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G394)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -29533,7 +29533,7 @@
         <f>"3. " &amp; data!$B$15</f>
       </c>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G355)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G352)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -29553,7 +29553,7 @@
         <f>'data'!$A$18</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G483)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G480)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -29578,7 +29578,7 @@
         <f>"2. " &amp; data!$B$17</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G441)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G438)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -29598,7 +29598,7 @@
     <row r="29">
       <c r="A29" s="22"/>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G569)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G566)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -29617,7 +29617,7 @@
         <f>"1. " &amp; data!$B$19</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G527)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G524)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -29640,7 +29640,7 @@
         <f>"3. " &amp; data!$B$21</f>
       </c>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G655)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G652)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -29658,7 +29658,7 @@
         <f>'data'!$A$24</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G613)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G610)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -29758,7 +29758,7 @@
         <f>"2. " &amp; data!$B$29</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O96)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O93)</f>
       </c>
     </row>
     <row r="7">
@@ -29779,7 +29779,7 @@
         <f>'data'!$A$33</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O49)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -29802,7 +29802,7 @@
         <f>"2. " &amp; data!$B$32</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O140)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O137)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -29819,7 +29819,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O182)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O179)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -29841,7 +29841,7 @@
         <f>"1. " &amp; data!$B$34</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O226)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -29866,7 +29866,7 @@
         <f>"3. " &amp; data!$B$36</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O268)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O265)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -29886,7 +29886,7 @@
         <f>'data'!$A$39</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O312)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O309)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -29905,7 +29905,7 @@
         <f>"2. " &amp; data!$B$38</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O354)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O351)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -29922,7 +29922,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O398)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O395)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -29944,7 +29944,7 @@
         <f>"1. " &amp; data!$B$40</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O440)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O437)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -29969,7 +29969,7 @@
         <f>"3. " &amp; data!$B$42</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O484)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O481)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -29989,7 +29989,7 @@
         <f>'data'!$A$45</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O526)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O523)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -30008,7 +30008,7 @@
         <f>"2. " &amp; data!$B$44</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O570)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O567)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -30029,7 +30029,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O612)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O609)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -30049,7 +30049,7 @@
         <f>"1. " &amp; data!$B$46</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O656)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O653)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -7331,10 +7331,10 @@
         <f>RANK(AC37,$AC$37:$AC$39)+COUNTIF($AC$36:AC36,AC37)</f>
       </c>
       <c r="U37" t="str">
-        <f>=(B37*1000000000)-(C37*10000000)+(D37*100000)+(B43*1000)-(C43*100)+(D43*10)+(E43*1)-(F43*0.01)</f>
+        <f>(B37*1000000000)-(C37*10000000)+(D37*100000)+(B43*1000)-(C43*100)+(D43*10)+(E43*1)-(F43*0.01)</f>
       </c>
       <c r="AC37" t="str">
-        <f>=(J37*1000000000)-(K37*10000000)+(L37*100000)+(J42*1000)-(K42*100)+(L42*10)+(M42*1)-(N42*0.01)</f>
+        <f>(J37*1000000000)-(K37*10000000)+(L37*100000)+(J42*1000)-(K42*100)+(L42*10)+(M42*1)-(N42*0.01)</f>
       </c>
     </row>
     <row r="38">
@@ -7369,10 +7369,10 @@
         <f>RANK(AC38,$AC$37:$AC$39)+COUNTIF($AC$36:AC37,AC38)</f>
       </c>
       <c r="U38" t="str">
-        <f>=(B38*1000000000)-(C38*10000000)+(D38*100000)+(B44*1000)-(C44*100)+(D44*10)+(E44*1)-(F44*0.01)</f>
+        <f>(B38*1000000000)-(C38*10000000)+(D38*100000)+(B44*1000)-(C44*100)+(D44*10)+(E44*1)-(F44*0.01)</f>
       </c>
       <c r="AC38" t="str">
-        <f>=(J38*1000000000)-(K38*10000000)+(L38*100000)+(J43*1000)-(K43*100)+(L43*10)+(M43*1)-(N43*0.01)</f>
+        <f>(J38*1000000000)-(K38*10000000)+(L38*100000)+(J43*1000)-(K43*100)+(L43*10)+(M43*1)-(N43*0.01)</f>
       </c>
     </row>
     <row r="39">
@@ -7407,10 +7407,10 @@
         <f>RANK(AC39,$AC$37:$AC$39)+COUNTIF($AC$36:AC38,AC39)</f>
       </c>
       <c r="U39" t="str">
-        <f>=(B39*1000000000)-(C39*10000000)+(D39*100000)+(B45*1000)-(C45*100)+(D45*10)+(E45*1)-(F45*0.01)</f>
+        <f>(B39*1000000000)-(C39*10000000)+(D39*100000)+(B45*1000)-(C45*100)+(D45*10)+(E45*1)-(F45*0.01)</f>
       </c>
       <c r="AC39" t="str">
-        <f>=(J39*1000000000)-(K39*10000000)+(L39*100000)+(J44*1000)-(K44*100)+(L44*10)+(M44*1)-(N44*0.01)</f>
+        <f>(J39*1000000000)-(K39*10000000)+(L39*100000)+(J44*1000)-(K44*100)+(L44*10)+(M44*1)-(N44*0.01)</f>
       </c>
     </row>
     <row r="40">
@@ -7430,7 +7430,7 @@
         <f>RANK(U40,$U$37:$U$40)+COUNTIF($U$36:U39,U40)</f>
       </c>
       <c r="U40" t="str">
-        <f>=(B40*1000000000)-(C40*10000000)+(D40*100000)+(B46*1000)-(C46*100)+(D46*10)+(E46*1)-(F46*0.01)</f>
+        <f>(B40*1000000000)-(C40*10000000)+(D40*100000)+(B46*1000)-(C46*100)+(D46*10)+(E46*1)-(F46*0.01)</f>
       </c>
     </row>
     <row r="41">
@@ -8319,10 +8319,10 @@
         <f>RANK(AC82,$AC$82:$AC$84)+COUNTIF($AC$81:AC81,AC82)</f>
       </c>
       <c r="U82" t="str">
-        <f>=(B82*1000000000)-(C82*10000000)+(D82*100000)+(B87*1000)-(C87*100)+(D87*10)+(E87*1)-(F87*0.01)</f>
+        <f>(B82*1000000000)-(C82*10000000)+(D82*100000)+(B87*1000)-(C87*100)+(D87*10)+(E87*1)-(F87*0.01)</f>
       </c>
       <c r="AC82" t="str">
-        <f>=(J82*1000000000)-(K82*10000000)+(L82*100000)+(J87*1000)-(K87*100)+(L87*10)+(M87*1)-(N87*0.01)</f>
+        <f>(J82*1000000000)-(K82*10000000)+(L82*100000)+(J87*1000)-(K87*100)+(L87*10)+(M87*1)-(N87*0.01)</f>
       </c>
     </row>
     <row r="83">
@@ -8357,10 +8357,10 @@
         <f>RANK(AC83,$AC$82:$AC$84)+COUNTIF($AC$81:AC82,AC83)</f>
       </c>
       <c r="U83" t="str">
-        <f>=(B83*1000000000)-(C83*10000000)+(D83*100000)+(B88*1000)-(C88*100)+(D88*10)+(E88*1)-(F88*0.01)</f>
+        <f>(B83*1000000000)-(C83*10000000)+(D83*100000)+(B88*1000)-(C88*100)+(D88*10)+(E88*1)-(F88*0.01)</f>
       </c>
       <c r="AC83" t="str">
-        <f>=(J83*1000000000)-(K83*10000000)+(L83*100000)+(J88*1000)-(K88*100)+(L88*10)+(M88*1)-(N88*0.01)</f>
+        <f>(J83*1000000000)-(K83*10000000)+(L83*100000)+(J88*1000)-(K88*100)+(L88*10)+(M88*1)-(N88*0.01)</f>
       </c>
     </row>
     <row r="84">
@@ -8395,10 +8395,10 @@
         <f>RANK(AC84,$AC$82:$AC$84)+COUNTIF($AC$81:AC83,AC84)</f>
       </c>
       <c r="U84" t="str">
-        <f>=(B84*1000000000)-(C84*10000000)+(D84*100000)+(B89*1000)-(C89*100)+(D89*10)+(E89*1)-(F89*0.01)</f>
+        <f>(B84*1000000000)-(C84*10000000)+(D84*100000)+(B89*1000)-(C89*100)+(D89*10)+(E89*1)-(F89*0.01)</f>
       </c>
       <c r="AC84" t="str">
-        <f>=(J84*1000000000)-(K84*10000000)+(L84*100000)+(J89*1000)-(K89*100)+(L89*10)+(M89*1)-(N89*0.01)</f>
+        <f>(J84*1000000000)-(K84*10000000)+(L84*100000)+(J89*1000)-(K89*100)+(L89*10)+(M89*1)-(N89*0.01)</f>
       </c>
     </row>
     <row r="86">
@@ -9253,10 +9253,10 @@
         <f>RANK(AC125,$AC$125:$AC$127)+COUNTIF($AC$124:AC124,AC125)</f>
       </c>
       <c r="U125" t="str">
-        <f>=(B125*1000000000)-(C125*10000000)+(D125*100000)+(B130*1000)-(C130*100)+(D130*10)+(E130*1)-(F130*0.01)</f>
+        <f>(B125*1000000000)-(C125*10000000)+(D125*100000)+(B130*1000)-(C130*100)+(D130*10)+(E130*1)-(F130*0.01)</f>
       </c>
       <c r="AC125" t="str">
-        <f>=(J125*1000000000)-(K125*10000000)+(L125*100000)+(J130*1000)-(K130*100)+(L130*10)+(M130*1)-(N130*0.01)</f>
+        <f>(J125*1000000000)-(K125*10000000)+(L125*100000)+(J130*1000)-(K130*100)+(L130*10)+(M130*1)-(N130*0.01)</f>
       </c>
     </row>
     <row r="126">
@@ -9291,10 +9291,10 @@
         <f>RANK(AC126,$AC$125:$AC$127)+COUNTIF($AC$124:AC125,AC126)</f>
       </c>
       <c r="U126" t="str">
-        <f>=(B126*1000000000)-(C126*10000000)+(D126*100000)+(B131*1000)-(C131*100)+(D131*10)+(E131*1)-(F131*0.01)</f>
+        <f>(B126*1000000000)-(C126*10000000)+(D126*100000)+(B131*1000)-(C131*100)+(D131*10)+(E131*1)-(F131*0.01)</f>
       </c>
       <c r="AC126" t="str">
-        <f>=(J126*1000000000)-(K126*10000000)+(L126*100000)+(J131*1000)-(K131*100)+(L131*10)+(M131*1)-(N131*0.01)</f>
+        <f>(J126*1000000000)-(K126*10000000)+(L126*100000)+(J131*1000)-(K131*100)+(L131*10)+(M131*1)-(N131*0.01)</f>
       </c>
     </row>
     <row r="127">
@@ -9329,10 +9329,10 @@
         <f>RANK(AC127,$AC$125:$AC$127)+COUNTIF($AC$124:AC126,AC127)</f>
       </c>
       <c r="U127" t="str">
-        <f>=(B127*1000000000)-(C127*10000000)+(D127*100000)+(B132*1000)-(C132*100)+(D132*10)+(E132*1)-(F132*0.01)</f>
+        <f>(B127*1000000000)-(C127*10000000)+(D127*100000)+(B132*1000)-(C132*100)+(D132*10)+(E132*1)-(F132*0.01)</f>
       </c>
       <c r="AC127" t="str">
-        <f>=(J127*1000000000)-(K127*10000000)+(L127*100000)+(J132*1000)-(K132*100)+(L132*10)+(M132*1)-(N132*0.01)</f>
+        <f>(J127*1000000000)-(K127*10000000)+(L127*100000)+(J132*1000)-(K132*100)+(L132*10)+(M132*1)-(N132*0.01)</f>
       </c>
     </row>
     <row r="129">
@@ -10187,10 +10187,10 @@
         <f>RANK(AC168,$AC$168:$AC$170)+COUNTIF($AC$167:AC167,AC168)</f>
       </c>
       <c r="U168" t="str">
-        <f>=(B168*1000000000)-(C168*10000000)+(D168*100000)+(B173*1000)-(C173*100)+(D173*10)+(E173*1)-(F173*0.01)</f>
+        <f>(B168*1000000000)-(C168*10000000)+(D168*100000)+(B173*1000)-(C173*100)+(D173*10)+(E173*1)-(F173*0.01)</f>
       </c>
       <c r="AC168" t="str">
-        <f>=(J168*1000000000)-(K168*10000000)+(L168*100000)+(J173*1000)-(K173*100)+(L173*10)+(M173*1)-(N173*0.01)</f>
+        <f>(J168*1000000000)-(K168*10000000)+(L168*100000)+(J173*1000)-(K173*100)+(L173*10)+(M173*1)-(N173*0.01)</f>
       </c>
     </row>
     <row r="169">
@@ -10225,10 +10225,10 @@
         <f>RANK(AC169,$AC$168:$AC$170)+COUNTIF($AC$167:AC168,AC169)</f>
       </c>
       <c r="U169" t="str">
-        <f>=(B169*1000000000)-(C169*10000000)+(D169*100000)+(B174*1000)-(C174*100)+(D174*10)+(E174*1)-(F174*0.01)</f>
+        <f>(B169*1000000000)-(C169*10000000)+(D169*100000)+(B174*1000)-(C174*100)+(D174*10)+(E174*1)-(F174*0.01)</f>
       </c>
       <c r="AC169" t="str">
-        <f>=(J169*1000000000)-(K169*10000000)+(L169*100000)+(J174*1000)-(K174*100)+(L174*10)+(M174*1)-(N174*0.01)</f>
+        <f>(J169*1000000000)-(K169*10000000)+(L169*100000)+(J174*1000)-(K174*100)+(L174*10)+(M174*1)-(N174*0.01)</f>
       </c>
     </row>
     <row r="170">
@@ -10263,10 +10263,10 @@
         <f>RANK(AC170,$AC$168:$AC$170)+COUNTIF($AC$167:AC169,AC170)</f>
       </c>
       <c r="U170" t="str">
-        <f>=(B170*1000000000)-(C170*10000000)+(D170*100000)+(B175*1000)-(C175*100)+(D175*10)+(E175*1)-(F175*0.01)</f>
+        <f>(B170*1000000000)-(C170*10000000)+(D170*100000)+(B175*1000)-(C175*100)+(D175*10)+(E175*1)-(F175*0.01)</f>
       </c>
       <c r="AC170" t="str">
-        <f>=(J170*1000000000)-(K170*10000000)+(L170*100000)+(J175*1000)-(K175*100)+(L175*10)+(M175*1)-(N175*0.01)</f>
+        <f>(J170*1000000000)-(K170*10000000)+(L170*100000)+(J175*1000)-(K175*100)+(L175*10)+(M175*1)-(N175*0.01)</f>
       </c>
     </row>
     <row r="172">
@@ -11121,10 +11121,10 @@
         <f>RANK(AC211,$AC$211:$AC$213)+COUNTIF($AC$210:AC210,AC211)</f>
       </c>
       <c r="U211" t="str">
-        <f>=(B211*1000000000)-(C211*10000000)+(D211*100000)+(B216*1000)-(C216*100)+(D216*10)+(E216*1)-(F216*0.01)</f>
+        <f>(B211*1000000000)-(C211*10000000)+(D211*100000)+(B216*1000)-(C216*100)+(D216*10)+(E216*1)-(F216*0.01)</f>
       </c>
       <c r="AC211" t="str">
-        <f>=(J211*1000000000)-(K211*10000000)+(L211*100000)+(J216*1000)-(K216*100)+(L216*10)+(M216*1)-(N216*0.01)</f>
+        <f>(J211*1000000000)-(K211*10000000)+(L211*100000)+(J216*1000)-(K216*100)+(L216*10)+(M216*1)-(N216*0.01)</f>
       </c>
     </row>
     <row r="212">
@@ -11159,10 +11159,10 @@
         <f>RANK(AC212,$AC$211:$AC$213)+COUNTIF($AC$210:AC211,AC212)</f>
       </c>
       <c r="U212" t="str">
-        <f>=(B212*1000000000)-(C212*10000000)+(D212*100000)+(B217*1000)-(C217*100)+(D217*10)+(E217*1)-(F217*0.01)</f>
+        <f>(B212*1000000000)-(C212*10000000)+(D212*100000)+(B217*1000)-(C217*100)+(D217*10)+(E217*1)-(F217*0.01)</f>
       </c>
       <c r="AC212" t="str">
-        <f>=(J212*1000000000)-(K212*10000000)+(L212*100000)+(J217*1000)-(K217*100)+(L217*10)+(M217*1)-(N217*0.01)</f>
+        <f>(J212*1000000000)-(K212*10000000)+(L212*100000)+(J217*1000)-(K217*100)+(L217*10)+(M217*1)-(N217*0.01)</f>
       </c>
     </row>
     <row r="213">
@@ -11197,10 +11197,10 @@
         <f>RANK(AC213,$AC$211:$AC$213)+COUNTIF($AC$210:AC212,AC213)</f>
       </c>
       <c r="U213" t="str">
-        <f>=(B213*1000000000)-(C213*10000000)+(D213*100000)+(B218*1000)-(C218*100)+(D218*10)+(E218*1)-(F218*0.01)</f>
+        <f>(B213*1000000000)-(C213*10000000)+(D213*100000)+(B218*1000)-(C218*100)+(D218*10)+(E218*1)-(F218*0.01)</f>
       </c>
       <c r="AC213" t="str">
-        <f>=(J213*1000000000)-(K213*10000000)+(L213*100000)+(J218*1000)-(K218*100)+(L218*10)+(M218*1)-(N218*0.01)</f>
+        <f>(J213*1000000000)-(K213*10000000)+(L213*100000)+(J218*1000)-(K218*100)+(L218*10)+(M218*1)-(N218*0.01)</f>
       </c>
     </row>
     <row r="215">
@@ -12055,10 +12055,10 @@
         <f>RANK(AC254,$AC$254:$AC$256)+COUNTIF($AC$253:AC253,AC254)</f>
       </c>
       <c r="U254" t="str">
-        <f>=(B254*1000000000)-(C254*10000000)+(D254*100000)+(B259*1000)-(C259*100)+(D259*10)+(E259*1)-(F259*0.01)</f>
+        <f>(B254*1000000000)-(C254*10000000)+(D254*100000)+(B259*1000)-(C259*100)+(D259*10)+(E259*1)-(F259*0.01)</f>
       </c>
       <c r="AC254" t="str">
-        <f>=(J254*1000000000)-(K254*10000000)+(L254*100000)+(J259*1000)-(K259*100)+(L259*10)+(M259*1)-(N259*0.01)</f>
+        <f>(J254*1000000000)-(K254*10000000)+(L254*100000)+(J259*1000)-(K259*100)+(L259*10)+(M259*1)-(N259*0.01)</f>
       </c>
     </row>
     <row r="255">
@@ -12093,10 +12093,10 @@
         <f>RANK(AC255,$AC$254:$AC$256)+COUNTIF($AC$253:AC254,AC255)</f>
       </c>
       <c r="U255" t="str">
-        <f>=(B255*1000000000)-(C255*10000000)+(D255*100000)+(B260*1000)-(C260*100)+(D260*10)+(E260*1)-(F260*0.01)</f>
+        <f>(B255*1000000000)-(C255*10000000)+(D255*100000)+(B260*1000)-(C260*100)+(D260*10)+(E260*1)-(F260*0.01)</f>
       </c>
       <c r="AC255" t="str">
-        <f>=(J255*1000000000)-(K255*10000000)+(L255*100000)+(J260*1000)-(K260*100)+(L260*10)+(M260*1)-(N260*0.01)</f>
+        <f>(J255*1000000000)-(K255*10000000)+(L255*100000)+(J260*1000)-(K260*100)+(L260*10)+(M260*1)-(N260*0.01)</f>
       </c>
     </row>
     <row r="256">
@@ -12131,10 +12131,10 @@
         <f>RANK(AC256,$AC$254:$AC$256)+COUNTIF($AC$253:AC255,AC256)</f>
       </c>
       <c r="U256" t="str">
-        <f>=(B256*1000000000)-(C256*10000000)+(D256*100000)+(B261*1000)-(C261*100)+(D261*10)+(E261*1)-(F261*0.01)</f>
+        <f>(B256*1000000000)-(C256*10000000)+(D256*100000)+(B261*1000)-(C261*100)+(D261*10)+(E261*1)-(F261*0.01)</f>
       </c>
       <c r="AC256" t="str">
-        <f>=(J256*1000000000)-(K256*10000000)+(L256*100000)+(J261*1000)-(K261*100)+(L261*10)+(M261*1)-(N261*0.01)</f>
+        <f>(J256*1000000000)-(K256*10000000)+(L256*100000)+(J261*1000)-(K261*100)+(L261*10)+(M261*1)-(N261*0.01)</f>
       </c>
     </row>
     <row r="258">
@@ -12989,10 +12989,10 @@
         <f>RANK(AC297,$AC$297:$AC$299)+COUNTIF($AC$296:AC296,AC297)</f>
       </c>
       <c r="U297" t="str">
-        <f>=(B297*1000000000)-(C297*10000000)+(D297*100000)+(B302*1000)-(C302*100)+(D302*10)+(E302*1)-(F302*0.01)</f>
+        <f>(B297*1000000000)-(C297*10000000)+(D297*100000)+(B302*1000)-(C302*100)+(D302*10)+(E302*1)-(F302*0.01)</f>
       </c>
       <c r="AC297" t="str">
-        <f>=(J297*1000000000)-(K297*10000000)+(L297*100000)+(J302*1000)-(K302*100)+(L302*10)+(M302*1)-(N302*0.01)</f>
+        <f>(J297*1000000000)-(K297*10000000)+(L297*100000)+(J302*1000)-(K302*100)+(L302*10)+(M302*1)-(N302*0.01)</f>
       </c>
     </row>
     <row r="298">
@@ -13027,10 +13027,10 @@
         <f>RANK(AC298,$AC$297:$AC$299)+COUNTIF($AC$296:AC297,AC298)</f>
       </c>
       <c r="U298" t="str">
-        <f>=(B298*1000000000)-(C298*10000000)+(D298*100000)+(B303*1000)-(C303*100)+(D303*10)+(E303*1)-(F303*0.01)</f>
+        <f>(B298*1000000000)-(C298*10000000)+(D298*100000)+(B303*1000)-(C303*100)+(D303*10)+(E303*1)-(F303*0.01)</f>
       </c>
       <c r="AC298" t="str">
-        <f>=(J298*1000000000)-(K298*10000000)+(L298*100000)+(J303*1000)-(K303*100)+(L303*10)+(M303*1)-(N303*0.01)</f>
+        <f>(J298*1000000000)-(K298*10000000)+(L298*100000)+(J303*1000)-(K303*100)+(L303*10)+(M303*1)-(N303*0.01)</f>
       </c>
     </row>
     <row r="299">
@@ -13065,10 +13065,10 @@
         <f>RANK(AC299,$AC$297:$AC$299)+COUNTIF($AC$296:AC298,AC299)</f>
       </c>
       <c r="U299" t="str">
-        <f>=(B299*1000000000)-(C299*10000000)+(D299*100000)+(B304*1000)-(C304*100)+(D304*10)+(E304*1)-(F304*0.01)</f>
+        <f>(B299*1000000000)-(C299*10000000)+(D299*100000)+(B304*1000)-(C304*100)+(D304*10)+(E304*1)-(F304*0.01)</f>
       </c>
       <c r="AC299" t="str">
-        <f>=(J299*1000000000)-(K299*10000000)+(L299*100000)+(J304*1000)-(K304*100)+(L304*10)+(M304*1)-(N304*0.01)</f>
+        <f>(J299*1000000000)-(K299*10000000)+(L299*100000)+(J304*1000)-(K304*100)+(L304*10)+(M304*1)-(N304*0.01)</f>
       </c>
     </row>
     <row r="301">
@@ -13923,10 +13923,10 @@
         <f>RANK(AC340,$AC$340:$AC$342)+COUNTIF($AC$339:AC339,AC340)</f>
       </c>
       <c r="U340" t="str">
-        <f>=(B340*1000000000)-(C340*10000000)+(D340*100000)+(B345*1000)-(C345*100)+(D345*10)+(E345*1)-(F345*0.01)</f>
+        <f>(B340*1000000000)-(C340*10000000)+(D340*100000)+(B345*1000)-(C345*100)+(D345*10)+(E345*1)-(F345*0.01)</f>
       </c>
       <c r="AC340" t="str">
-        <f>=(J340*1000000000)-(K340*10000000)+(L340*100000)+(J345*1000)-(K345*100)+(L345*10)+(M345*1)-(N345*0.01)</f>
+        <f>(J340*1000000000)-(K340*10000000)+(L340*100000)+(J345*1000)-(K345*100)+(L345*10)+(M345*1)-(N345*0.01)</f>
       </c>
     </row>
     <row r="341">
@@ -13961,10 +13961,10 @@
         <f>RANK(AC341,$AC$340:$AC$342)+COUNTIF($AC$339:AC340,AC341)</f>
       </c>
       <c r="U341" t="str">
-        <f>=(B341*1000000000)-(C341*10000000)+(D341*100000)+(B346*1000)-(C346*100)+(D346*10)+(E346*1)-(F346*0.01)</f>
+        <f>(B341*1000000000)-(C341*10000000)+(D341*100000)+(B346*1000)-(C346*100)+(D346*10)+(E346*1)-(F346*0.01)</f>
       </c>
       <c r="AC341" t="str">
-        <f>=(J341*1000000000)-(K341*10000000)+(L341*100000)+(J346*1000)-(K346*100)+(L346*10)+(M346*1)-(N346*0.01)</f>
+        <f>(J341*1000000000)-(K341*10000000)+(L341*100000)+(J346*1000)-(K346*100)+(L346*10)+(M346*1)-(N346*0.01)</f>
       </c>
     </row>
     <row r="342">
@@ -13999,10 +13999,10 @@
         <f>RANK(AC342,$AC$340:$AC$342)+COUNTIF($AC$339:AC341,AC342)</f>
       </c>
       <c r="U342" t="str">
-        <f>=(B342*1000000000)-(C342*10000000)+(D342*100000)+(B347*1000)-(C347*100)+(D347*10)+(E347*1)-(F347*0.01)</f>
+        <f>(B342*1000000000)-(C342*10000000)+(D342*100000)+(B347*1000)-(C347*100)+(D347*10)+(E347*1)-(F347*0.01)</f>
       </c>
       <c r="AC342" t="str">
-        <f>=(J342*1000000000)-(K342*10000000)+(L342*100000)+(J347*1000)-(K347*100)+(L347*10)+(M347*1)-(N347*0.01)</f>
+        <f>(J342*1000000000)-(K342*10000000)+(L342*100000)+(J347*1000)-(K347*100)+(L347*10)+(M347*1)-(N347*0.01)</f>
       </c>
     </row>
     <row r="344">
@@ -14857,10 +14857,10 @@
         <f>RANK(AC383,$AC$383:$AC$385)+COUNTIF($AC$382:AC382,AC383)</f>
       </c>
       <c r="U383" t="str">
-        <f>=(B383*1000000000)-(C383*10000000)+(D383*100000)+(B388*1000)-(C388*100)+(D388*10)+(E388*1)-(F388*0.01)</f>
+        <f>(B383*1000000000)-(C383*10000000)+(D383*100000)+(B388*1000)-(C388*100)+(D388*10)+(E388*1)-(F388*0.01)</f>
       </c>
       <c r="AC383" t="str">
-        <f>=(J383*1000000000)-(K383*10000000)+(L383*100000)+(J388*1000)-(K388*100)+(L388*10)+(M388*1)-(N388*0.01)</f>
+        <f>(J383*1000000000)-(K383*10000000)+(L383*100000)+(J388*1000)-(K388*100)+(L388*10)+(M388*1)-(N388*0.01)</f>
       </c>
     </row>
     <row r="384">
@@ -14895,10 +14895,10 @@
         <f>RANK(AC384,$AC$383:$AC$385)+COUNTIF($AC$382:AC383,AC384)</f>
       </c>
       <c r="U384" t="str">
-        <f>=(B384*1000000000)-(C384*10000000)+(D384*100000)+(B389*1000)-(C389*100)+(D389*10)+(E389*1)-(F389*0.01)</f>
+        <f>(B384*1000000000)-(C384*10000000)+(D384*100000)+(B389*1000)-(C389*100)+(D389*10)+(E389*1)-(F389*0.01)</f>
       </c>
       <c r="AC384" t="str">
-        <f>=(J384*1000000000)-(K384*10000000)+(L384*100000)+(J389*1000)-(K389*100)+(L389*10)+(M389*1)-(N389*0.01)</f>
+        <f>(J384*1000000000)-(K384*10000000)+(L384*100000)+(J389*1000)-(K389*100)+(L389*10)+(M389*1)-(N389*0.01)</f>
       </c>
     </row>
     <row r="385">
@@ -14933,10 +14933,10 @@
         <f>RANK(AC385,$AC$383:$AC$385)+COUNTIF($AC$382:AC384,AC385)</f>
       </c>
       <c r="U385" t="str">
-        <f>=(B385*1000000000)-(C385*10000000)+(D385*100000)+(B390*1000)-(C390*100)+(D390*10)+(E390*1)-(F390*0.01)</f>
+        <f>(B385*1000000000)-(C385*10000000)+(D385*100000)+(B390*1000)-(C390*100)+(D390*10)+(E390*1)-(F390*0.01)</f>
       </c>
       <c r="AC385" t="str">
-        <f>=(J385*1000000000)-(K385*10000000)+(L385*100000)+(J390*1000)-(K390*100)+(L390*10)+(M390*1)-(N390*0.01)</f>
+        <f>(J385*1000000000)-(K385*10000000)+(L385*100000)+(J390*1000)-(K390*100)+(L390*10)+(M390*1)-(N390*0.01)</f>
       </c>
     </row>
     <row r="387">
@@ -15791,10 +15791,10 @@
         <f>RANK(AC426,$AC$426:$AC$428)+COUNTIF($AC$425:AC425,AC426)</f>
       </c>
       <c r="U426" t="str">
-        <f>=(B426*1000000000)-(C426*10000000)+(D426*100000)+(B431*1000)-(C431*100)+(D431*10)+(E431*1)-(F431*0.01)</f>
+        <f>(B426*1000000000)-(C426*10000000)+(D426*100000)+(B431*1000)-(C431*100)+(D431*10)+(E431*1)-(F431*0.01)</f>
       </c>
       <c r="AC426" t="str">
-        <f>=(J426*1000000000)-(K426*10000000)+(L426*100000)+(J431*1000)-(K431*100)+(L431*10)+(M431*1)-(N431*0.01)</f>
+        <f>(J426*1000000000)-(K426*10000000)+(L426*100000)+(J431*1000)-(K431*100)+(L431*10)+(M431*1)-(N431*0.01)</f>
       </c>
     </row>
     <row r="427">
@@ -15829,10 +15829,10 @@
         <f>RANK(AC427,$AC$426:$AC$428)+COUNTIF($AC$425:AC426,AC427)</f>
       </c>
       <c r="U427" t="str">
-        <f>=(B427*1000000000)-(C427*10000000)+(D427*100000)+(B432*1000)-(C432*100)+(D432*10)+(E432*1)-(F432*0.01)</f>
+        <f>(B427*1000000000)-(C427*10000000)+(D427*100000)+(B432*1000)-(C432*100)+(D432*10)+(E432*1)-(F432*0.01)</f>
       </c>
       <c r="AC427" t="str">
-        <f>=(J427*1000000000)-(K427*10000000)+(L427*100000)+(J432*1000)-(K432*100)+(L432*10)+(M432*1)-(N432*0.01)</f>
+        <f>(J427*1000000000)-(K427*10000000)+(L427*100000)+(J432*1000)-(K432*100)+(L432*10)+(M432*1)-(N432*0.01)</f>
       </c>
     </row>
     <row r="428">
@@ -15867,10 +15867,10 @@
         <f>RANK(AC428,$AC$426:$AC$428)+COUNTIF($AC$425:AC427,AC428)</f>
       </c>
       <c r="U428" t="str">
-        <f>=(B428*1000000000)-(C428*10000000)+(D428*100000)+(B433*1000)-(C433*100)+(D433*10)+(E433*1)-(F433*0.01)</f>
+        <f>(B428*1000000000)-(C428*10000000)+(D428*100000)+(B433*1000)-(C433*100)+(D433*10)+(E433*1)-(F433*0.01)</f>
       </c>
       <c r="AC428" t="str">
-        <f>=(J428*1000000000)-(K428*10000000)+(L428*100000)+(J433*1000)-(K433*100)+(L433*10)+(M433*1)-(N433*0.01)</f>
+        <f>(J428*1000000000)-(K428*10000000)+(L428*100000)+(J433*1000)-(K433*100)+(L433*10)+(M433*1)-(N433*0.01)</f>
       </c>
     </row>
     <row r="430">
@@ -16725,10 +16725,10 @@
         <f>RANK(AC469,$AC$469:$AC$471)+COUNTIF($AC$468:AC468,AC469)</f>
       </c>
       <c r="U469" t="str">
-        <f>=(B469*1000000000)-(C469*10000000)+(D469*100000)+(B474*1000)-(C474*100)+(D474*10)+(E474*1)-(F474*0.01)</f>
+        <f>(B469*1000000000)-(C469*10000000)+(D469*100000)+(B474*1000)-(C474*100)+(D474*10)+(E474*1)-(F474*0.01)</f>
       </c>
       <c r="AC469" t="str">
-        <f>=(J469*1000000000)-(K469*10000000)+(L469*100000)+(J474*1000)-(K474*100)+(L474*10)+(M474*1)-(N474*0.01)</f>
+        <f>(J469*1000000000)-(K469*10000000)+(L469*100000)+(J474*1000)-(K474*100)+(L474*10)+(M474*1)-(N474*0.01)</f>
       </c>
     </row>
     <row r="470">
@@ -16763,10 +16763,10 @@
         <f>RANK(AC470,$AC$469:$AC$471)+COUNTIF($AC$468:AC469,AC470)</f>
       </c>
       <c r="U470" t="str">
-        <f>=(B470*1000000000)-(C470*10000000)+(D470*100000)+(B475*1000)-(C475*100)+(D475*10)+(E475*1)-(F475*0.01)</f>
+        <f>(B470*1000000000)-(C470*10000000)+(D470*100000)+(B475*1000)-(C475*100)+(D475*10)+(E475*1)-(F475*0.01)</f>
       </c>
       <c r="AC470" t="str">
-        <f>=(J470*1000000000)-(K470*10000000)+(L470*100000)+(J475*1000)-(K475*100)+(L475*10)+(M475*1)-(N475*0.01)</f>
+        <f>(J470*1000000000)-(K470*10000000)+(L470*100000)+(J475*1000)-(K475*100)+(L475*10)+(M475*1)-(N475*0.01)</f>
       </c>
     </row>
     <row r="471">
@@ -16801,10 +16801,10 @@
         <f>RANK(AC471,$AC$469:$AC$471)+COUNTIF($AC$468:AC470,AC471)</f>
       </c>
       <c r="U471" t="str">
-        <f>=(B471*1000000000)-(C471*10000000)+(D471*100000)+(B476*1000)-(C476*100)+(D476*10)+(E476*1)-(F476*0.01)</f>
+        <f>(B471*1000000000)-(C471*10000000)+(D471*100000)+(B476*1000)-(C476*100)+(D476*10)+(E476*1)-(F476*0.01)</f>
       </c>
       <c r="AC471" t="str">
-        <f>=(J471*1000000000)-(K471*10000000)+(L471*100000)+(J476*1000)-(K476*100)+(L476*10)+(M476*1)-(N476*0.01)</f>
+        <f>(J471*1000000000)-(K471*10000000)+(L471*100000)+(J476*1000)-(K476*100)+(L476*10)+(M476*1)-(N476*0.01)</f>
       </c>
     </row>
     <row r="473">
@@ -17659,10 +17659,10 @@
         <f>RANK(AC512,$AC$512:$AC$514)+COUNTIF($AC$511:AC511,AC512)</f>
       </c>
       <c r="U512" t="str">
-        <f>=(B512*1000000000)-(C512*10000000)+(D512*100000)+(B517*1000)-(C517*100)+(D517*10)+(E517*1)-(F517*0.01)</f>
+        <f>(B512*1000000000)-(C512*10000000)+(D512*100000)+(B517*1000)-(C517*100)+(D517*10)+(E517*1)-(F517*0.01)</f>
       </c>
       <c r="AC512" t="str">
-        <f>=(J512*1000000000)-(K512*10000000)+(L512*100000)+(J517*1000)-(K517*100)+(L517*10)+(M517*1)-(N517*0.01)</f>
+        <f>(J512*1000000000)-(K512*10000000)+(L512*100000)+(J517*1000)-(K517*100)+(L517*10)+(M517*1)-(N517*0.01)</f>
       </c>
     </row>
     <row r="513">
@@ -17697,10 +17697,10 @@
         <f>RANK(AC513,$AC$512:$AC$514)+COUNTIF($AC$511:AC512,AC513)</f>
       </c>
       <c r="U513" t="str">
-        <f>=(B513*1000000000)-(C513*10000000)+(D513*100000)+(B518*1000)-(C518*100)+(D518*10)+(E518*1)-(F518*0.01)</f>
+        <f>(B513*1000000000)-(C513*10000000)+(D513*100000)+(B518*1000)-(C518*100)+(D518*10)+(E518*1)-(F518*0.01)</f>
       </c>
       <c r="AC513" t="str">
-        <f>=(J513*1000000000)-(K513*10000000)+(L513*100000)+(J518*1000)-(K518*100)+(L518*10)+(M518*1)-(N518*0.01)</f>
+        <f>(J513*1000000000)-(K513*10000000)+(L513*100000)+(J518*1000)-(K518*100)+(L518*10)+(M518*1)-(N518*0.01)</f>
       </c>
     </row>
     <row r="514">
@@ -17735,10 +17735,10 @@
         <f>RANK(AC514,$AC$512:$AC$514)+COUNTIF($AC$511:AC513,AC514)</f>
       </c>
       <c r="U514" t="str">
-        <f>=(B514*1000000000)-(C514*10000000)+(D514*100000)+(B519*1000)-(C519*100)+(D519*10)+(E519*1)-(F519*0.01)</f>
+        <f>(B514*1000000000)-(C514*10000000)+(D514*100000)+(B519*1000)-(C519*100)+(D519*10)+(E519*1)-(F519*0.01)</f>
       </c>
       <c r="AC514" t="str">
-        <f>=(J514*1000000000)-(K514*10000000)+(L514*100000)+(J519*1000)-(K519*100)+(L519*10)+(M519*1)-(N519*0.01)</f>
+        <f>(J514*1000000000)-(K514*10000000)+(L514*100000)+(J519*1000)-(K519*100)+(L519*10)+(M519*1)-(N519*0.01)</f>
       </c>
     </row>
     <row r="516">
@@ -18593,10 +18593,10 @@
         <f>RANK(AC555,$AC$555:$AC$557)+COUNTIF($AC$554:AC554,AC555)</f>
       </c>
       <c r="U555" t="str">
-        <f>=(B555*1000000000)-(C555*10000000)+(D555*100000)+(B560*1000)-(C560*100)+(D560*10)+(E560*1)-(F560*0.01)</f>
+        <f>(B555*1000000000)-(C555*10000000)+(D555*100000)+(B560*1000)-(C560*100)+(D560*10)+(E560*1)-(F560*0.01)</f>
       </c>
       <c r="AC555" t="str">
-        <f>=(J555*1000000000)-(K555*10000000)+(L555*100000)+(J560*1000)-(K560*100)+(L560*10)+(M560*1)-(N560*0.01)</f>
+        <f>(J555*1000000000)-(K555*10000000)+(L555*100000)+(J560*1000)-(K560*100)+(L560*10)+(M560*1)-(N560*0.01)</f>
       </c>
     </row>
     <row r="556">
@@ -18631,10 +18631,10 @@
         <f>RANK(AC556,$AC$555:$AC$557)+COUNTIF($AC$554:AC555,AC556)</f>
       </c>
       <c r="U556" t="str">
-        <f>=(B556*1000000000)-(C556*10000000)+(D556*100000)+(B561*1000)-(C561*100)+(D561*10)+(E561*1)-(F561*0.01)</f>
+        <f>(B556*1000000000)-(C556*10000000)+(D556*100000)+(B561*1000)-(C561*100)+(D561*10)+(E561*1)-(F561*0.01)</f>
       </c>
       <c r="AC556" t="str">
-        <f>=(J556*1000000000)-(K556*10000000)+(L556*100000)+(J561*1000)-(K561*100)+(L561*10)+(M561*1)-(N561*0.01)</f>
+        <f>(J556*1000000000)-(K556*10000000)+(L556*100000)+(J561*1000)-(K561*100)+(L561*10)+(M561*1)-(N561*0.01)</f>
       </c>
     </row>
     <row r="557">
@@ -18669,10 +18669,10 @@
         <f>RANK(AC557,$AC$555:$AC$557)+COUNTIF($AC$554:AC556,AC557)</f>
       </c>
       <c r="U557" t="str">
-        <f>=(B557*1000000000)-(C557*10000000)+(D557*100000)+(B562*1000)-(C562*100)+(D562*10)+(E562*1)-(F562*0.01)</f>
+        <f>(B557*1000000000)-(C557*10000000)+(D557*100000)+(B562*1000)-(C562*100)+(D562*10)+(E562*1)-(F562*0.01)</f>
       </c>
       <c r="AC557" t="str">
-        <f>=(J557*1000000000)-(K557*10000000)+(L557*100000)+(J562*1000)-(K562*100)+(L562*10)+(M562*1)-(N562*0.01)</f>
+        <f>(J557*1000000000)-(K557*10000000)+(L557*100000)+(J562*1000)-(K562*100)+(L562*10)+(M562*1)-(N562*0.01)</f>
       </c>
     </row>
     <row r="559">
@@ -19527,10 +19527,10 @@
         <f>RANK(AC598,$AC$598:$AC$600)+COUNTIF($AC$597:AC597,AC598)</f>
       </c>
       <c r="U598" t="str">
-        <f>=(B598*1000000000)-(C598*10000000)+(D598*100000)+(B603*1000)-(C603*100)+(D603*10)+(E603*1)-(F603*0.01)</f>
+        <f>(B598*1000000000)-(C598*10000000)+(D598*100000)+(B603*1000)-(C603*100)+(D603*10)+(E603*1)-(F603*0.01)</f>
       </c>
       <c r="AC598" t="str">
-        <f>=(J598*1000000000)-(K598*10000000)+(L598*100000)+(J603*1000)-(K603*100)+(L603*10)+(M603*1)-(N603*0.01)</f>
+        <f>(J598*1000000000)-(K598*10000000)+(L598*100000)+(J603*1000)-(K603*100)+(L603*10)+(M603*1)-(N603*0.01)</f>
       </c>
     </row>
     <row r="599">
@@ -19565,10 +19565,10 @@
         <f>RANK(AC599,$AC$598:$AC$600)+COUNTIF($AC$597:AC598,AC599)</f>
       </c>
       <c r="U599" t="str">
-        <f>=(B599*1000000000)-(C599*10000000)+(D599*100000)+(B604*1000)-(C604*100)+(D604*10)+(E604*1)-(F604*0.01)</f>
+        <f>(B599*1000000000)-(C599*10000000)+(D599*100000)+(B604*1000)-(C604*100)+(D604*10)+(E604*1)-(F604*0.01)</f>
       </c>
       <c r="AC599" t="str">
-        <f>=(J599*1000000000)-(K599*10000000)+(L599*100000)+(J604*1000)-(K604*100)+(L604*10)+(M604*1)-(N604*0.01)</f>
+        <f>(J599*1000000000)-(K599*10000000)+(L599*100000)+(J604*1000)-(K604*100)+(L604*10)+(M604*1)-(N604*0.01)</f>
       </c>
     </row>
     <row r="600">
@@ -19603,10 +19603,10 @@
         <f>RANK(AC600,$AC$598:$AC$600)+COUNTIF($AC$597:AC599,AC600)</f>
       </c>
       <c r="U600" t="str">
-        <f>=(B600*1000000000)-(C600*10000000)+(D600*100000)+(B605*1000)-(C605*100)+(D605*10)+(E605*1)-(F605*0.01)</f>
+        <f>(B600*1000000000)-(C600*10000000)+(D600*100000)+(B605*1000)-(C605*100)+(D605*10)+(E605*1)-(F605*0.01)</f>
       </c>
       <c r="AC600" t="str">
-        <f>=(J600*1000000000)-(K600*10000000)+(L600*100000)+(J605*1000)-(K605*100)+(L605*10)+(M605*1)-(N605*0.01)</f>
+        <f>(J600*1000000000)-(K600*10000000)+(L600*100000)+(J605*1000)-(K605*100)+(L605*10)+(M605*1)-(N605*0.01)</f>
       </c>
     </row>
     <row r="602">
@@ -20461,10 +20461,10 @@
         <f>RANK(AC641,$AC$641:$AC$643)+COUNTIF($AC$640:AC640,AC641)</f>
       </c>
       <c r="U641" t="str">
-        <f>=(B641*1000000000)-(C641*10000000)+(D641*100000)+(B646*1000)-(C646*100)+(D646*10)+(E646*1)-(F646*0.01)</f>
+        <f>(B641*1000000000)-(C641*10000000)+(D641*100000)+(B646*1000)-(C646*100)+(D646*10)+(E646*1)-(F646*0.01)</f>
       </c>
       <c r="AC641" t="str">
-        <f>=(J641*1000000000)-(K641*10000000)+(L641*100000)+(J646*1000)-(K646*100)+(L646*10)+(M646*1)-(N646*0.01)</f>
+        <f>(J641*1000000000)-(K641*10000000)+(L641*100000)+(J646*1000)-(K646*100)+(L646*10)+(M646*1)-(N646*0.01)</f>
       </c>
     </row>
     <row r="642">
@@ -20499,10 +20499,10 @@
         <f>RANK(AC642,$AC$641:$AC$643)+COUNTIF($AC$640:AC641,AC642)</f>
       </c>
       <c r="U642" t="str">
-        <f>=(B642*1000000000)-(C642*10000000)+(D642*100000)+(B647*1000)-(C647*100)+(D647*10)+(E647*1)-(F647*0.01)</f>
+        <f>(B642*1000000000)-(C642*10000000)+(D642*100000)+(B647*1000)-(C647*100)+(D647*10)+(E647*1)-(F647*0.01)</f>
       </c>
       <c r="AC642" t="str">
-        <f>=(J642*1000000000)-(K642*10000000)+(L642*100000)+(J647*1000)-(K647*100)+(L647*10)+(M647*1)-(N647*0.01)</f>
+        <f>(J642*1000000000)-(K642*10000000)+(L642*100000)+(J647*1000)-(K647*100)+(L647*10)+(M647*1)-(N647*0.01)</f>
       </c>
     </row>
     <row r="643">
@@ -20537,10 +20537,10 @@
         <f>RANK(AC643,$AC$641:$AC$643)+COUNTIF($AC$640:AC642,AC643)</f>
       </c>
       <c r="U643" t="str">
-        <f>=(B643*1000000000)-(C643*10000000)+(D643*100000)+(B648*1000)-(C648*100)+(D648*10)+(E648*1)-(F648*0.01)</f>
+        <f>(B643*1000000000)-(C643*10000000)+(D643*100000)+(B648*1000)-(C648*100)+(D648*10)+(E648*1)-(F648*0.01)</f>
       </c>
       <c r="AC643" t="str">
-        <f>=(J643*1000000000)-(K643*10000000)+(L643*100000)+(J648*1000)-(K648*100)+(L648*10)+(M648*1)-(N648*0.01)</f>
+        <f>(J643*1000000000)-(K643*10000000)+(L643*100000)+(J648*1000)-(K648*100)+(L648*10)+(M648*1)-(N648*0.01)</f>
       </c>
     </row>
     <row r="645">

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -6631,17 +6631,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -6650,17 +6650,17 @@
         <f>'data'!$B$50</f>
       </c>
       <c r="J4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L4" s="18"/>
       <c r="M4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O4" s="14" t="str">
         <f>'data'!$B$49</f>
@@ -6819,17 +6819,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G12" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -6838,17 +6838,17 @@
         <f>'data'!$B$51</f>
       </c>
       <c r="J12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O12" s="14" t="str">
         <f>'data'!$B$49</f>
@@ -7007,17 +7007,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G20" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -7026,17 +7026,17 @@
         <f>'data'!$B$51</f>
       </c>
       <c r="J20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L20" s="18"/>
       <c r="M20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O20" s="14" t="str">
         <f>'data'!$B$50</f>
@@ -7182,17 +7182,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G28" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -7720,17 +7720,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B57" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C57" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D57" s="18"/>
       <c r="E57" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F57" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G57" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -7739,17 +7739,17 @@
         <f>'data'!$B$53</f>
       </c>
       <c r="J57" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L58:L62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58:J62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58:K62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58:M62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58:N62," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K57" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58:J62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58:K62," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58:M62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58:N62," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N57" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L58:L62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58:M62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58:N62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58:J62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58:K62," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O57" s="14" t="str">
         <f>'data'!$B$52</f>
@@ -7908,17 +7908,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B65" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D66:D70)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66:B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66:C70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66:E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66:F70," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C65" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66:B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66:C70," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D65" s="18"/>
       <c r="E65" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66:E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66:F70," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F65" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D66:D70)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66:E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66:F70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66:B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66:C70," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G65" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -7927,17 +7927,17 @@
         <f>'data'!$B$54</f>
       </c>
       <c r="J65" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L66:L70)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66:J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66:K70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66:M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66:N70," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K65" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66:J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66:K70," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66:M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66:N70," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N65" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L66:L70)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66:M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66:N70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66:J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66:K70," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O65" s="14" t="str">
         <f>'data'!$B$52</f>
@@ -8096,17 +8096,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B73" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C73" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F73" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G73" s="14" t="str">
         <f>'data'!$B$8</f>
@@ -8115,17 +8115,17 @@
         <f>'data'!$B$54</f>
       </c>
       <c r="J73" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L74:L78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74:J78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74:K78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74:M78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74:N78," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K73" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74:J78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74:K78," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74:M78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74:N78," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N73" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L74:L78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74:M78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74:N78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74:J78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74:K78," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O73" s="14" t="str">
         <f>'data'!$B$53</f>
@@ -8654,17 +8654,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B100" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D101:D105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C100" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D100" s="18"/>
       <c r="E100" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F100" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D101:D105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G100" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -8673,17 +8673,17 @@
         <f>'data'!$B$56</f>
       </c>
       <c r="J100" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L101:L105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K100" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L100" s="18"/>
       <c r="M100" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N100" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L101:L105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O100" s="14" t="str">
         <f>'data'!$B$55</f>
@@ -8842,17 +8842,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="B108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D109:D113)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109:B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109:C113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109:E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109:F113," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109:B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109:C113," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109:E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109:F113," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D109:D113)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109:E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109:F113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109:B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109:C113," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G108" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -8861,17 +8861,17 @@
         <f>'data'!$B$57</f>
       </c>
       <c r="J108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L109:L113)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109:J113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109:K113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109:M113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109:N113," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109:J113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109:K113," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L108" s="18"/>
       <c r="M108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109:M113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109:N113," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L109:L113)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109:M113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109:N113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109:J113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109:K113," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O108" s="14" t="str">
         <f>'data'!$B$55</f>
@@ -9030,17 +9030,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="B116" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D117:D121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C116" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D116" s="18"/>
       <c r="E116" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F116" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D117:D121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G116" s="14" t="str">
         <f>'data'!$B$11</f>
@@ -9049,17 +9049,17 @@
         <f>'data'!$B$57</f>
       </c>
       <c r="J116" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L117:L121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K116" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L116" s="18"/>
       <c r="M116" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N116" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L117:L121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O116" s="14" t="str">
         <f>'data'!$B$56</f>
@@ -9588,17 +9588,17 @@
         <f>'data'!$B$14</f>
       </c>
       <c r="B143" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D144:D148)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144:B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144:C148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144:E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144:F148," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C143" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144:B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144:C148," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D143" s="18"/>
       <c r="E143" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144:E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144:F148," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F143" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D144:D148)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144:E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144:F148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144:B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144:C148," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G143" s="14" t="str">
         <f>'data'!$B$13</f>
@@ -9607,17 +9607,17 @@
         <f>'data'!$B$59</f>
       </c>
       <c r="J143" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L144:L148)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144:J148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144:K148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144:M148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144:N148," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K143" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144:J148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144:K148," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L143" s="18"/>
       <c r="M143" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144:M148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144:N148," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N143" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L144:L148)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144:M148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144:N148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144:J148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144:K148," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O143" s="14" t="str">
         <f>'data'!$B$58</f>
@@ -9776,17 +9776,17 @@
         <f>'data'!$B$15</f>
       </c>
       <c r="B151" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D152:D156)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152:B156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152:C156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152:E156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152:F156," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C151" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152:B156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152:C156," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D151" s="18"/>
       <c r="E151" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152:E156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152:F156," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F151" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D152:D156)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152:E156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152:F156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152:B156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152:C156," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G151" s="14" t="str">
         <f>'data'!$B$13</f>
@@ -9795,17 +9795,17 @@
         <f>'data'!$B$60</f>
       </c>
       <c r="J151" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L152:L156)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152:J156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152:K156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152:M156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152:N156," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K151" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152:J156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152:K156," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L151" s="18"/>
       <c r="M151" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152:M156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152:N156," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N151" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L152:L156)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152:M156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152:N156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152:J156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152:K156," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O151" s="14" t="str">
         <f>'data'!$B$58</f>
@@ -9964,17 +9964,17 @@
         <f>'data'!$B$15</f>
       </c>
       <c r="B159" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D160:D164)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160:B164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160:C164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160:E164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160:F164," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C159" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160:B164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160:C164," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D159" s="18"/>
       <c r="E159" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160:E164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160:F164," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F159" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D160:D164)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160:E164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160:F164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160:B164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160:C164," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G159" s="14" t="str">
         <f>'data'!$B$14</f>
@@ -9983,17 +9983,17 @@
         <f>'data'!$B$60</f>
       </c>
       <c r="J159" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L160:L164)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160:J164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160:K164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160:M164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160:N164," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K159" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160:J164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160:K164," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L159" s="18"/>
       <c r="M159" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160:M164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160:N164," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N159" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L160:L164)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160:M164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160:N164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160:J164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160:K164," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O159" s="14" t="str">
         <f>'data'!$B$59</f>
@@ -10522,17 +10522,17 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="B186" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D187:D191)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187:B191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187:C191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187:E191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187:F191," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C186" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187:B191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187:C191," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D186" s="18"/>
       <c r="E186" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187:E191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187:F191," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F186" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D187:D191)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187:E191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187:F191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187:B191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187:C191," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G186" s="14" t="str">
         <f>'data'!$B$16</f>
@@ -10541,17 +10541,17 @@
         <f>'data'!$B$62</f>
       </c>
       <c r="J186" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L187:L191)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187:J191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187:K191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187:M191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187:N191," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K186" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187:J191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187:K191," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L186" s="18"/>
       <c r="M186" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187:M191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187:N191," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N186" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L187:L191)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187:M191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187:N191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187:J191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187:K191," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O186" s="14" t="str">
         <f>'data'!$B$61</f>
@@ -10710,17 +10710,17 @@
         <f>'data'!$B$18</f>
       </c>
       <c r="B194" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D195:D199)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195:B199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195:C199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195:E199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195:F199," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C194" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195:B199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195:C199," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D194" s="18"/>
       <c r="E194" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195:E199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195:F199," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F194" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D195:D199)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195:E199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195:F199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195:B199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195:C199," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G194" s="14" t="str">
         <f>'data'!$B$16</f>
@@ -10729,17 +10729,17 @@
         <f>'data'!$B$63</f>
       </c>
       <c r="J194" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L195:L199)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195:J199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195:K199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195:M199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195:N199," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K194" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195:J199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195:K199," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L194" s="18"/>
       <c r="M194" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195:M199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195:N199," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N194" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L195:L199)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195:M199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195:N199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195:J199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195:K199," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O194" s="14" t="str">
         <f>'data'!$B$61</f>
@@ -10898,17 +10898,17 @@
         <f>'data'!$B$18</f>
       </c>
       <c r="B202" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D203:D207)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203:B207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203:C207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203:E207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203:F207," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C202" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203:B207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203:C207," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D202" s="18"/>
       <c r="E202" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203:E207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203:F207," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F202" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D203:D207)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203:E207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203:F207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203:B207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203:C207," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G202" s="14" t="str">
         <f>'data'!$B$17</f>
@@ -10917,17 +10917,17 @@
         <f>'data'!$B$63</f>
       </c>
       <c r="J202" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L203:L207)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203:J207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203:K207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203:M207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203:N207," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K202" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203:J207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203:K207," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L202" s="18"/>
       <c r="M202" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203:M207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203:N207," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N202" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L203:L207)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203:M207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203:N207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203:J207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203:K207," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O202" s="14" t="str">
         <f>'data'!$B$62</f>
@@ -11456,17 +11456,17 @@
         <f>'data'!$B$20</f>
       </c>
       <c r="B229" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D230:D234)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230:B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230:C234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230:E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230:F234," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C229" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230:B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230:C234," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D229" s="18"/>
       <c r="E229" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230:E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230:F234," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F229" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D230:D234)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230:E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230:F234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230:B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230:C234," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G229" s="14" t="str">
         <f>'data'!$B$19</f>
@@ -11475,17 +11475,17 @@
         <f>'data'!$B$65</f>
       </c>
       <c r="J229" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L230:L234)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230:J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230:K234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230:M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230:N234," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K229" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230:J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230:K234," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L229" s="18"/>
       <c r="M229" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230:M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230:N234," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N229" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L230:L234)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230:M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230:N234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230:J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230:K234," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O229" s="14" t="str">
         <f>'data'!$B$64</f>
@@ -11644,17 +11644,17 @@
         <f>'data'!$B$21</f>
       </c>
       <c r="B237" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D238:D242)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238:B242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238:C242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238:E242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238:F242," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C237" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238:B242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238:C242," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D237" s="18"/>
       <c r="E237" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238:E242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238:F242," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F237" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D238:D242)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238:E242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238:F242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238:B242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238:C242," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G237" s="14" t="str">
         <f>'data'!$B$19</f>
@@ -11663,17 +11663,17 @@
         <f>'data'!$B$66</f>
       </c>
       <c r="J237" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L238:L242)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238:J242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238:K242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238:M242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238:N242," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K237" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238:J242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238:K242," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L237" s="18"/>
       <c r="M237" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238:M242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238:N242," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N237" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L238:L242)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238:M242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238:N242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238:J242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238:K242," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O237" s="14" t="str">
         <f>'data'!$B$64</f>
@@ -11832,17 +11832,17 @@
         <f>'data'!$B$21</f>
       </c>
       <c r="B245" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D246:D250)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246:B250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246:C250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246:E250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246:F250," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C245" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246:B250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246:C250," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D245" s="18"/>
       <c r="E245" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246:E250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246:F250," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F245" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D246:D250)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246:E250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246:F250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246:B250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246:C250," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G245" s="14" t="str">
         <f>'data'!$B$20</f>
@@ -11851,17 +11851,17 @@
         <f>'data'!$B$66</f>
       </c>
       <c r="J245" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L246:L250)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246:J250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246:K250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246:M250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246:N250," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K245" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246:J250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246:K250," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L245" s="18"/>
       <c r="M245" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246:M250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246:N250," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N245" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L246:L250)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246:M250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246:N250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246:J250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246:K250," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O245" s="14" t="str">
         <f>'data'!$B$65</f>
@@ -12390,17 +12390,17 @@
         <f>'data'!$B$23</f>
       </c>
       <c r="B272" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D273:D277)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273:B277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273:C277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273:E277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273:F277," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C272" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273:B277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273:C277," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D272" s="18"/>
       <c r="E272" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273:E277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273:F277," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F272" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D273:D277)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273:E277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273:F277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273:B277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273:C277," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G272" s="14" t="str">
         <f>'data'!$B$22</f>
@@ -12409,17 +12409,17 @@
         <f>'data'!$B$68</f>
       </c>
       <c r="J272" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L273:L277)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273:J277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273:K277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273:M277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273:N277," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K272" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273:J277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273:K277," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L272" s="18"/>
       <c r="M272" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273:M277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273:N277," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N272" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L273:L277)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273:M277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273:N277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273:J277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273:K277," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O272" s="14" t="str">
         <f>'data'!$B$67</f>
@@ -12578,17 +12578,17 @@
         <f>'data'!$B$24</f>
       </c>
       <c r="B280" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D281:D285)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281:B285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281:C285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281:E285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281:F285," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C280" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281:B285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281:C285," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D280" s="18"/>
       <c r="E280" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281:E285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281:F285," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F280" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D281:D285)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281:E285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281:F285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281:B285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281:C285," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G280" s="14" t="str">
         <f>'data'!$B$22</f>
@@ -12597,17 +12597,17 @@
         <f>'data'!$B$69</f>
       </c>
       <c r="J280" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L281:L285)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281:J285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281:K285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281:M285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281:N285," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K280" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281:J285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281:K285," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L280" s="18"/>
       <c r="M280" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281:M285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281:N285," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N280" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L281:L285)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281:M285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281:N285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281:J285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281:K285," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O280" s="14" t="str">
         <f>'data'!$B$67</f>
@@ -12766,17 +12766,17 @@
         <f>'data'!$B$24</f>
       </c>
       <c r="B288" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D289:D293)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289:B293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289:C293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289:E293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289:F293," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C288" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289:B293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289:C293," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D288" s="18"/>
       <c r="E288" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289:E293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289:F293," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F288" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D289:D293)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289:E293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289:F293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289:B293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289:C293," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G288" s="14" t="str">
         <f>'data'!$B$23</f>
@@ -12785,17 +12785,17 @@
         <f>'data'!$B$69</f>
       </c>
       <c r="J288" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L289:L293)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289:J293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289:K293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289:M293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289:N293," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K288" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289:J293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289:K293," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L288" s="18"/>
       <c r="M288" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289:M293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289:N293," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N288" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L289:L293)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289:M293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289:N293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289:J293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289:K293," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O288" s="14" t="str">
         <f>'data'!$B$68</f>
@@ -13324,17 +13324,17 @@
         <f>'data'!$B$26</f>
       </c>
       <c r="B315" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D316:D320)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316:B320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316:C320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316:E320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316:F320," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C315" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316:B320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316:C320," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D315" s="18"/>
       <c r="E315" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316:E320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316:F320," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F315" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D316:D320)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316:E320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316:F320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316:B320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316:C320," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G315" s="14" t="str">
         <f>'data'!$B$25</f>
@@ -13343,17 +13343,17 @@
         <f>'data'!$B$71</f>
       </c>
       <c r="J315" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L316:L320)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316:J320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316:K320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316:M320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316:N320," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K315" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316:J320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316:K320," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L315" s="18"/>
       <c r="M315" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316:M320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316:N320," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N315" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L316:L320)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316:M320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316:N320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316:J320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316:K320," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O315" s="14" t="str">
         <f>'data'!$B$70</f>
@@ -13512,17 +13512,17 @@
         <f>'data'!$B$27</f>
       </c>
       <c r="B323" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D324:D328)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324:B328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324:C328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324:E328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324:F328," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C323" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324:B328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324:C328," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D323" s="18"/>
       <c r="E323" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324:E328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324:F328," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F323" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D324:D328)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324:E328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324:F328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324:B328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324:C328," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G323" s="14" t="str">
         <f>'data'!$B$25</f>
@@ -13531,17 +13531,17 @@
         <f>'data'!$B$72</f>
       </c>
       <c r="J323" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L324:L328)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324:J328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324:K328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324:M328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324:N328," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K323" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324:J328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324:K328," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L323" s="18"/>
       <c r="M323" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324:M328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324:N328," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N323" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L324:L328)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324:M328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324:N328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324:J328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324:K328," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O323" s="14" t="str">
         <f>'data'!$B$70</f>
@@ -13700,17 +13700,17 @@
         <f>'data'!$B$27</f>
       </c>
       <c r="B331" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D332:D336)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332:B336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332:C336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332:E336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332:F336," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C331" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332:B336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332:C336," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D331" s="18"/>
       <c r="E331" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332:E336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332:F336," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F331" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D332:D336)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332:E336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332:F336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332:B336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332:C336," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G331" s="14" t="str">
         <f>'data'!$B$26</f>
@@ -13719,17 +13719,17 @@
         <f>'data'!$B$72</f>
       </c>
       <c r="J331" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L332:L336)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332:J336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332:K336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332:M336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332:N336," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K331" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332:J336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332:K336," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L331" s="18"/>
       <c r="M331" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332:M336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332:N336," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N331" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L332:L336)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332:M336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332:N336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332:J336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332:K336," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O331" s="14" t="str">
         <f>'data'!$B$71</f>
@@ -14258,17 +14258,17 @@
         <f>'data'!$B$29</f>
       </c>
       <c r="B358" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D359:D363)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359:B363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359:C363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359:E363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359:F363," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C358" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359:B363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359:C363," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D358" s="18"/>
       <c r="E358" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359:E363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359:F363," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F358" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D359:D363)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359:E363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359:F363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359:B363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359:C363," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G358" s="14" t="str">
         <f>'data'!$B$28</f>
@@ -14277,17 +14277,17 @@
         <f>'data'!$B$74</f>
       </c>
       <c r="J358" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L359:L363)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359:J363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359:K363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359:M363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359:N363," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K358" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359:J363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359:K363," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L358" s="18"/>
       <c r="M358" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359:M363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359:N363," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N358" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L359:L363)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359:M363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359:N363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359:J363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359:K363," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O358" s="14" t="str">
         <f>'data'!$B$73</f>
@@ -14446,17 +14446,17 @@
         <f>'data'!$B$30</f>
       </c>
       <c r="B366" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D367:D371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367:B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367:C371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367:E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367:F371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C366" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367:B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367:C371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D366" s="18"/>
       <c r="E366" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367:E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367:F371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F366" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D367:D371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367:E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367:F371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367:B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367:C371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G366" s="14" t="str">
         <f>'data'!$B$28</f>
@@ -14465,17 +14465,17 @@
         <f>'data'!$B$75</f>
       </c>
       <c r="J366" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L367:L371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367:J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367:K371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367:M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367:N371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K366" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367:J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367:K371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L366" s="18"/>
       <c r="M366" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367:M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367:N371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N366" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L367:L371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367:M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367:N371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367:J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367:K371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O366" s="14" t="str">
         <f>'data'!$B$73</f>
@@ -14634,17 +14634,17 @@
         <f>'data'!$B$30</f>
       </c>
       <c r="B374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D375:D379)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375:B379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375:C379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375:E379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375:F379," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375:B379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375:C379," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D374" s="18"/>
       <c r="E374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375:E379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375:F379," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D375:D379)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375:E379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375:F379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375:B379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375:C379," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G374" s="14" t="str">
         <f>'data'!$B$29</f>
@@ -14653,17 +14653,17 @@
         <f>'data'!$B$75</f>
       </c>
       <c r="J374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L375:L379)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375:J379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375:K379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375:M379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375:N379," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375:J379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375:K379," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L374" s="18"/>
       <c r="M374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375:M379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375:N379," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L375:L379)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375:M379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375:N379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375:J379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375:K379," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O374" s="14" t="str">
         <f>'data'!$B$74</f>
@@ -15192,17 +15192,17 @@
         <f>'data'!$B$32</f>
       </c>
       <c r="B401" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D402:D406)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402:B406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402:C406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402:E406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402:F406," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C401" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402:B406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402:C406," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D401" s="18"/>
       <c r="E401" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402:E406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402:F406," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F401" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D402:D406)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402:E406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402:F406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402:B406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402:C406," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G401" s="14" t="str">
         <f>'data'!$B$31</f>
@@ -15211,17 +15211,17 @@
         <f>'data'!$B$77</f>
       </c>
       <c r="J401" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L402:L406)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402:J406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402:K406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402:M406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402:N406," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K401" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402:J406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402:K406," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L401" s="18"/>
       <c r="M401" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402:M406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402:N406," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N401" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L402:L406)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402:M406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402:N406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402:J406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402:K406," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O401" s="14" t="str">
         <f>'data'!$B$76</f>
@@ -15380,17 +15380,17 @@
         <f>'data'!$B$33</f>
       </c>
       <c r="B409" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D410:D414)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410:B414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410:C414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410:E414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410:F414," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C409" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410:B414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410:C414," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D409" s="18"/>
       <c r="E409" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410:E414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410:F414," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F409" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D410:D414)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410:E414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410:F414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410:B414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410:C414," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G409" s="14" t="str">
         <f>'data'!$B$31</f>
@@ -15399,17 +15399,17 @@
         <f>'data'!$B$78</f>
       </c>
       <c r="J409" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L410:L414)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410:J414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410:K414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410:M414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410:N414," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K409" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410:J414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410:K414," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L409" s="18"/>
       <c r="M409" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410:M414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410:N414," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N409" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L410:L414)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410:M414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410:N414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410:J414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410:K414," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O409" s="14" t="str">
         <f>'data'!$B$76</f>
@@ -15568,17 +15568,17 @@
         <f>'data'!$B$33</f>
       </c>
       <c r="B417" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D418:D422)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418:B422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418:C422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418:E422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418:F422," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C417" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418:B422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418:C422," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D417" s="18"/>
       <c r="E417" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418:E422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418:F422," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F417" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D418:D422)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418:E422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418:F422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418:B422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418:C422," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G417" s="14" t="str">
         <f>'data'!$B$32</f>
@@ -15587,17 +15587,17 @@
         <f>'data'!$B$78</f>
       </c>
       <c r="J417" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L418:L422)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418:J422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418:K422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418:M422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418:N422," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K417" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418:J422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418:K422," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L417" s="18"/>
       <c r="M417" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418:M422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418:N422," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N417" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L418:L422)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418:M422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418:N422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418:J422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418:K422," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O417" s="14" t="str">
         <f>'data'!$B$77</f>
@@ -16126,17 +16126,17 @@
         <f>'data'!$B$35</f>
       </c>
       <c r="B444" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D445:D449)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445:B449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445:C449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445:E449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445:F449," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C444" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445:B449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445:C449," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D444" s="18"/>
       <c r="E444" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445:E449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445:F449," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F444" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D445:D449)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445:E449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445:F449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445:B449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445:C449," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G444" s="14" t="str">
         <f>'data'!$B$34</f>
@@ -16145,17 +16145,17 @@
         <f>'data'!$B$80</f>
       </c>
       <c r="J444" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L445:L449)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445:J449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445:K449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445:M449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445:N449," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K444" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445:J449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445:K449," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L444" s="18"/>
       <c r="M444" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445:M449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445:N449," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N444" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L445:L449)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445:M449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445:N449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445:J449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445:K449," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O444" s="14" t="str">
         <f>'data'!$B$79</f>
@@ -16314,17 +16314,17 @@
         <f>'data'!$B$36</f>
       </c>
       <c r="B452" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D453:D457)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453:B457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453:C457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453:E457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453:F457," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C452" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453:B457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453:C457," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D452" s="18"/>
       <c r="E452" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453:E457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453:F457," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F452" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D453:D457)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453:E457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453:F457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453:B457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453:C457," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G452" s="14" t="str">
         <f>'data'!$B$34</f>
@@ -16333,17 +16333,17 @@
         <f>'data'!$B$81</f>
       </c>
       <c r="J452" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L453:L457)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453:J457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453:K457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453:M457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453:N457," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K452" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453:J457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453:K457," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L452" s="18"/>
       <c r="M452" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453:M457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453:N457," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N452" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L453:L457)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453:M457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453:N457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453:J457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453:K457," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O452" s="14" t="str">
         <f>'data'!$B$79</f>
@@ -16502,17 +16502,17 @@
         <f>'data'!$B$36</f>
       </c>
       <c r="B460" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D461:D465)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461:B465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461:C465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461:E465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461:F465," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C460" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461:B465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461:C465," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D460" s="18"/>
       <c r="E460" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461:E465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461:F465," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F460" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D461:D465)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461:E465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461:F465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461:B465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461:C465," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G460" s="14" t="str">
         <f>'data'!$B$35</f>
@@ -16521,17 +16521,17 @@
         <f>'data'!$B$81</f>
       </c>
       <c r="J460" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L461:L465)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461:J465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461:K465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461:M465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461:N465," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K460" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461:J465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461:K465," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L460" s="18"/>
       <c r="M460" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461:M465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461:N465," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N460" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L461:L465)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461:M465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461:N465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461:J465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461:K465," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O460" s="14" t="str">
         <f>'data'!$B$80</f>
@@ -17060,17 +17060,17 @@
         <f>'data'!$B$38</f>
       </c>
       <c r="B487" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D488:D492)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488:B492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488:C492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488:E492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488:F492," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C487" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488:B492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488:C492," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D487" s="18"/>
       <c r="E487" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488:E492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488:F492," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F487" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D488:D492)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488:E492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488:F492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488:B492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488:C492," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G487" s="14" t="str">
         <f>'data'!$B$37</f>
@@ -17079,17 +17079,17 @@
         <f>'data'!$B$83</f>
       </c>
       <c r="J487" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L488:L492)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488:J492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488:K492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488:M492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488:N492," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K487" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488:J492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488:K492," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L487" s="18"/>
       <c r="M487" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488:M492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488:N492," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N487" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L488:L492)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488:M492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488:N492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488:J492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488:K492," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O487" s="14" t="str">
         <f>'data'!$B$82</f>
@@ -17248,17 +17248,17 @@
         <f>'data'!$B$39</f>
       </c>
       <c r="B495" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D496:D500)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496:B500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496:C500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496:E500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496:F500," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C495" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496:B500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496:C500," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D495" s="18"/>
       <c r="E495" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496:E500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496:F500," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F495" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D496:D500)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496:E500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496:F500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496:B500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496:C500," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G495" s="14" t="str">
         <f>'data'!$B$37</f>
@@ -17267,17 +17267,17 @@
         <f>'data'!$B$84</f>
       </c>
       <c r="J495" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L496:L500)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496:J500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496:K500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496:M500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496:N500," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K495" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496:J500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496:K500," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L495" s="18"/>
       <c r="M495" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496:M500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496:N500," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N495" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L496:L500)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496:M500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496:N500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496:J500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496:K500," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O495" s="14" t="str">
         <f>'data'!$B$82</f>
@@ -17436,17 +17436,17 @@
         <f>'data'!$B$39</f>
       </c>
       <c r="B503" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D504:D508)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504:B508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504:C508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504:E508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504:F508," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C503" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504:B508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504:C508," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D503" s="18"/>
       <c r="E503" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504:E508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504:F508," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F503" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D504:D508)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504:E508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504:F508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504:B508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504:C508," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G503" s="14" t="str">
         <f>'data'!$B$38</f>
@@ -17455,17 +17455,17 @@
         <f>'data'!$B$84</f>
       </c>
       <c r="J503" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L504:L508)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504:J508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504:K508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504:M508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504:N508," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K503" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504:J508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504:K508," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L503" s="18"/>
       <c r="M503" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504:M508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504:N508," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N503" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L504:L508)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504:M508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504:N508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504:J508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504:K508," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O503" s="14" t="str">
         <f>'data'!$B$83</f>
@@ -17994,17 +17994,17 @@
         <f>'data'!$B$41</f>
       </c>
       <c r="B530" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D531:D535)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531:B535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531:C535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531:E535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531:F535," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C530" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531:B535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531:C535," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D530" s="18"/>
       <c r="E530" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531:E535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531:F535," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F530" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D531:D535)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531:E535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531:F535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531:B535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531:C535," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G530" s="14" t="str">
         <f>'data'!$B$40</f>
@@ -18013,17 +18013,17 @@
         <f>'data'!$B$86</f>
       </c>
       <c r="J530" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L531:L535)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531:J535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531:K535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531:M535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531:N535," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K530" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531:J535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531:K535," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L530" s="18"/>
       <c r="M530" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531:M535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531:N535," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N530" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L531:L535)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531:M535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531:N535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531:J535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531:K535," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O530" s="14" t="str">
         <f>'data'!$B$85</f>
@@ -18182,17 +18182,17 @@
         <f>'data'!$B$42</f>
       </c>
       <c r="B538" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D539:D543)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539:B543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539:C543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539:E543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539:F543," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C538" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539:B543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539:C543," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D538" s="18"/>
       <c r="E538" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539:E543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539:F543," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F538" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D539:D543)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539:E543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539:F543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539:B543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539:C543," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G538" s="14" t="str">
         <f>'data'!$B$40</f>
@@ -18201,17 +18201,17 @@
         <f>'data'!$B$87</f>
       </c>
       <c r="J538" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L539:L543)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539:J543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539:K543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539:M543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539:N543," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K538" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539:J543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539:K543," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L538" s="18"/>
       <c r="M538" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539:M543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539:N543," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N538" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L539:L543)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539:M543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539:N543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539:J543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539:K543," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O538" s="14" t="str">
         <f>'data'!$B$85</f>
@@ -18370,17 +18370,17 @@
         <f>'data'!$B$42</f>
       </c>
       <c r="B546" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D547:D551)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547:B551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547:C551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547:E551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547:F551," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C546" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547:B551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547:C551," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D546" s="18"/>
       <c r="E546" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547:E551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547:F551," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F546" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D547:D551)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547:E551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547:F551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547:B551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547:C551," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G546" s="14" t="str">
         <f>'data'!$B$41</f>
@@ -18389,17 +18389,17 @@
         <f>'data'!$B$87</f>
       </c>
       <c r="J546" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L547:L551)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547:J551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547:K551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547:M551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547:N551," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K546" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547:J551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547:K551," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L546" s="18"/>
       <c r="M546" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547:M551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547:N551," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N546" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L547:L551)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547:M551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547:N551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547:J551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547:K551," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O546" s="14" t="str">
         <f>'data'!$B$86</f>
@@ -18928,17 +18928,17 @@
         <f>'data'!$B$44</f>
       </c>
       <c r="B573" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D574:D578)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574:B578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574:C578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574:E578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574:F578," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C573" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574:B578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574:C578," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D573" s="18"/>
       <c r="E573" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574:E578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574:F578," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F573" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D574:D578)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574:E578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574:F578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574:B578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574:C578," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G573" s="14" t="str">
         <f>'data'!$B$43</f>
@@ -18947,17 +18947,17 @@
         <f>'data'!$B$89</f>
       </c>
       <c r="J573" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L574:L578)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574:J578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574:K578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574:M578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574:N578," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K573" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574:J578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574:K578," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L573" s="18"/>
       <c r="M573" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574:M578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574:N578," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N573" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L574:L578)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574:M578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574:N578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574:J578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574:K578," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O573" s="14" t="str">
         <f>'data'!$B$88</f>
@@ -19116,17 +19116,17 @@
         <f>'data'!$B$45</f>
       </c>
       <c r="B581" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D582:D586)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582:B586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582:C586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582:E586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582:F586," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C581" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582:B586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582:C586," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D581" s="18"/>
       <c r="E581" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582:E586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582:F586," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F581" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D582:D586)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582:E586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582:F586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582:B586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582:C586," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G581" s="14" t="str">
         <f>'data'!$B$43</f>
@@ -19135,17 +19135,17 @@
         <f>'data'!$B$90</f>
       </c>
       <c r="J581" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L582:L586)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582:J586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582:K586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582:M586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582:N586," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K581" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582:J586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582:K586," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L581" s="18"/>
       <c r="M581" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582:M586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582:N586," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N581" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L582:L586)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582:M586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582:N586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582:J586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582:K586," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O581" s="14" t="str">
         <f>'data'!$B$88</f>
@@ -19304,17 +19304,17 @@
         <f>'data'!$B$45</f>
       </c>
       <c r="B589" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D590:D594)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590:B594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590:C594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590:E594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590:F594," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C589" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590:B594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590:C594," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D589" s="18"/>
       <c r="E589" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590:E594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590:F594," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F589" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D590:D594)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590:E594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590:F594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590:B594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590:C594," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G589" s="14" t="str">
         <f>'data'!$B$44</f>
@@ -19323,17 +19323,17 @@
         <f>'data'!$B$90</f>
       </c>
       <c r="J589" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L590:L594)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590:J594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590:K594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590:M594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590:N594," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K589" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590:J594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590:K594," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L589" s="18"/>
       <c r="M589" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590:M594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590:N594," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N589" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L590:L594)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590:M594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590:N594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590:J594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590:K594," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O589" s="14" t="str">
         <f>'data'!$B$89</f>
@@ -19862,17 +19862,17 @@
         <f>'data'!$B$47</f>
       </c>
       <c r="B616" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D617:D621)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617:B621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617:C621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617:E621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617:F621," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C616" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617:B621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617:C621," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D616" s="18"/>
       <c r="E616" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617:E621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617:F621," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F616" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D617:D621)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617:E621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617:F621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617:B621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617:C621," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G616" s="14" t="str">
         <f>'data'!$B$46</f>
@@ -19881,17 +19881,17 @@
         <f>'data'!$B$92</f>
       </c>
       <c r="J616" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L617:L621)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617:J621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617:K621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617:M621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617:N621," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K616" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617:J621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617:K621," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L616" s="18"/>
       <c r="M616" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617:M621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617:N621," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N616" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L617:L621)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617:M621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617:N621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617:J621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617:K621," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O616" s="14" t="str">
         <f>'data'!$B$91</f>
@@ -20050,17 +20050,17 @@
         <f>'data'!$B$48</f>
       </c>
       <c r="B624" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D625:D629)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625:B629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625:C629," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625:E629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625:F629," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D628)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C628," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F628," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D629)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C629," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F629," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C624" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625:B629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625:C629," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C629," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D624" s="18"/>
       <c r="E624" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625:E629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625:F629," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F629," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F624" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D625:D629)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625:E629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625:F629," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625:B629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625:C629," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D628)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F628," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C628," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D629)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F629," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C629," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G624" s="14" t="str">
         <f>'data'!$B$46</f>
@@ -20069,17 +20069,17 @@
         <f>'data'!$B$93</f>
       </c>
       <c r="J624" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L625:L629)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J625:J629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K625:K629," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M625:M629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N625:N629," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N627," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L628)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K628," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N628," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L629)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K629," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N629," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K624" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J625:J629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K625:K629," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K629," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L624" s="18"/>
       <c r="M624" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M625:M629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N625:N629," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N629," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N624" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L625:L629)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M625:M629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N625:N629," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J625:J629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K625:K629," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K627," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L628)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N628," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K628," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L629)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N629," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K629," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O624" s="14" t="str">
         <f>'data'!$B$91</f>
@@ -20238,17 +20238,17 @@
         <f>'data'!$B$48</f>
       </c>
       <c r="B632" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D633:D637)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B633:B637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C633:C637," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E633:E637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F633:F637," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D633)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C633," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F633," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D634)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C634," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F634," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D635)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C635," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F635," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D636)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C636," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F636," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D637)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C637," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F637," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C632" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B633:B637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C633:C637," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C637," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D632" s="18"/>
       <c r="E632" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E633:E637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F633:F637," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F637," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F632" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D633:D637)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E633:E637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F633:F637," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B633:B637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C633:C637," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D633)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F633," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C633," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D634)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F634," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C634," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D635)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F635," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C635," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D636)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F636," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C636," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D637)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F637," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C637," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G632" s="14" t="str">
         <f>'data'!$B$47</f>
@@ -20257,17 +20257,17 @@
         <f>'data'!$B$93</f>
       </c>
       <c r="J632" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L633:L637)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J633:J637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K633:K637," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M633:M637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N633:N637," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L633)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K633," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N633," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L634)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K634," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N634," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L635)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K635," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N635," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L636)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K636," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N636," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L637)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K637," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N637," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K632" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J633:J637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K633:K637," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K637," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L632" s="18"/>
       <c r="M632" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M633:M637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N633:N637," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N637," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N632" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L633:L637)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M633:M637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N633:N637," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J633:J637," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K633:K637," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L633)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N633," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J633," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K633," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L634)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N634," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J634," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K634," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L635)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N635," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J635," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K635," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L636)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N636," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J636," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K636," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L637)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N637," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J637," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K637," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O632" s="14" t="str">
         <f>'data'!$B$92</f>
@@ -21073,17 +21073,17 @@
         <v>348</v>
       </c>
       <c r="B12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G12" s="14" t="s">
         <v>348</v>
@@ -21092,17 +21092,17 @@
         <v>348</v>
       </c>
       <c r="J12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O12" s="14" t="s">
         <v>348</v>
@@ -21357,17 +21357,17 @@
         <v>348</v>
       </c>
       <c r="B28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G28" s="14" t="s">
         <v>348</v>
@@ -21376,17 +21376,17 @@
         <v>348</v>
       </c>
       <c r="J28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L28" s="14"/>
       <c r="M28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O28" s="14" t="s">
         <v>348</v>
@@ -21641,17 +21641,17 @@
         <v>348</v>
       </c>
       <c r="B44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G44" s="14" t="s">
         <v>348</v>
@@ -21660,17 +21660,17 @@
         <v>348</v>
       </c>
       <c r="J44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L37:L41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37:J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37:K41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37:M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37:N41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37:J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37:K41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L44" s="14"/>
       <c r="M44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37:M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37:N41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L37:L41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37:M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37:N41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37:J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37:K41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O44" s="14" t="s">
         <v>348</v>
@@ -21925,17 +21925,17 @@
         <v>348</v>
       </c>
       <c r="B60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D53:D57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53:B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53:C57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53:E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53:F57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53:B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53:C57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53:E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53:F57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D53:D57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53:E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53:F57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53:B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53:C57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G60" s="14" t="s">
         <v>348</v>
@@ -21944,17 +21944,17 @@
         <v>348</v>
       </c>
       <c r="J60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L53:L57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53:J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53:K57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53:M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53:N57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53:J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53:K57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L60" s="14"/>
       <c r="M60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53:M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53:N57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L53:L57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53:M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53:N57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53:J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53:K57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O60" s="14" t="s">
         <v>348</v>
@@ -22209,17 +22209,17 @@
         <v>348</v>
       </c>
       <c r="B76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D69:D73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69:B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69:C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69:E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69:F73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69:B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69:C73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69:E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69:F73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D69:D73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69:E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69:F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69:B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69:C73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G76" s="14" t="s">
         <v>348</v>
@@ -22228,17 +22228,17 @@
         <v>348</v>
       </c>
       <c r="J76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L69:L73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69:J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69:K73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69:M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69:N73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69:J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69:K73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L76" s="14"/>
       <c r="M76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69:M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69:N73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L69:L73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69:M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69:N73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69:J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69:K73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O76" s="14" t="s">
         <v>348</v>
@@ -22493,17 +22493,17 @@
         <v>348</v>
       </c>
       <c r="B92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D85:D89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85:B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85:C89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85:E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85:F89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85:B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85:C89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D92" s="14"/>
       <c r="E92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85:E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85:F89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D85:D89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85:E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85:F89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85:B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85:C89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G92" s="14" t="s">
         <v>348</v>
@@ -22512,17 +22512,17 @@
         <v>348</v>
       </c>
       <c r="J92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L85:L89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85:J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85:K89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85:M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85:N89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85:J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85:K89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L92" s="14"/>
       <c r="M92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85:M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85:N89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L85:L89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85:M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85:N89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85:J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85:K89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O92" s="14" t="s">
         <v>348</v>
@@ -22777,17 +22777,17 @@
         <v>348</v>
       </c>
       <c r="B108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D101:D105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D101:D105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G108" s="14" t="s">
         <v>348</v>
@@ -22796,17 +22796,17 @@
         <v>348</v>
       </c>
       <c r="J108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L101:L105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L108" s="14"/>
       <c r="M108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L101:L105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O108" s="14" t="s">
         <v>348</v>
@@ -23061,17 +23061,17 @@
         <v>348</v>
       </c>
       <c r="B124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D117:D121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D117:D121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G124" s="14" t="s">
         <v>348</v>
@@ -23080,17 +23080,17 @@
         <v>348</v>
       </c>
       <c r="J124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L117:L121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L124" s="14"/>
       <c r="M124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L117:L121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O124" s="14" t="s">
         <v>348</v>
@@ -23345,17 +23345,17 @@
         <v>348</v>
       </c>
       <c r="B140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D133:D137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133:B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133:C137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133:E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133:F137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133:B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133:C137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D140" s="14"/>
       <c r="E140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133:E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133:F137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D133:D137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133:E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133:F137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133:B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133:C137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G140" s="14" t="s">
         <v>348</v>
@@ -23364,17 +23364,17 @@
         <v>348</v>
       </c>
       <c r="J140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L133:L137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133:J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133:K137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133:M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133:N137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133:J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133:K137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L140" s="14"/>
       <c r="M140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133:M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133:N137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L133:L137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133:M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133:N137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133:J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133:K137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O140" s="14" t="s">
         <v>348</v>
@@ -23629,17 +23629,17 @@
         <v>348</v>
       </c>
       <c r="B156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D149:D153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149:B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149:C153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149:E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149:F153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149:B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149:C153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D156" s="14"/>
       <c r="E156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149:E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149:F153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D149:D153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149:E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149:F153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149:B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149:C153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G156" s="14" t="s">
         <v>348</v>
@@ -23648,17 +23648,17 @@
         <v>348</v>
       </c>
       <c r="J156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L149:L153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149:J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149:K153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149:M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149:N153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149:J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149:K153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L156" s="14"/>
       <c r="M156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149:M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149:N153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L149:L153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149:M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149:N153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149:J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149:K153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O156" s="14" t="s">
         <v>348</v>
@@ -23913,17 +23913,17 @@
         <v>348</v>
       </c>
       <c r="B172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D165:D169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165:B169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165:C169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165:E169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165:F169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165:B169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165:C169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D172" s="14"/>
       <c r="E172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165:E169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165:F169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D165:D169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165:E169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165:F169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165:B169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165:C169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G172" s="14" t="s">
         <v>348</v>
@@ -23932,17 +23932,17 @@
         <v>348</v>
       </c>
       <c r="J172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L165:L169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165:J169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165:K169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165:M169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165:N169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165:J169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165:K169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L172" s="14"/>
       <c r="M172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165:M169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165:N169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L165:L169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165:M169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165:N169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165:J169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165:K169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O172" s="14" t="s">
         <v>348</v>
@@ -24197,17 +24197,17 @@
         <v>348</v>
       </c>
       <c r="B188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D181:D185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181:B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181:C185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181:E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181:F185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181:B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181:C185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D188" s="14"/>
       <c r="E188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181:E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181:F185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D181:D185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181:E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181:F185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181:B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181:C185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G188" s="14" t="s">
         <v>348</v>
@@ -24216,17 +24216,17 @@
         <v>348</v>
       </c>
       <c r="J188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L181:L185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181:J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181:K185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181:M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181:N185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181:J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181:K185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L188" s="14"/>
       <c r="M188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181:M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181:N185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L181:L185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181:M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181:N185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181:J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181:K185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O188" s="14" t="s">
         <v>348</v>
@@ -24481,17 +24481,17 @@
         <v>348</v>
       </c>
       <c r="B204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D197:D201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197:B201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197:C201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197:E201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197:F201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197:B201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197:C201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D204" s="14"/>
       <c r="E204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197:E201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197:F201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D197:D201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197:E201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197:F201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197:B201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197:C201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G204" s="14" t="s">
         <v>348</v>
@@ -24500,17 +24500,17 @@
         <v>348</v>
       </c>
       <c r="J204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L197:L201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197:J201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197:K201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197:M201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197:N201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197:J201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197:K201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L204" s="14"/>
       <c r="M204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197:M201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197:N201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L197:L201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197:M201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197:N201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197:J201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197:K201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O204" s="14" t="s">
         <v>348</v>
@@ -24765,17 +24765,17 @@
         <v>348</v>
       </c>
       <c r="B220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D213:D217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213:B217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213:C217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213:E217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213:F217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213:B217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213:C217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D220" s="14"/>
       <c r="E220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213:E217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213:F217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D213:D217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213:E217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213:F217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213:B217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213:C217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G220" s="14" t="s">
         <v>348</v>
@@ -24784,17 +24784,17 @@
         <v>348</v>
       </c>
       <c r="J220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L213:L217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213:J217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213:K217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213:M217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213:N217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213:J217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213:K217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L220" s="14"/>
       <c r="M220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213:M217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213:N217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L213:L217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213:M217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213:N217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213:J217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213:K217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O220" s="14" t="s">
         <v>348</v>
@@ -25049,17 +25049,17 @@
         <v>348</v>
       </c>
       <c r="B241" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D234:D238)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234:B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234:C238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234:E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234:F238," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C235," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F235," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C241" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234:B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234:C238," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D241" s="14"/>
       <c r="E241" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234:E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234:F238," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F241" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D234:D238)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234:E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234:F238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234:B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234:C238," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F235," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C235," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G241" s="14" t="s">
         <v>348</v>
@@ -25068,17 +25068,17 @@
         <v>348</v>
       </c>
       <c r="J241" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L234:L238)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234:J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234:K238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234:M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234:N238," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K235," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N235," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K241" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234:J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234:K238," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L241" s="14"/>
       <c r="M241" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234:M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234:N238," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N241" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L234:L238)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234:M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234:N238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234:J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234:K238," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L235)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N235," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J235," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K235," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O241" s="14" t="s">
         <v>348</v>
@@ -25333,17 +25333,17 @@
         <v>348</v>
       </c>
       <c r="B257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D250:D254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250:B254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250:C254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250:E254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250:F254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250:B254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250:C254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D257" s="14"/>
       <c r="E257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250:E254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250:F254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D250:D254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250:E254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250:F254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250:B254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250:C254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G257" s="14" t="s">
         <v>348</v>
@@ -25352,17 +25352,17 @@
         <v>348</v>
       </c>
       <c r="J257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L250:L254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250:J254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250:K254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250:M254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250:N254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250:J254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250:K254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L257" s="14"/>
       <c r="M257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250:M254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250:N254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L250:L254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250:M254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250:N254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250:J254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250:K254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O257" s="14" t="s">
         <v>348</v>
@@ -25617,17 +25617,17 @@
         <v>348</v>
       </c>
       <c r="B273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D266:D270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266:B270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266:C270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266:E270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266:F270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266:B270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266:C270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D273" s="14"/>
       <c r="E273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266:E270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266:F270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D266:D270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266:E270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266:F270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266:B270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266:C270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G273" s="14" t="s">
         <v>348</v>
@@ -25636,17 +25636,17 @@
         <v>348</v>
       </c>
       <c r="J273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L266:L270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266:J270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266:K270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266:M270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266:N270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266:J270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266:K270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L273" s="14"/>
       <c r="M273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266:M270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266:N270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L266:L270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266:M270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266:N270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266:J270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266:K270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O273" s="14" t="s">
         <v>348</v>
@@ -25901,17 +25901,17 @@
         <v>348</v>
       </c>
       <c r="B289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D282:D286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282:B286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282:C286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282:E286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282:F286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282:B286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282:C286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D289" s="14"/>
       <c r="E289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282:E286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282:F286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D282:D286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282:E286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282:F286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282:B286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282:C286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G289" s="14" t="s">
         <v>348</v>
@@ -25920,17 +25920,17 @@
         <v>348</v>
       </c>
       <c r="J289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L282:L286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282:J286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282:K286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282:M286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282:N286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282:J286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282:K286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L289" s="14"/>
       <c r="M289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282:M286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282:N286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L282:L286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282:M286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282:N286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282:J286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282:K286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O289" s="14" t="s">
         <v>348</v>
@@ -26185,17 +26185,17 @@
         <v>348</v>
       </c>
       <c r="B305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D298:D302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298:B302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298:C302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298:E302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298:F302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298:B302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298:C302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D305" s="14"/>
       <c r="E305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298:E302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298:F302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D298:D302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298:E302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298:F302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298:B302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298:C302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G305" s="14" t="s">
         <v>348</v>
@@ -26204,17 +26204,17 @@
         <v>348</v>
       </c>
       <c r="J305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L298:L302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298:J302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298:K302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298:M302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298:N302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298:J302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298:K302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L305" s="14"/>
       <c r="M305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298:M302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298:N302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L298:L302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298:M302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298:N302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298:J302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298:K302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O305" s="14" t="s">
         <v>348</v>
@@ -26469,17 +26469,17 @@
         <v>348</v>
       </c>
       <c r="B321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D314:D318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D321" s="14"/>
       <c r="E321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D314:D318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G321" s="14" t="s">
         <v>348</v>
@@ -26488,17 +26488,17 @@
         <v>348</v>
       </c>
       <c r="J321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L314:L318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L321" s="14"/>
       <c r="M321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L314:L318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O321" s="14" t="s">
         <v>348</v>
@@ -26753,17 +26753,17 @@
         <v>348</v>
       </c>
       <c r="B337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D330:D334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330:B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330:C334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330:E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330:F334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330:B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330:C334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D337" s="14"/>
       <c r="E337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330:E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330:F334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D330:D334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330:E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330:F334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330:B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330:C334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G337" s="14" t="s">
         <v>348</v>
@@ -26772,17 +26772,17 @@
         <v>348</v>
       </c>
       <c r="J337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L330:L334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330:J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330:K334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330:M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330:N334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330:J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330:K334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L337" s="14"/>
       <c r="M337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330:M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330:N334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L330:L334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330:M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330:N334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330:J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330:K334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O337" s="14" t="s">
         <v>348</v>
@@ -27037,17 +27037,17 @@
         <v>348</v>
       </c>
       <c r="B353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D346:D350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346:B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346:C350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346:E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346:F350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346:B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346:C350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D353" s="14"/>
       <c r="E353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346:E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346:F350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D346:D350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346:E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346:F350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346:B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346:C350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G353" s="14" t="s">
         <v>348</v>
@@ -27056,17 +27056,17 @@
         <v>348</v>
       </c>
       <c r="J353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L346:L350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346:J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346:K350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346:M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346:N350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346:J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346:K350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L353" s="14"/>
       <c r="M353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346:M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346:N350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L346:L350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346:M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346:N350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346:J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346:K350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O353" s="14" t="s">
         <v>348</v>
@@ -27321,17 +27321,17 @@
         <v>348</v>
       </c>
       <c r="B374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D367:D371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367:B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367:C371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367:E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367:F371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367:B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367:C371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D374" s="14"/>
       <c r="E374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367:E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367:F371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D367:D371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367:E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367:F371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367:B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367:C371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G374" s="14" t="s">
         <v>348</v>
@@ -27340,17 +27340,17 @@
         <v>348</v>
       </c>
       <c r="J374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L367:L371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367:J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367:K371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367:M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367:N371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367:J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367:K371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L374" s="14"/>
       <c r="M374" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367:M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367:N371," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N374" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L367:L371)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367:M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367:N371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367:J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367:K371," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O374" s="14" t="s">
         <v>348</v>
@@ -27605,17 +27605,17 @@
         <v>348</v>
       </c>
       <c r="B390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D383:D387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383:B387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383:C387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383:E387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383:F387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383:B387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383:C387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D390" s="14"/>
       <c r="E390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383:E387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383:F387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D383:D387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383:E387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383:F387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383:B387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383:C387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G390" s="14" t="s">
         <v>348</v>
@@ -27624,17 +27624,17 @@
         <v>348</v>
       </c>
       <c r="J390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L383:L387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383:J387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383:K387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383:M387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383:N387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383:J387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383:K387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L390" s="14"/>
       <c r="M390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383:M387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383:N387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L383:L387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383:M387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383:N387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383:J387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383:K387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O390" s="14" t="s">
         <v>348</v>
@@ -27889,17 +27889,17 @@
         <v>348</v>
       </c>
       <c r="B406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D399:D403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399:B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399:C403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399:E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399:F403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399:B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399:C403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D406" s="14"/>
       <c r="E406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399:E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399:F403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D399:D403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399:E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399:F403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399:B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399:C403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G406" s="14" t="s">
         <v>348</v>
@@ -27908,17 +27908,17 @@
         <v>348</v>
       </c>
       <c r="J406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L399:L403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399:J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399:K403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399:M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399:N403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399:J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399:K403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L406" s="14"/>
       <c r="M406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399:M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399:N403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L399:L403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399:M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399:N403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399:J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399:K403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O406" s="14" t="s">
         <v>348</v>
@@ -28173,17 +28173,17 @@
         <v>348</v>
       </c>
       <c r="B422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D415:D419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415:B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415:C419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415:E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415:F419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415:B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415:C419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D422" s="14"/>
       <c r="E422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415:E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415:F419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D415:D419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415:E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415:F419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415:B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415:C419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G422" s="14" t="s">
         <v>348</v>
@@ -28192,17 +28192,17 @@
         <v>348</v>
       </c>
       <c r="J422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L415:L419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415:J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415:K419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415:M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415:N419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415:J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415:K419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L422" s="14"/>
       <c r="M422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415:M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415:N419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L415:L419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415:M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415:N419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415:J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415:K419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O422" s="14" t="s">
         <v>348</v>
@@ -28457,17 +28457,17 @@
         <v>348</v>
       </c>
       <c r="B443" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D436:D440)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436:B440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436:C440," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436:E440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436:F440," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D440)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C440," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F440," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C443" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436:B440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436:C440," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C440," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D443" s="14"/>
       <c r="E443" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436:E440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436:F440," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F440," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F443" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D436:D440)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436:E440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436:F440," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436:B440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436:C440," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D440)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F440," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C440," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G443" s="14" t="s">
         <v>348</v>
@@ -28476,17 +28476,17 @@
         <v>348</v>
       </c>
       <c r="J443" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L436:L440)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436:J440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436:K440," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436:M440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436:N440," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L440)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K440," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N440," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K443" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436:J440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436:K440," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K440," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L443" s="14"/>
       <c r="M443" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436:M440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436:N440," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N440," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N443" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L436:L440)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436:M440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436:N440," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436:J440," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436:K440," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L440)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N440," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J440," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K440," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O443" s="14" t="s">
         <v>348</v>
@@ -28741,17 +28741,17 @@
         <v>348</v>
       </c>
       <c r="B459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D452:D456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452:B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452:C456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452:E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452:F456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452:B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452:C456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D459" s="14"/>
       <c r="E459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452:E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452:F456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D452:D456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452:E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452:F456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452:B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452:C456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G459" s="14" t="s">
         <v>348</v>
@@ -28760,17 +28760,17 @@
         <v>348</v>
       </c>
       <c r="J459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L452:L456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452:J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452:K456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452:M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452:N456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452:J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452:K456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L459" s="14"/>
       <c r="M459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452:M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452:N456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L452:L456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452:M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452:N456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452:J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452:K456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O459" s="14" t="s">
         <v>348</v>
@@ -29025,17 +29025,17 @@
         <v>348</v>
       </c>
       <c r="B480" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D473:D477)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B473:B477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C473:C477," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E473:E477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F473:F477," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D473)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C473," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F473," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D474)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C474," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F474," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D475)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C475," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F475," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D476)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C476," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F476," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D477)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C477," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F477," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C480" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B473:B477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C473:C477," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C477," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D480" s="14"/>
       <c r="E480" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E473:E477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F473:F477," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F477," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F480" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D473:D477)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E473:E477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F473:F477," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B473:B477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C473:C477," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D473)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F473," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C473," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D474)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F474," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C474," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D475)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F475," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C475," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D476)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F476," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C476," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D477)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F477," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C477," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G480" s="14" t="s">
         <v>348</v>
@@ -29044,17 +29044,17 @@
         <v>348</v>
       </c>
       <c r="J480" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L473:L477)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J473:J477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K473:K477," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M473:M477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N473:N477," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L473)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K473," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N473," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L474)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K474," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N474," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L475)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K475," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N475," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L476)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K476," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N476," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L477)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K477," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N477," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K480" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J473:J477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K473:K477," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K477," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L480" s="14"/>
       <c r="M480" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M473:M477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N473:N477," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N477," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N480" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L473:L477)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M473:M477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N473:N477," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J473:J477," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K473:K477," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L473)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N473," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J473," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K473," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L474)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N474," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J474," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K474," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L475)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N475," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J475," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K475," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L476)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N476," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J476," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K476," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L477)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N477," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J477," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K477," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O480" s="14" t="s">
         <v>348</v>
@@ -29206,17 +29206,17 @@
         <v>348</v>
       </c>
       <c r="B501" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D494:D498)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494:B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494:C498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494:E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494:F498," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C501" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494:B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494:C498," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D501" s="14"/>
       <c r="E501" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494:E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494:F498," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F501" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D494:D498)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494:E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494:F498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494:B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494:C498," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G501" s="14" t="s">
         <v>348</v>

--- a/pools-example-large-teams.xlsx
+++ b/pools-example-large-teams.xlsx
@@ -6631,17 +6631,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -6650,17 +6650,17 @@
         <f>'data'!$B$50</f>
       </c>
       <c r="J4" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L4" s="18"/>
       <c r="M4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N4" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O4" s="14" t="str">
         <f>'data'!$B$49</f>
@@ -6819,17 +6819,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B12" s="14" t="str">
-        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -6838,17 +6838,17 @@
         <f>'data'!$B$51</f>
       </c>
       <c r="J12" s="14" t="str">
-        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O12" s="14" t="str">
         <f>'data'!$B$49</f>
@@ -7007,17 +7007,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B20" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F20" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G20" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -7026,17 +7026,17 @@
         <f>'data'!$B$51</f>
       </c>
       <c r="J20" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L20" s="18"/>
       <c r="M20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N20" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O20" s="14" t="str">
         <f>'data'!$B$50</f>
@@ -7182,17 +7182,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B28" s="14" t="str">
-        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F28" s="14" t="str">
-        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G28" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -7720,17 +7720,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B57" s="14" t="str">
-        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D57" s="18"/>
       <c r="E57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F57" s="14" t="str">
-        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G57" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -7739,17 +7739,17 @@
         <f>'data'!$B$53</f>
       </c>
       <c r="J57" s="14" t="str">
-        <f>IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N57" s="14" t="str">
-        <f>IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K62," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O57" s="14" t="str">
         <f>'data'!$B$52</f>
@@ -7908,17 +7908,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B65" s="14" t="str">
-        <f>IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C65" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D65" s="18"/>
       <c r="E65" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F65" s="14" t="str">
-        <f>IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G65" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -7927,17 +7927,17 @@
         <f>'data'!$B$54</f>
       </c>
       <c r="J65" s="14" t="str">
-        <f>IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K65" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N65" s="14" t="str">
-        <f>IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O65" s="14" t="str">
         <f>'data'!$B$52</f>
@@ -8096,17 +8096,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B73" s="14" t="str">
-        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C73" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F73" s="14" t="str">
-        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G73" s="14" t="str">
         <f>'data'!$B$8</f>
@@ -8115,17 +8115,17 @@
         <f>'data'!$B$54</f>
       </c>
       <c r="J73" s="14" t="str">
-        <f>IF(UPPER(L74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K73" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N73" s="14" t="str">
-        <f>IF(UPPER(L74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K78," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O73" s="14" t="str">
         <f>'data'!$B$53</f>
@@ -8654,17 +8654,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B100" s="14" t="str">
-        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C100" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D100" s="18"/>
       <c r="E100" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F100" s="14" t="str">
-        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G100" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -8673,17 +8673,17 @@
         <f>'data'!$B$56</f>
       </c>
       <c r="J100" s="14" t="str">
-        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K100" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L100" s="18"/>
       <c r="M100" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N100" s="14" t="str">
-        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O100" s="14" t="str">
         <f>'data'!$B$55</f>
@@ -8842,17 +8842,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="B108" s="14" t="str">
-        <f>IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F108" s="14" t="str">
-        <f>IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G108" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -8861,17 +8861,17 @@
         <f>'data'!$B$57</f>
       </c>
       <c r="J108" s="14" t="str">
-        <f>IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L108" s="18"/>
       <c r="M108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N108" s="14" t="str">
-        <f>IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K113," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O108" s="14" t="str">
         <f>'data'!$B$55</f>
@@ -9030,17 +9030,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="B116" s="14" t="str">
-        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C116" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D116" s="18"/>
       <c r="E116" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F116" s="14" t="str">
-        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G116" s="14" t="str">
         <f>'data'!$B$11</f>
@@ -9049,17 +9049,17 @@
         <f>'data'!$B$57</f>
       </c>
       <c r="J116" s="14" t="str">
-        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K116" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L116" s="18"/>
       <c r="M116" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N116" s="14" t="str">
-        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O116" s="14" t="str">
         <f>'data'!$B$56</f>
@@ -9588,17 +9588,17 @@
         <f>'data'!$B$14</f>
       </c>
       <c r="B143" s="14" t="str">
-        <f>IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C143" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D143" s="18"/>
       <c r="E143" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F143" s="14" t="str">
-        <f>IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F147," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C147," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G143" s="14" t="str">
         <f>'data'!$B$13</f>
@@ -9607,17 +9607,17 @@
         <f>'data'!$B$59</f>
       </c>
       <c r="J143" s="14" t="str">
-        <f>IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K143" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L143" s="18"/>
       <c r="M143" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N143" s="14" t="str">
-        <f>IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L147)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N147," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J147," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K147," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K148," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O143" s="14" t="str">
         <f>'data'!$B$58</f>
@@ -9776,17 +9776,17 @@
         <f>'data'!$B$15</f>
       </c>
       <c r="B151" s="14" t="str">
-        <f>IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C151" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D151" s="18"/>
       <c r="E151" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F151" s="14" t="str">
-        <f>IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F155," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C155," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C156," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G151" s="14" t="str">
         <f>'data'!$B$13</f>
@@ -9795,17 +9795,17 @@
         <f>'data'!$B$60</f>
       </c>
       <c r="J151" s="14" t="str">
-        <f>IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K151" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L151" s="18"/>
       <c r="M151" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N151" s="14" t="str">
-        <f>IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L155)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N155," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J155," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K155," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L156)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N156," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J156," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K156," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O151" s="14" t="str">
         <f>'data'!$B$58</f>
@@ -9964,17 +9964,17 @@
         <f>'data'!$B$15</f>
       </c>
       <c r="B159" s="14" t="str">
-        <f>IF(UPPER(D160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C159" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D159" s="18"/>
       <c r="E159" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F159" s="14" t="str">
-        <f>IF(UPPER(D160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F160," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C160," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F161," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C161," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F162," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C162," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F163," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C163," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C164," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G159" s="14" t="str">
         <f>'data'!$B$14</f>
@@ -9983,17 +9983,17 @@
         <f>'data'!$B$60</f>
       </c>
       <c r="J159" s="14" t="str">
-        <f>IF(UPPER(L160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K159" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L159" s="18"/>
       <c r="M159" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N159" s="14" t="str">
-        <f>IF(UPPER(L160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L160)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N160," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J160," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K160," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L161)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N161," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J161," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K161," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L162)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N162," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J162," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K162," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L163)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N163," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J163," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K163," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L164)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N164," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J164," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K164," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O159" s="14" t="str">
         <f>'data'!$B$59</f>
@@ -10522,17 +10522,17 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="B186" s="14" t="str">
-        <f>IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C186" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D186" s="18"/>
       <c r="E186" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F186" s="14" t="str">
-        <f>IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F190," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C190," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C191," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G186" s="14" t="str">
         <f>'data'!$B$16</f>
@@ -10541,17 +10541,17 @@
         <f>'data'!$B$62</f>
       </c>
       <c r="J186" s="14" t="str">
-        <f>IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K186" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L186" s="18"/>
       <c r="M186" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N186" s="14" t="str">
-        <f>IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L190)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N190," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J190," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K190," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L191)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N191," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J191," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K191," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O186" s="14" t="str">
         <f>'data'!$B$61</f>
@@ -10710,17 +10710,17 @@
         <f>'data'!$B$18</f>
       </c>
       <c r="B194" s="14" t="str">
-        <f>IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C194" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D194" s="18"/>
       <c r="E194" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F194" s="14" t="str">
-        <f>IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G194" s="14" t="str">
         <f>'data'!$B$16</f>
@@ -10729,17 +10729,17 @@
         <f>'data'!$B$63</f>
       </c>
       <c r="J194" s="14" t="str">
-        <f>IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K194" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L194" s="18"/>
       <c r="M194" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N194" s="14" t="str">
-        <f>IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O194" s="14" t="str">
         <f>'data'!$B$61</f>
@@ -10898,17 +10898,17 @@
         <f>'data'!$B$18</f>
       </c>
       <c r="B202" s="14" t="str">
-        <f>IF(UPPER(D203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C202" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D202" s="18"/>
       <c r="E202" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F202" s="14" t="str">
-        <f>IF(UPPER(D203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F203," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C203," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F204," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C204," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F205," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C205," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F206," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C206," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C207," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G202" s="14" t="str">
         <f>'data'!$B$17</f>
@@ -10917,17 +10917,17 @@
         <f>'data'!$B$63</f>
       </c>
       <c r="J202" s="14" t="str">
-        <f>IF(UPPER(L203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K202" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L202" s="18"/>
       <c r="M202" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N202" s="14" t="str">
-        <f>IF(UPPER(L203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L203)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N203," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J203," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K203," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L204)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N204," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J204," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K204," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L205)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N205," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J205," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K205," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L206)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N206," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J206," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K206," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L207)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N207," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J207," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K207," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O202" s="14" t="str">
         <f>'data'!$B$62</f>
@@ -11456,17 +11456,17 @@
         <f>'data'!$B$20</f>
       </c>
       <c r="B229" s="14" t="str">
-        <f>IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C229" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D229" s="18"/>
       <c r="E229" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F229" s="14" t="str">
-        <f>IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C234," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G229" s="14" t="str">
         <f>'data'!$B$19</f>
@@ -11475,17 +11475,17 @@
         <f>'data'!$B$65</f>
       </c>
       <c r="J229" s="14" t="str">
-        <f>IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K229" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L229" s="18"/>
       <c r="M229" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N229" s="14" t="str">
-        <f>IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L234)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N234," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J234," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K234," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O229" s="14" t="str">
         <f>'data'!$B$64</f>
@@ -11644,17 +11644,17 @@
         <f>'data'!$B$21</f>
       </c>
       <c r="B237" s="14" t="str">
-        <f>IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C237" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D237" s="18"/>
       <c r="E237" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F237" s="14" t="str">
-        <f>IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F241," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C241," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C242," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G237" s="14" t="str">
         <f>'data'!$B$19</f>
@@ -11663,17 +11663,17 @@
         <f>'data'!$B$66</f>
       </c>
       <c r="J237" s="14" t="str">
-        <f>IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K237" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L237" s="18"/>
       <c r="M237" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N237" s="14" t="str">
-        <f>IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L241)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N241," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J241," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K241," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L242)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N242," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J242," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K242," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O237" s="14" t="str">
         <f>'data'!$B$64</f>
@@ -11832,17 +11832,17 @@
         <f>'data'!$B$21</f>
       </c>
       <c r="B245" s="14" t="str">
-        <f>IF(UPPER(D246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C245" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D245" s="18"/>
       <c r="E245" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F245" s="14" t="str">
-        <f>IF(UPPER(D246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F246," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C246," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F247," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C247," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F248," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C248," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F249," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C249," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G245" s="14" t="str">
         <f>'data'!$B$20</f>
@@ -11851,17 +11851,17 @@
         <f>'data'!$B$66</f>
       </c>
       <c r="J245" s="14" t="str">
-        <f>IF(UPPER(L246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K245" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L245" s="18"/>
       <c r="M245" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N245" s="14" t="str">
-        <f>IF(UPPER(L246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L246)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N246," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J246," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K246," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L247)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N247," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J247," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K247," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L248)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N248," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J248," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K248," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L249)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N249," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J249," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K249," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O245" s="14" t="str">
         <f>'data'!$B$65</f>
@@ -12390,17 +12390,17 @@
         <f>'data'!$B$23</f>
       </c>
       <c r="B272" s="14" t="str">
-        <f>IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C272" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D272" s="18"/>
       <c r="E272" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F272" s="14" t="str">
-        <f>IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F276," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C276," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C277," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G272" s="14" t="str">
         <f>'data'!$B$22</f>
@@ -12409,17 +12409,17 @@
         <f>'data'!$B$68</f>
       </c>
       <c r="J272" s="14" t="str">
-        <f>IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K272" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L272" s="18"/>
       <c r="M272" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N272" s="14" t="str">
-        <f>IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L276)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N276," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J276," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K276," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L277)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N277," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J277," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K277," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O272" s="14" t="str">
         <f>'data'!$B$67</f>
@@ -12578,17 +12578,17 @@
         <f>'data'!$B$24</f>
       </c>
       <c r="B280" s="14" t="str">
-        <f>IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C280" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D280" s="18"/>
       <c r="E280" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F280" s="14" t="str">
-        <f>IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G280" s="14" t="str">
         <f>'data'!$B$22</f>
@@ -12597,17 +12597,17 @@
         <f>'data'!$B$69</f>
       </c>
       <c r="J280" s="14" t="str">
-        <f>IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K280" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L280" s="18"/>
       <c r="M280" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N280" s="14" t="str">
-        <f>IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O280" s="14" t="str">
         <f>'data'!$B$67</f>
@@ -12766,17 +12766,17 @@
         <f>'data'!$B$24</f>
       </c>
       <c r="B288" s="14" t="str">
-        <f>IF(UPPER(D289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C288" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D288" s="18"/>
       <c r="E288" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F288" s="14" t="str">
-        <f>IF(UPPER(D289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F289," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C289," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F290," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C290," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F291," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C291," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F292," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C292," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C293," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G288" s="14" t="str">
         <f>'data'!$B$23</f>
@@ -12785,17 +12785,17 @@
         <f>'data'!$B$69</f>
       </c>
       <c r="J288" s="14" t="str">
-        <f>IF(UPPER(L289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K288" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L288" s="18"/>
       <c r="M288" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N288" s="14" t="str">
-        <f>IF(UPPER(L289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L289)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N289," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J289," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K289," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L290)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N290," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J290," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K290," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L291)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N291," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J291," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K291," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L292)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N292," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J292," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K292," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L293)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N293," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J293," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K293," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O288" s="14" t="str">
         <f>'data'!$B$68</f>
@@ -13324,17 +13324,17 @@
         <f>'data'!$B$26</f>
       </c>
       <c r="B315" s="14" t="str">
-        <f>IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C315" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D315" s="18"/>
       <c r="E315" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F315" s="14" t="str">
-        <f>IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F319," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C319," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C320," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G315" s="14" t="str">
         <f>'data'!$B$25</f>
@@ -13343,17 +13343,17 @@
         <f>'data'!$B$71</f>
       </c>
       <c r="J315" s="14" t="str">
-        <f>IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K315" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L315" s="18"/>
       <c r="M315" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N315" s="14" t="str">
-        <f>IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L319)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N319," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J319," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K319," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L320)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N320," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J320," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K320," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O315" s="14" t="str">
         <f>'data'!$B$70</f>
@@ -13512,17 +13512,17 @@
         <f>'data'!$B$27</f>
       </c>
       <c r="B323" s="14" t="str">
-        <f>IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C323" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D323" s="18"/>
       <c r="E323" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F323" s="14" t="str">
-        <f>IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F327," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C327," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C328," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G323" s="14" t="str">
         <f>'data'!$B$25</f>
@@ -13531,17 +13531,17 @@
         <f>'data'!$B$72</f>
       </c>
       <c r="J323" s="14" t="str">
-        <f>IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K323" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L323" s="18"/>
       <c r="M323" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N323" s="14" t="str">
-        <f>IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L327)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N327," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J327," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K327," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L328)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N328," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J328," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K328," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O323" s="14" t="str">
         <f>'data'!$B$70</f>
@@ -13700,17 +13700,17 @@
         <f>'data'!$B$27</f>
       </c>
       <c r="B331" s="14" t="str">
-        <f>IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C331" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D331" s="18"/>
       <c r="E331" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F331" s="14" t="str">
-        <f>IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F335," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C335," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C336," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G331" s="14" t="str">
         <f>'data'!$B$26</f>
@@ -13719,17 +13719,17 @@
         <f>'data'!$B$72</f>
       </c>
       <c r="J331" s="14" t="str">
-        <f>IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K331" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L331" s="18"/>
       <c r="M331" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N331" s="14" t="str">
-        <f>IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L335)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N335," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J335," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K335," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L336)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N336," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J336," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K336," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O331" s="14" t="str">
         <f>'data'!$B$71</f>
@@ -14258,17 +14258,17 @@
         <f>'data'!$B$29</f>
       </c>
       <c r="B358" s="14" t="str">
-        <f>IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C358" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D358" s="18"/>
       <c r="E358" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F358" s="14" t="str">
-        <f>IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G358" s="14" t="str">
         <f>'data'!$B$28</f>
@@ -14277,17 +14277,17 @@
         <f>'data'!$B$74</f>
       </c>
       <c r="J358" s="14" t="str">
-        <f>IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K358" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L358" s="18"/>
       <c r="M358" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N358" s="14" t="str">
-        <f>IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O358" s="14" t="str">
         <f>'data'!$B$73</f>
@@ -14446,17 +14446,17 @@
         <f>'data'!$B$30</f>
       </c>
       <c r="B366" s="14" t="str">
-        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C366" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D366" s="18"/>
       <c r="E366" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F366" s="14" t="str">
-        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F370," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C370," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C371," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G366" s="14" t="str">
         <f>'data'!$B$28</f>
@@ -14465,17 +14465,17 @@
         <f>'data'!$B$75</f>
       </c>
       <c r="J366" s="14" t="str">
-        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K366" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L366" s="18"/>
       <c r="M366" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N366" s="14" t="str">
-        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L370)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N370," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J370," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K370," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L371)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N371," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J371," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K371," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O366" s="14" t="str">
         <f>'data'!$B$73</f>
@@ -14634,17 +14634,17 @@
         <f>'data'!$B$30</f>
       </c>
       <c r="B374" s="14" t="str">
-        <f>IF(UPPER(D375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C374" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D374" s="18"/>
       <c r="E374" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F374" s="14" t="str">
-        <f>IF(UPPER(D375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F375," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C375," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F376," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C376," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F377," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C377," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F378," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C378," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C379," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G374" s="14" t="str">
         <f>'data'!$B$29</f>
@@ -14653,17 +14653,17 @@
         <f>'data'!$B$75</f>
       </c>
       <c r="J374" s="14" t="str">
-        <f>IF(UPPER(L375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K374" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L374" s="18"/>
       <c r="M374" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N374" s="14" t="str">
-        <f>IF(UPPER(L375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L375)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N375," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J375," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K375," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L376)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N376," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J376," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K376," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L377)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N377," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J377," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K377," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L378)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N378," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J378," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K378," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L379)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N379," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J379," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K379," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O374" s="14" t="str">
         <f>'data'!$B$74</f>
@@ -15192,17 +15192,17 @@
         <f>'data'!$B$32</f>
       </c>
       <c r="B401" s="14" t="str">
-        <f>IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C401" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D401" s="18"/>
       <c r="E401" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F401" s="14" t="str">
-        <f>IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F405," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C405," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C406," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G401" s="14" t="str">
         <f>'data'!$B$31</f>
@@ -15211,17 +15211,17 @@
         <f>'data'!$B$77</f>
       </c>
       <c r="J401" s="14" t="str">
-        <f>IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K401" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L401" s="18"/>
       <c r="M401" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N401" s="14" t="str">
-        <f>IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L405)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N405," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J405," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K405," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L406)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N406," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J406," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K406," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O401" s="14" t="str">
         <f>'data'!$B$76</f>
@@ -15380,17 +15380,17 @@
         <f>'data'!$B$33</f>
       </c>
       <c r="B409" s="14" t="str">
-        <f>IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C409" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D409" s="18"/>
       <c r="E409" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F409" s="14" t="str">
-        <f>IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F413," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C413," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C414," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G409" s="14" t="str">
         <f>'data'!$B$31</f>
@@ -15399,17 +15399,17 @@
         <f>'data'!$B$78</f>
       </c>
       <c r="J409" s="14" t="str">
-        <f>IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K409" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L409" s="18"/>
       <c r="M409" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N409" s="14" t="str">
-        <f>IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L413)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N413," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J413," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K413," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L414)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N414," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J414," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K414," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O409" s="14" t="str">
         <f>'data'!$B$76</f>
@@ -15568,17 +15568,17 @@
         <f>'data'!$B$33</f>
       </c>
       <c r="B417" s="14" t="str">
-        <f>IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C417" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D417" s="18"/>
       <c r="E417" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F417" s="14" t="str">
-        <f>IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F420," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C420," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F421," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C421," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C422," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G417" s="14" t="str">
         <f>'data'!$B$32</f>
@@ -15587,17 +15587,17 @@
         <f>'data'!$B$78</f>
       </c>
       <c r="J417" s="14" t="str">
-        <f>IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K417" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L417" s="18"/>
       <c r="M417" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N417" s="14" t="str">
-        <f>IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L420)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N420," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J420," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K420," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L421)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N421," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J421," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K421," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L422)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N422," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J422," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K422," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O417" s="14" t="str">
         <f>'data'!$B$77</f>
@@ -16126,17 +16126,17 @@
         <f>'data'!$B$35</f>
       </c>
       <c r="B444" s="14" t="str">
-        <f>IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C444" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D444" s="18"/>
       <c r="E444" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F444" s="14" t="str">
-        <f>IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F448," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C448," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C449," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G444" s="14" t="str">
         <f>'data'!$B$34</f>
@@ -16145,17 +16145,17 @@
         <f>'data'!$B$80</f>
       </c>
       <c r="J444" s="14" t="str">
-        <f>IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K444" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L444" s="18"/>
       <c r="M444" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N444" s="14" t="str">
-        <f>IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L448)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N448," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J448," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K448," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L449)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N449," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J449," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K449," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O444" s="14" t="str">
         <f>'data'!$B$79</f>
@@ -16314,17 +16314,17 @@
         <f>'data'!$B$36</f>
       </c>
       <c r="B452" s="14" t="str">
-        <f>IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C452" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D452" s="18"/>
       <c r="E452" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F452" s="14" t="str">
-        <f>IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C457," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G452" s="14" t="str">
         <f>'data'!$B$34</f>
@@ -16333,17 +16333,17 @@
         <f>'data'!$B$81</f>
       </c>
       <c r="J452" s="14" t="str">
-        <f>IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K452" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L452" s="18"/>
       <c r="M452" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N452" s="14" t="str">
-        <f>IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L457)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N457," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J457," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K457," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O452" s="14" t="str">
         <f>'data'!$B$79</f>
@@ -16502,17 +16502,17 @@
         <f>'data'!$B$36</f>
       </c>
       <c r="B460" s="14" t="str">
-        <f>IF(UPPER(D461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C460" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D460" s="18"/>
       <c r="E460" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F460" s="14" t="str">
-        <f>IF(UPPER(D461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F461," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C461," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F462," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C462," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F463," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C463," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F464," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C464," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C465," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G460" s="14" t="str">
         <f>'data'!$B$35</f>
@@ -16521,17 +16521,17 @@
         <f>'data'!$B$81</f>
       </c>
       <c r="J460" s="14" t="str">
-        <f>IF(UPPER(L461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K460" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L460" s="18"/>
       <c r="M460" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N460" s="14" t="str">
-        <f>IF(UPPER(L461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L461)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N461," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J461," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K461," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L462)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N462," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J462," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K462," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L463)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N463," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J463," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K463," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L464)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N464," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J464," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K464," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L465)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N465," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J465," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K465," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O460" s="14" t="str">
         <f>'data'!$B$80</f>
@@ -17060,17 +17060,17 @@
         <f>'data'!$B$38</f>
       </c>
       <c r="B487" s="14" t="str">
-        <f>IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C487" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D487" s="18"/>
       <c r="E487" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F487" s="14" t="str">
-        <f>IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G487" s="14" t="str">
         <f>'data'!$B$37</f>
@@ -17079,17 +17079,17 @@
         <f>'data'!$B$83</f>
       </c>
       <c r="J487" s="14" t="str">
-        <f>IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K487" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L487" s="18"/>
       <c r="M487" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N487" s="14" t="str">
-        <f>IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O487" s="14" t="str">
         <f>'data'!$B$82</f>
@@ -17248,17 +17248,17 @@
         <f>'data'!$B$39</f>
       </c>
       <c r="B495" s="14" t="str">
-        <f>IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C495" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D495" s="18"/>
       <c r="E495" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F495" s="14" t="str">
-        <f>IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F499," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C499," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C500," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G495" s="14" t="str">
         <f>'data'!$B$37</f>
@@ -17267,17 +17267,17 @@
         <f>'data'!$B$84</f>
       </c>
       <c r="J495" s="14" t="str">
-        <f>IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K495" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L495" s="18"/>
       <c r="M495" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N495" s="14" t="str">
-        <f>IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L499)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N499," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J499," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K499," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L500)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N500," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J500," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K500," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O495" s="14" t="str">
         <f>'data'!$B$82</f>
@@ -17436,17 +17436,17 @@
         <f>'data'!$B$39</f>
       </c>
       <c r="B503" s="14" t="str">
-        <f>IF(UPPER(D504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C503" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D503" s="18"/>
       <c r="E503" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F503" s="14" t="str">
-        <f>IF(UPPER(D504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F504," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C504," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F505," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C505," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F506," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C506," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F507," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C507," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C508," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G503" s="14" t="str">
         <f>'data'!$B$38</f>
@@ -17455,17 +17455,17 @@
         <f>'data'!$B$84</f>
       </c>
       <c r="J503" s="14" t="str">
-        <f>IF(UPPER(L504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K503" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L503" s="18"/>
       <c r="M503" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N503" s="14" t="str">
-        <f>IF(UPPER(L504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L504)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N504," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J504," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K504," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L505)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N505," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J505," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K505," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L506)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N506," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J506," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K506," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L507)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N507," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J507," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K507," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L508)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N508," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J508," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K508," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O503" s="14" t="str">
         <f>'data'!$B$83</f>
@@ -17994,17 +17994,17 @@
         <f>'data'!$B$41</f>
       </c>
       <c r="B530" s="14" t="str">
-        <f>IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C530" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D530" s="18"/>
       <c r="E530" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F530" s="14" t="str">
-        <f>IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F534," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C534," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C535," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G530" s="14" t="str">
         <f>'data'!$B$40</f>
@@ -18013,17 +18013,17 @@
         <f>'data'!$B$86</f>
       </c>
       <c r="J530" s="14" t="str">
-        <f>IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K530" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L530" s="18"/>
       <c r="M530" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N530" s="14" t="str">
-        <f>IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L534)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N534," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J534," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K534," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L535)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N535," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J535," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K535," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O530" s="14" t="str">
         <f>'data'!$B$85</f>
@@ -18182,17 +18182,17 @@
         <f>'data'!$B$42</f>
       </c>
       <c r="B538" s="14" t="str">
-        <f>IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C538" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D538" s="18"/>
       <c r="E538" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F538" s="14" t="str">
-        <f>IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F542," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C542," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C543," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G538" s="14" t="str">
         <f>'data'!$B$40</f>
@@ -18201,17 +18201,17 @@
         <f>'data'!$B$87</f>
       </c>
       <c r="J538" s="14" t="str">
-        <f>IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K538" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L538" s="18"/>
       <c r="M538" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N538" s="14" t="str">
-        <f>IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L542)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N542," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J542," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K542," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L543)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N543," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J543," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K543," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O538" s="14" t="str">
         <f>'data'!$B$85</f>
@@ -18370,17 +18370,17 @@
         <f>'data'!$B$42</f>
       </c>
       <c r="B546" s="14" t="str">
-        <f>IF(UPPER(D547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C546" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D546" s="18"/>
       <c r="E546" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F546" s="14" t="str">
-        <f>IF(UPPER(D547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F547," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C547," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F548," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C548," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F549," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C549," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F550," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C550," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C551," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G546" s="14" t="str">
         <f>'data'!$B$41</f>
@@ -18389,17 +18389,17 @@
         <f>'data'!$B$87</f>
       </c>
       <c r="J546" s="14" t="str">
-        <f>IF(UPPER(L547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K546" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L546" s="18"/>
       <c r="M546" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N546" s="14" t="str">
-        <f>IF(UPPER(L547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L547)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N547," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J547," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K547," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L548)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N548," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J548," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K548," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L549)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N549," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J549," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K549," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L550)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N550," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J550," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K550," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L551)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N551," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J551," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K551," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O546" s="14" t="str">
         <f>'data'!$B$86</f>
@@ -18928,17 +18928,17 @@
         <f>'data'!$B$44</f>
       </c>
       <c r="B573" s="14" t="str">
-        <f>IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C573" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D573" s="18"/>
       <c r="E573" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F573" s="14" t="str">
-        <f>IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F577," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C577," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C578," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G573" s="14" t="str">
         <f>'data'!$B$43</f>
@@ -18947,17 +18947,17 @@
         <f>'data'!$B$89</f>
       </c>
       <c r="J573" s="14" t="str">
-        <f>IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K573" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L573" s="18"/>
       <c r="M573" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N573" s="14" t="str">
-        <f>IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L577)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N577," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J577," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K577," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L578)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N578," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J578," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K578," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O573" s="14" t="str">
         <f>'data'!$B$88</f>
@@ -19116,17 +19116,17 @@
         <f>'data'!$B$45</f>
       </c>
       <c r="B581" s="14" t="str">
-        <f>IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C581" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D581" s="18"/>
       <c r="E581" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F581" s="14" t="str">
-        <f>IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F585," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C585," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C586," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G581" s="14" t="str">
         <f>'data'!$B$43</f>
@@ -19135,17 +19135,17 @@
         <f>'data'!$B$90</f>
       </c>
       <c r="J581" s="14" t="str">
-        <f>IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K581" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L581" s="18"/>
       <c r="M581" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N581" s="14" t="str">
-        <f>IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L585)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N585," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J585," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K585," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L586)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N586," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J586," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K586," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O581" s="14" t="str">
         <f>'data'!$B$88</f>
@@ -19304,17 +19304,17 @@
         <f>'data'!$B$45</f>
       </c>
       <c r="B589" s="14" t="str">
-        <f>IF(UPPER(D590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C589" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D589" s="18"/>
       <c r="E589" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F589" s="14" t="str">
-        <f>IF(UPPER(D590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F590," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C590," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F591," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C591," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F592," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C592," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F593," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C593," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C594," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G589" s="14" t="str">
         <f>'data'!$B$44</f>
@@ -19323,17 +19323,17 @@
         <f>'data'!$B$90</f>
       </c>
       <c r="J589" s="14" t="str">
-        <f>IF(UPPER(L590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K589" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L589" s="18"/>
       <c r="M589" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N589" s="14" t="str">
-        <f>IF(UPPER(L590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L590)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N590," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J590," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K590," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L591)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N591," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J591," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K591," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L592)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N592," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J592," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K592," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L593)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N593," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J593," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K593," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L594)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N594," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J594," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K594," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O589" s="14" t="str">
         <f>'data'!$B$89</f>
@@ -19862,17 +19862,17 @@
         <f>'data'!$B$47</f>
       </c>
       <c r="B616" s="14" t="str">
-        <f>IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C616" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D616" s="18"/>
       <c r="E616" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F616" s="14" t="str">
-        <f>IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F620," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C620," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C621," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G616" s="14" t="str">
         <f>'data'!$B$46</f>
@@ -19881,17 +19881,17 @@
         <f>'data'!$B$92</f>
       </c>
       <c r="J616" s="14" t="str">
-        <f>IF(UPPER(L617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K616" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L616" s="18"/>
       <c r="M616" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N616" s="14" t="str">
-        <f>IF(UPPER(L617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N617," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K617," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N618," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K618," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K619," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L620)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N620," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J620," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K620," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L621)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N621," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J621," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K621," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O616" s="14" t="str">
         <f>'data'!$B$91</f>
@@ -20050,17 +20050,17 @@
         <f>'data'!$B$48</f>
       </c>
       <c r="B624" s="14" t="str">
-        <f>IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D628)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C628," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F628," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D629)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C629," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F629," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D628)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B628," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C628," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E628," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F628," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D629)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C629," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F629," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C624" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C629," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B628," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C628," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B629," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C629," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D624" s="18"/>
       <c r="E624" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F628," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E629," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F629," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-",""))+LEN(SUBSTITU